--- a/data/template/boq/BOQ Documentation.xlsx
+++ b/data/template/boq/BOQ Documentation.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\JACOBS\SERVICE\API\data\template\boq\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6EFABEB1-59CA-48F2-9C0E-B5952CC0B513}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F8A2A263-974A-404F-B2E5-6E06898FFC61}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12105" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12105" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Save" sheetId="3" r:id="rId1"/>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2029" uniqueCount="921">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1323" uniqueCount="859">
   <si>
     <t>program</t>
   </si>
@@ -1730,9 +1730,6 @@
     <t>Testing</t>
   </si>
   <si>
-    <t>Note</t>
-  </si>
-  <si>
     <t>area_city</t>
   </si>
   <si>
@@ -1751,51 +1748,27 @@
     <t>prep_a1_rambu_papan</t>
   </si>
   <si>
-    <t>signage + safety boards</t>
-  </si>
-  <si>
     <t>prep_a2_direksi_keet</t>
   </si>
   <si>
-    <t>basecamp/shelter</t>
-  </si>
-  <si>
     <t>prep_a3_koordinasi_pu</t>
   </si>
   <si>
-    <t>warga + PU permit</t>
-  </si>
-  <si>
     <t>prep_a4_koordinasi_pjka</t>
   </si>
   <si>
-    <t>railway permit</t>
-  </si>
-  <si>
     <t>prep_a5_koordinasi_toll</t>
   </si>
   <si>
-    <t>toll road permit</t>
-  </si>
-  <si>
     <t>prep_a6_koordinasi_private_supervise</t>
   </si>
   <si>
-    <t>private/community + supervise</t>
-  </si>
-  <si>
     <t>prep_a7_survey_abd</t>
   </si>
   <si>
-    <t>survey + ABD/KML</t>
-  </si>
-  <si>
     <t>prep_a8_mobilisasi_transport</t>
   </si>
   <si>
-    <t>mobilization</t>
-  </si>
-  <si>
     <t>Categories</t>
   </si>
   <si>
@@ -1811,45 +1784,21 @@
     <t>mat_fo_aerial_12_m</t>
   </si>
   <si>
-    <t>Aerial FO cable 12 core (meter)</t>
-  </si>
-  <si>
     <t>mat_fo_aerial_24_m</t>
   </si>
   <si>
-    <t>Aerial FO cable 24 core</t>
-  </si>
-  <si>
     <t>mat_fo_aerial_48_m</t>
   </si>
   <si>
-    <t>Aerial FO cable 48 core</t>
-  </si>
-  <si>
     <t>mat_fo_aerial_72_m</t>
   </si>
   <si>
-    <t>Aerial FO cable 72 core</t>
-  </si>
-  <si>
     <t>mat_fo_aerial_96_m</t>
   </si>
   <si>
-    <t>Aerial FO cable 96 core</t>
-  </si>
-  <si>
     <t>mat_fo_aerial_144_m</t>
   </si>
   <si>
-    <t>Aerial FO cable 144 core</t>
-  </si>
-  <si>
-    <t>Variable Name</t>
-  </si>
-  <si>
-    <t>Item Code</t>
-  </si>
-  <si>
     <t>mat_fo_adss_12_m</t>
   </si>
   <si>
@@ -1940,9 +1889,6 @@
     <t>mat_closure_dome_24_qty</t>
   </si>
   <si>
-    <t>qty</t>
-  </si>
-  <si>
     <t>mat_closure_dome_48_qty</t>
   </si>
   <si>
@@ -1973,93 +1919,48 @@
     <t>mat_otb_12_sc_upc_qty</t>
   </si>
   <si>
-    <t>OTB Capacity 12 Core SC-UPC</t>
-  </si>
-  <si>
     <t>mat_otb_12_fc_upc_qty</t>
   </si>
   <si>
-    <t>OTB Capacity 12 Core FC-UPC</t>
-  </si>
-  <si>
     <t>mat_otb_24_sc_upc_qty</t>
   </si>
   <si>
-    <t>OTB Capacity 24 Core SC-UPC</t>
-  </si>
-  <si>
     <t>mat_otb_24_fc_upc_qty</t>
   </si>
   <si>
-    <t>OTB Capacity 24 Core FC-UPC</t>
-  </si>
-  <si>
     <t>mat_otb_48_sc_upc_qty</t>
   </si>
   <si>
-    <t>OTB Capacity 48 Core SC-UPC</t>
-  </si>
-  <si>
     <t>mat_otb_96_sc_upc_qty</t>
   </si>
   <si>
-    <t>OTB Capacity 96 Core SC-UPC</t>
-  </si>
-  <si>
     <t>mat_otb_144_sc_upc_qty</t>
   </si>
   <si>
-    <t>OTB Capacity 144 Core SC-UPC</t>
-  </si>
-  <si>
     <t>mat_otb_288_sc_upc_qty</t>
   </si>
   <si>
-    <t>OTB Capacity 288 Core SC-UPC</t>
-  </si>
-  <si>
     <t>mat_otb_288_lc_upc_hd_qty</t>
   </si>
   <si>
-    <t>OTB Capacity 288 Core LC-UPC High Density</t>
-  </si>
-  <si>
     <t>mat_odp_4_sc_upc_qty</t>
   </si>
   <si>
-    <t>ODP Capacity 4 Core SC-UPC</t>
-  </si>
-  <si>
     <t>mat_odp_8_sc_upc_qty</t>
   </si>
   <si>
-    <t>ODP Capacity 8 Core SC-UPC</t>
-  </si>
-  <si>
     <t>mat_odp_16_sc_upc_qty</t>
   </si>
   <si>
-    <t>ODP Capacity 16 Core SC-UPC</t>
-  </si>
-  <si>
     <t>mat_odp_24_sc_upc_qty</t>
   </si>
   <si>
-    <t>ODP Capacity 24 Core SC-UPC</t>
-  </si>
-  <si>
     <t>mat_odp_96_sc_upc_qty</t>
   </si>
   <si>
-    <t>ODP Capacity 96 Core SC-UPC</t>
-  </si>
-  <si>
     <t>mat_odp_pedestal_16_ug_qty</t>
   </si>
   <si>
-    <t>ODP Pedestal 16 Core Underground</t>
-  </si>
-  <si>
     <t>mat_splitter_1to2_sc_upc_qty</t>
   </si>
   <si>
@@ -2087,66 +1988,36 @@
     <t>mat_hdpe_subduct_32_27_qty</t>
   </si>
   <si>
-    <t>HDPE Pipe Subduct 32/27</t>
-  </si>
-  <si>
     <t>mat_hdpe_subduct_40_33_qty</t>
   </si>
   <si>
-    <t>HDPE Pipe Subduct 40/33</t>
-  </si>
-  <si>
     <t>mat_hdpe_subduct_50_43_qty</t>
   </si>
   <si>
-    <t>HDPE Pipe Subduct 50/43</t>
-  </si>
-  <si>
     <t>mat_hdpe_microduct_4way_12_10_qty</t>
   </si>
   <si>
-    <t>HDPE Pipe Micro Duct 4 Way 12/10</t>
-  </si>
-  <si>
     <t>mat_hdpe_microduct_7way_12_10_qty</t>
   </si>
   <si>
-    <t>HDPE Pipe Micro Duct 7 Way 12/10</t>
-  </si>
-  <si>
     <t>mat_hdpe_microduct_14way_12_10_qty</t>
   </si>
   <si>
-    <t>HDPE Pipe Micro Duct 14 Way 12/10</t>
-  </si>
-  <si>
     <t>mat_hdpe_microduct_4way_18_14_qty</t>
   </si>
   <si>
-    <t>HDPE Pipe Micro Duct 4 Way 18/14</t>
-  </si>
-  <si>
     <t>mat_hdpe_microduct_7way_18_14_qty</t>
   </si>
   <si>
-    <t>HDPE Pipe Micro Duct 7 Way 18/14</t>
-  </si>
-  <si>
     <t>mat_hdpe_microduct_14way_18_14_qty</t>
   </si>
   <si>
-    <t>HDPE Pipe Micro Duct 14 Way 18/14</t>
-  </si>
-  <si>
     <t>mat_gi_pipe_1in_qty</t>
   </si>
   <si>
     <t>mat_gi_pipe_1p5in_qty</t>
   </si>
   <si>
-    <t>Galvanized Pipe 1½ inch</t>
-  </si>
-  <si>
     <t>mat_gi_pipe_2in_qty</t>
   </si>
   <si>
@@ -2165,9 +2036,6 @@
     <t>mat_pvc_pipe_1p5in_qty</t>
   </si>
   <si>
-    <t>PVC Pipe 1½ inch</t>
-  </si>
-  <si>
     <t>mat_pvc_pipe_2in_qty</t>
   </si>
   <si>
@@ -2183,108 +2051,57 @@
     <t>mat_flex_conduit_0p75in_qty</t>
   </si>
   <si>
-    <t>Flexible Conduit Armor ¾ inch</t>
-  </si>
-  <si>
     <t>mat_flex_conduit_2in_qty</t>
   </si>
   <si>
-    <t>Flexible Conduit Armor 2 inch</t>
-  </si>
-  <si>
     <t>mat_flex_conduit_3in_qty</t>
   </si>
   <si>
-    <t>Flexible Conduit Armor 3 inch</t>
-  </si>
-  <si>
     <t>mat_flex_conduit_20mm_qty</t>
   </si>
   <si>
-    <t>Flexible Conduit 20 mm</t>
-  </si>
-  <si>
     <t>mat_rack_open_42u_qty</t>
   </si>
   <si>
-    <t>Open Rack 42 U</t>
-  </si>
-  <si>
     <t>mat_rack_closed_8u_450_qty</t>
   </si>
   <si>
-    <t>Closed Rack 8U-450 mm</t>
-  </si>
-  <si>
     <t>mat_rack_closed_20u_900_qty</t>
   </si>
   <si>
-    <t>Closed Rack 20U-900 mm</t>
-  </si>
-  <si>
     <t>mat_rack_closed_42u_900_qty</t>
   </si>
   <si>
-    <t>Closed Rack 42U-900 mm</t>
-  </si>
-  <si>
     <t>mat_rack_closed_42u_1150_qty</t>
   </si>
   <si>
-    <t>Closed Rack 42U-1150 mm</t>
-  </si>
-  <si>
     <t>mat_odc_144_qty</t>
   </si>
   <si>
-    <t>ODC Cap 144 Core</t>
-  </si>
-  <si>
     <t>mat_odc_288_qty</t>
   </si>
   <si>
-    <t>ODC Cap 288 Core</t>
-  </si>
-  <si>
     <t>mat_odc_576_qty</t>
   </si>
   <si>
-    <t>ODC Cap 576 Core</t>
-  </si>
-  <si>
     <t>mat_warning_tape_fo_6in_m</t>
   </si>
   <si>
     <t>mat_pole_fo_7m_2step_qty</t>
   </si>
   <si>
-    <t>Pole Fiber Optic 7 m 2 Step</t>
-  </si>
-  <si>
     <t>mat_pole_fo_9m_3step_qty</t>
   </si>
   <si>
-    <t>Pole Fiber Optic 9 m 3 Step</t>
-  </si>
-  <si>
     <t>mat_slack_support_50x50x3_qty</t>
   </si>
   <si>
-    <t>Slack Support + Clamp 50×50×3 mm</t>
-  </si>
-  <si>
     <t>mat_pole_fo_12m_3step_qty</t>
   </si>
   <si>
-    <t>Pole Fiber Optic 12 m 3 Step</t>
-  </si>
-  <si>
     <t>mat_slack_support_70x70x3_qty</t>
   </si>
   <si>
-    <t>Slack Support + Clamp 70×70×3 mm</t>
-  </si>
-  <si>
     <t>mat_patch_indoor_sm_sc_upc_sc_upc_5m</t>
   </si>
   <si>
@@ -2358,9 +2175,6 @@
   </si>
   <si>
     <t>mat_adapter_fc_sc_hybrid_qty</t>
-  </si>
-  <si>
-    <t>Code</t>
   </si>
   <si>
     <t>svc_trenching_reinstate_hotmix_m</t>
@@ -2926,7 +2740,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="29">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -2936,38 +2750,7 @@
     <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2993,6 +2776,33 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -3296,7 +3106,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6EE5A39B-3467-4561-B304-6288CE016003}">
-  <dimension ref="A1:T263"/>
+  <dimension ref="A1:M263"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.140625" style="1"/>
@@ -3308,54 +3118,50 @@
     <col min="8" max="8" width="8" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="5.140625" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="50.5703125" style="1" customWidth="1"/>
-    <col min="17" max="17" width="29.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A1" s="19" t="s">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A1" s="9" t="s">
         <v>3</v>
       </c>
-      <c r="B1" s="19" t="s">
-        <v>591</v>
-      </c>
-      <c r="C1" s="19" t="s">
-        <v>592</v>
-      </c>
-      <c r="D1" s="19" t="s">
-        <v>594</v>
-      </c>
-      <c r="E1" s="19" t="s">
+      <c r="B1" s="9" t="s">
+        <v>582</v>
+      </c>
+      <c r="C1" s="9" t="s">
+        <v>583</v>
+      </c>
+      <c r="D1" s="9" t="s">
+        <v>585</v>
+      </c>
+      <c r="E1" s="9" t="s">
         <v>551</v>
       </c>
-      <c r="F1" s="19" t="s">
+      <c r="F1" s="9" t="s">
         <v>467</v>
       </c>
-      <c r="G1" s="19" t="s">
+      <c r="G1" s="9" t="s">
         <v>264</v>
       </c>
-      <c r="H1" s="19" t="s">
+      <c r="H1" s="9" t="s">
         <v>429</v>
       </c>
-      <c r="I1" s="19" t="s">
+      <c r="I1" s="9" t="s">
         <v>460</v>
       </c>
-      <c r="J1" s="19" t="s">
-        <v>573</v>
-      </c>
-      <c r="K1" s="19" t="s">
+      <c r="J1" s="9" t="s">
+        <v>572</v>
+      </c>
+      <c r="K1" s="9" t="s">
         <v>2</v>
       </c>
-      <c r="L1" s="19" t="s">
+      <c r="L1" s="9" t="s">
         <v>552</v>
       </c>
-      <c r="M1" s="19" t="s">
+      <c r="M1" s="9" t="s">
         <v>553</v>
       </c>
-      <c r="N1" s="20" t="s">
-        <v>569</v>
-      </c>
-    </row>
-    <row r="2" spans="1:14" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="2" spans="1:13" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="2">
         <v>1</v>
       </c>
@@ -3375,9 +3181,8 @@
       <c r="K2" s="2"/>
       <c r="L2" s="2"/>
       <c r="M2" s="2"/>
-      <c r="N2" s="15"/>
-    </row>
-    <row r="3" spans="1:14" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="3" spans="1:13" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="2">
         <v>2</v>
       </c>
@@ -3397,9 +3202,8 @@
       <c r="K3" s="2"/>
       <c r="L3" s="2"/>
       <c r="M3" s="2"/>
-      <c r="N3" s="15"/>
-    </row>
-    <row r="4" spans="1:14" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="4" spans="1:13" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="2">
         <v>3</v>
       </c>
@@ -3419,9 +3223,8 @@
       <c r="K4" s="2"/>
       <c r="L4" s="2"/>
       <c r="M4" s="2"/>
-      <c r="N4" s="15"/>
-    </row>
-    <row r="5" spans="1:14" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="5" spans="1:13" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="2">
         <v>4</v>
       </c>
@@ -3441,9 +3244,8 @@
       <c r="K5" s="2"/>
       <c r="L5" s="2"/>
       <c r="M5" s="2"/>
-      <c r="N5" s="15"/>
-    </row>
-    <row r="6" spans="1:14" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="6" spans="1:13" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="2">
         <v>5</v>
       </c>
@@ -3463,9 +3265,8 @@
       <c r="K6" s="2"/>
       <c r="L6" s="2"/>
       <c r="M6" s="2"/>
-      <c r="N6" s="15"/>
-    </row>
-    <row r="7" spans="1:14" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="7" spans="1:13" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="2">
         <v>6</v>
       </c>
@@ -3485,9 +3286,8 @@
       <c r="K7" s="2"/>
       <c r="L7" s="2"/>
       <c r="M7" s="2"/>
-      <c r="N7" s="15"/>
-    </row>
-    <row r="8" spans="1:14" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="8" spans="1:13" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="2">
         <v>7</v>
       </c>
@@ -3507,9 +3307,8 @@
       <c r="K8" s="2"/>
       <c r="L8" s="2"/>
       <c r="M8" s="2"/>
-      <c r="N8" s="15"/>
-    </row>
-    <row r="9" spans="1:14" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="9" spans="1:13" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A9" s="2">
         <v>8</v>
       </c>
@@ -3529,9 +3328,8 @@
       <c r="K9" s="2"/>
       <c r="L9" s="2"/>
       <c r="M9" s="2"/>
-      <c r="N9" s="15"/>
-    </row>
-    <row r="10" spans="1:14" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="10" spans="1:13" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A10" s="2">
         <v>9</v>
       </c>
@@ -3551,9 +3349,8 @@
       <c r="K10" s="2"/>
       <c r="L10" s="2"/>
       <c r="M10" s="2"/>
-      <c r="N10" s="15"/>
-    </row>
-    <row r="11" spans="1:14" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="11" spans="1:13" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A11" s="3">
         <v>10</v>
       </c>
@@ -3561,7 +3358,7 @@
       <c r="C11" s="3"/>
       <c r="D11" s="3"/>
       <c r="E11" s="3" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="F11" s="3"/>
       <c r="G11" s="3" t="s">
@@ -3573,9 +3370,8 @@
       <c r="K11" s="3"/>
       <c r="L11" s="3"/>
       <c r="M11" s="3"/>
-      <c r="N11" s="15"/>
-    </row>
-    <row r="12" spans="1:14" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="12" spans="1:13" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A12" s="3">
         <v>11</v>
       </c>
@@ -3595,9 +3391,8 @@
       <c r="K12" s="3"/>
       <c r="L12" s="3"/>
       <c r="M12" s="3"/>
-      <c r="N12" s="15"/>
-    </row>
-    <row r="13" spans="1:14" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="13" spans="1:13" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A13" s="3">
         <v>12</v>
       </c>
@@ -3617,9 +3412,8 @@
       <c r="K13" s="3"/>
       <c r="L13" s="3"/>
       <c r="M13" s="3"/>
-      <c r="N13" s="15"/>
-    </row>
-    <row r="14" spans="1:14" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="14" spans="1:13" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A14" s="3">
         <v>13</v>
       </c>
@@ -3627,7 +3421,7 @@
       <c r="C14" s="3"/>
       <c r="D14" s="3"/>
       <c r="E14" s="3" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="F14" s="3"/>
       <c r="G14" s="3" t="s">
@@ -3639,9 +3433,8 @@
       <c r="K14" s="3"/>
       <c r="L14" s="3"/>
       <c r="M14" s="3"/>
-      <c r="N14" s="15"/>
-    </row>
-    <row r="15" spans="1:14" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="15" spans="1:13" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A15" s="3">
         <v>14</v>
       </c>
@@ -3649,7 +3442,7 @@
       <c r="C15" s="3"/>
       <c r="D15" s="3"/>
       <c r="E15" s="3" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="F15" s="3"/>
       <c r="G15" s="3" t="s">
@@ -3661,9 +3454,8 @@
       <c r="K15" s="3"/>
       <c r="L15" s="3"/>
       <c r="M15" s="3"/>
-      <c r="N15" s="15"/>
-    </row>
-    <row r="16" spans="1:14" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="16" spans="1:13" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A16" s="3">
         <v>15</v>
       </c>
@@ -3683,19 +3475,18 @@
       <c r="K16" s="3"/>
       <c r="L16" s="3"/>
       <c r="M16" s="3"/>
-      <c r="N16" s="15"/>
-    </row>
-    <row r="17" spans="1:20" x14ac:dyDescent="0.25">
+    </row>
+    <row r="17" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A17" s="4">
         <v>16</v>
       </c>
-      <c r="B17" s="16" t="s">
+      <c r="B17" s="18" t="s">
         <v>565</v>
       </c>
-      <c r="C17" s="21"/>
-      <c r="D17" s="21"/>
+      <c r="C17" s="10"/>
+      <c r="D17" s="10"/>
       <c r="E17" s="4" t="s">
-        <v>575</v>
+        <v>574</v>
       </c>
       <c r="F17" s="4" t="s">
         <v>18</v>
@@ -3710,27 +3501,21 @@
         <v>461</v>
       </c>
       <c r="J17" s="4" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="K17" s="4"/>
       <c r="L17" s="4"/>
       <c r="M17" s="4"/>
-      <c r="N17" s="15" t="s">
-        <v>576</v>
-      </c>
-      <c r="P17" s="1"/>
-      <c r="Q17" s="1"/>
-      <c r="R17" s="1"/>
-    </row>
-    <row r="18" spans="1:20" x14ac:dyDescent="0.25">
+    </row>
+    <row r="18" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A18" s="4">
         <v>17</v>
       </c>
-      <c r="B18" s="16"/>
-      <c r="C18" s="21"/>
-      <c r="D18" s="21"/>
+      <c r="B18" s="18"/>
+      <c r="C18" s="10"/>
+      <c r="D18" s="10"/>
       <c r="E18" s="4" t="s">
-        <v>577</v>
+        <v>575</v>
       </c>
       <c r="F18" s="4" t="s">
         <v>19</v>
@@ -3748,22 +3533,16 @@
       <c r="K18" s="4"/>
       <c r="L18" s="4"/>
       <c r="M18" s="4"/>
-      <c r="N18" s="15" t="s">
-        <v>578</v>
-      </c>
-      <c r="P18" s="1"/>
-      <c r="Q18" s="1"/>
-      <c r="R18" s="1"/>
-    </row>
-    <row r="19" spans="1:20" x14ac:dyDescent="0.25">
+    </row>
+    <row r="19" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A19" s="4">
         <v>18</v>
       </c>
-      <c r="B19" s="16"/>
-      <c r="C19" s="21"/>
-      <c r="D19" s="21"/>
+      <c r="B19" s="18"/>
+      <c r="C19" s="10"/>
+      <c r="D19" s="10"/>
       <c r="E19" s="4" t="s">
-        <v>579</v>
+        <v>576</v>
       </c>
       <c r="F19" s="4" t="s">
         <v>20</v>
@@ -3781,22 +3560,16 @@
       <c r="K19" s="4"/>
       <c r="L19" s="4"/>
       <c r="M19" s="4"/>
-      <c r="N19" s="15" t="s">
-        <v>580</v>
-      </c>
-      <c r="P19" s="1"/>
-      <c r="Q19" s="1"/>
-      <c r="R19" s="1"/>
-    </row>
-    <row r="20" spans="1:20" x14ac:dyDescent="0.25">
+    </row>
+    <row r="20" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A20" s="4">
         <v>19</v>
       </c>
-      <c r="B20" s="16"/>
-      <c r="C20" s="21"/>
-      <c r="D20" s="21"/>
+      <c r="B20" s="18"/>
+      <c r="C20" s="10"/>
+      <c r="D20" s="10"/>
       <c r="E20" s="4" t="s">
-        <v>581</v>
+        <v>577</v>
       </c>
       <c r="F20" s="4" t="s">
         <v>21</v>
@@ -3814,22 +3587,16 @@
       <c r="K20" s="4"/>
       <c r="L20" s="4"/>
       <c r="M20" s="4"/>
-      <c r="N20" s="15" t="s">
-        <v>582</v>
-      </c>
-      <c r="P20" s="1"/>
-      <c r="Q20" s="1"/>
-      <c r="R20" s="1"/>
-    </row>
-    <row r="21" spans="1:20" x14ac:dyDescent="0.25">
+    </row>
+    <row r="21" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A21" s="4">
         <v>20</v>
       </c>
-      <c r="B21" s="16"/>
-      <c r="C21" s="21"/>
-      <c r="D21" s="21"/>
+      <c r="B21" s="18"/>
+      <c r="C21" s="10"/>
+      <c r="D21" s="10"/>
       <c r="E21" s="4" t="s">
-        <v>583</v>
+        <v>578</v>
       </c>
       <c r="F21" s="4" t="s">
         <v>22</v>
@@ -3847,22 +3614,16 @@
       <c r="K21" s="4"/>
       <c r="L21" s="4"/>
       <c r="M21" s="4"/>
-      <c r="N21" s="15" t="s">
-        <v>584</v>
-      </c>
-      <c r="P21" s="1"/>
-      <c r="Q21" s="1"/>
-      <c r="R21" s="1"/>
-    </row>
-    <row r="22" spans="1:20" x14ac:dyDescent="0.25">
+    </row>
+    <row r="22" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A22" s="4">
         <v>21</v>
       </c>
-      <c r="B22" s="16"/>
-      <c r="C22" s="21"/>
-      <c r="D22" s="21"/>
+      <c r="B22" s="18"/>
+      <c r="C22" s="10"/>
+      <c r="D22" s="10"/>
       <c r="E22" s="4" t="s">
-        <v>585</v>
+        <v>579</v>
       </c>
       <c r="F22" s="4" t="s">
         <v>23</v>
@@ -3880,22 +3641,16 @@
       <c r="K22" s="4"/>
       <c r="L22" s="4"/>
       <c r="M22" s="4"/>
-      <c r="N22" s="15" t="s">
-        <v>586</v>
-      </c>
-      <c r="P22" s="1"/>
-      <c r="Q22" s="1"/>
-      <c r="R22" s="1"/>
-    </row>
-    <row r="23" spans="1:20" x14ac:dyDescent="0.25">
+    </row>
+    <row r="23" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A23" s="4">
         <v>22</v>
       </c>
-      <c r="B23" s="16"/>
-      <c r="C23" s="21"/>
-      <c r="D23" s="21"/>
+      <c r="B23" s="18"/>
+      <c r="C23" s="10"/>
+      <c r="D23" s="10"/>
       <c r="E23" s="4" t="s">
-        <v>587</v>
+        <v>580</v>
       </c>
       <c r="F23" s="4" t="s">
         <v>24</v>
@@ -3913,22 +3668,16 @@
       <c r="K23" s="4"/>
       <c r="L23" s="4"/>
       <c r="M23" s="4"/>
-      <c r="N23" s="15" t="s">
-        <v>588</v>
-      </c>
-      <c r="P23" s="1"/>
-      <c r="Q23" s="1"/>
-      <c r="R23" s="1"/>
-    </row>
-    <row r="24" spans="1:20" x14ac:dyDescent="0.25">
+    </row>
+    <row r="24" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A24" s="4">
         <v>23</v>
       </c>
-      <c r="B24" s="16"/>
-      <c r="C24" s="21"/>
-      <c r="D24" s="21"/>
+      <c r="B24" s="18"/>
+      <c r="C24" s="10"/>
+      <c r="D24" s="10"/>
       <c r="E24" s="4" t="s">
-        <v>589</v>
+        <v>581</v>
       </c>
       <c r="F24" s="4" t="s">
         <v>25</v>
@@ -3946,38 +3695,22 @@
       <c r="K24" s="4"/>
       <c r="L24" s="4"/>
       <c r="M24" s="4"/>
-      <c r="N24" s="15" t="s">
-        <v>590</v>
-      </c>
-      <c r="P24" s="1"/>
-      <c r="Q24" s="1" t="s">
-        <v>607</v>
-      </c>
-      <c r="R24" s="1" t="s">
-        <v>608</v>
-      </c>
-      <c r="S24" s="1" t="s">
-        <v>264</v>
-      </c>
-      <c r="T24" s="1" t="s">
-        <v>460</v>
-      </c>
-    </row>
-    <row r="25" spans="1:20" x14ac:dyDescent="0.25">
+    </row>
+    <row r="25" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A25" s="5">
         <v>24</v>
       </c>
-      <c r="B25" s="17" t="s">
+      <c r="B25" s="19" t="s">
         <v>566</v>
       </c>
-      <c r="C25" s="9" t="s">
-        <v>593</v>
-      </c>
-      <c r="D25" s="25" t="s">
-        <v>886</v>
+      <c r="C25" s="21" t="s">
+        <v>584</v>
+      </c>
+      <c r="D25" s="14" t="s">
+        <v>824</v>
       </c>
       <c r="E25" s="5" t="s">
-        <v>595</v>
+        <v>586</v>
       </c>
       <c r="F25" s="5" t="s">
         <v>26</v>
@@ -3995,31 +3728,16 @@
       <c r="K25" s="5"/>
       <c r="L25" s="5"/>
       <c r="M25" s="5"/>
-      <c r="N25" s="15" t="s">
-        <v>596</v>
-      </c>
-      <c r="Q25" s="1" t="s">
-        <v>595</v>
-      </c>
-      <c r="R25" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="S25" s="1" t="s">
-        <v>271</v>
-      </c>
-      <c r="T25" s="1" t="s">
-        <v>462</v>
-      </c>
-    </row>
-    <row r="26" spans="1:20" x14ac:dyDescent="0.25">
+    </row>
+    <row r="26" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A26" s="5">
         <v>25</v>
       </c>
-      <c r="B26" s="17"/>
-      <c r="C26" s="10"/>
-      <c r="D26" s="26"/>
+      <c r="B26" s="19"/>
+      <c r="C26" s="22"/>
+      <c r="D26" s="15"/>
       <c r="E26" s="5" t="s">
-        <v>597</v>
+        <v>587</v>
       </c>
       <c r="F26" s="5" t="s">
         <v>27</v>
@@ -4037,32 +3755,16 @@
       <c r="K26" s="5"/>
       <c r="L26" s="5"/>
       <c r="M26" s="5"/>
-      <c r="N26" s="15" t="s">
-        <v>598</v>
-      </c>
-      <c r="P26" s="1"/>
-      <c r="Q26" s="1" t="s">
-        <v>597</v>
-      </c>
-      <c r="R26" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="S26" s="1" t="s">
-        <v>272</v>
-      </c>
-      <c r="T26" s="1" t="s">
-        <v>462</v>
-      </c>
-    </row>
-    <row r="27" spans="1:20" x14ac:dyDescent="0.25">
+    </row>
+    <row r="27" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A27" s="5">
         <v>26</v>
       </c>
-      <c r="B27" s="17"/>
-      <c r="C27" s="10"/>
-      <c r="D27" s="26"/>
+      <c r="B27" s="19"/>
+      <c r="C27" s="22"/>
+      <c r="D27" s="15"/>
       <c r="E27" s="5" t="s">
-        <v>599</v>
+        <v>588</v>
       </c>
       <c r="F27" s="5" t="s">
         <v>28</v>
@@ -4080,32 +3782,16 @@
       <c r="K27" s="5"/>
       <c r="L27" s="5"/>
       <c r="M27" s="5"/>
-      <c r="N27" s="15" t="s">
-        <v>600</v>
-      </c>
-      <c r="P27" s="1"/>
-      <c r="Q27" s="1" t="s">
-        <v>599</v>
-      </c>
-      <c r="R27" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="S27" s="1" t="s">
-        <v>273</v>
-      </c>
-      <c r="T27" s="1" t="s">
-        <v>462</v>
-      </c>
-    </row>
-    <row r="28" spans="1:20" x14ac:dyDescent="0.25">
+    </row>
+    <row r="28" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A28" s="5">
         <v>27</v>
       </c>
-      <c r="B28" s="17"/>
-      <c r="C28" s="10"/>
-      <c r="D28" s="26"/>
+      <c r="B28" s="19"/>
+      <c r="C28" s="22"/>
+      <c r="D28" s="15"/>
       <c r="E28" s="5" t="s">
-        <v>601</v>
+        <v>589</v>
       </c>
       <c r="F28" s="5" t="s">
         <v>29</v>
@@ -4123,32 +3809,16 @@
       <c r="K28" s="5"/>
       <c r="L28" s="5"/>
       <c r="M28" s="5"/>
-      <c r="N28" s="15" t="s">
-        <v>602</v>
-      </c>
-      <c r="P28" s="1"/>
-      <c r="Q28" s="1" t="s">
-        <v>601</v>
-      </c>
-      <c r="R28" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="S28" s="1" t="s">
-        <v>274</v>
-      </c>
-      <c r="T28" s="1" t="s">
-        <v>462</v>
-      </c>
-    </row>
-    <row r="29" spans="1:20" x14ac:dyDescent="0.25">
+    </row>
+    <row r="29" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A29" s="5">
         <v>28</v>
       </c>
-      <c r="B29" s="17"/>
-      <c r="C29" s="10"/>
-      <c r="D29" s="26"/>
+      <c r="B29" s="19"/>
+      <c r="C29" s="22"/>
+      <c r="D29" s="15"/>
       <c r="E29" s="5" t="s">
-        <v>603</v>
+        <v>590</v>
       </c>
       <c r="F29" s="5" t="s">
         <v>30</v>
@@ -4166,32 +3836,16 @@
       <c r="K29" s="5"/>
       <c r="L29" s="5"/>
       <c r="M29" s="5"/>
-      <c r="N29" s="15" t="s">
-        <v>604</v>
-      </c>
-      <c r="P29" s="1"/>
-      <c r="Q29" s="1" t="s">
-        <v>603</v>
-      </c>
-      <c r="R29" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="S29" s="1" t="s">
-        <v>275</v>
-      </c>
-      <c r="T29" s="1" t="s">
-        <v>462</v>
-      </c>
-    </row>
-    <row r="30" spans="1:20" x14ac:dyDescent="0.25">
+    </row>
+    <row r="30" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A30" s="5">
         <v>29</v>
       </c>
-      <c r="B30" s="17"/>
-      <c r="C30" s="10"/>
-      <c r="D30" s="27"/>
+      <c r="B30" s="19"/>
+      <c r="C30" s="22"/>
+      <c r="D30" s="16"/>
       <c r="E30" s="5" t="s">
-        <v>605</v>
+        <v>591</v>
       </c>
       <c r="F30" s="5" t="s">
         <v>31</v>
@@ -4209,34 +3863,18 @@
       <c r="K30" s="5"/>
       <c r="L30" s="5"/>
       <c r="M30" s="5"/>
-      <c r="N30" s="15" t="s">
-        <v>606</v>
-      </c>
-      <c r="P30" s="1"/>
-      <c r="Q30" s="1" t="s">
-        <v>605</v>
-      </c>
-      <c r="R30" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="S30" s="1" t="s">
-        <v>276</v>
-      </c>
-      <c r="T30" s="1" t="s">
-        <v>462</v>
-      </c>
-    </row>
-    <row r="31" spans="1:20" x14ac:dyDescent="0.25">
+    </row>
+    <row r="31" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A31" s="6">
         <v>30</v>
       </c>
-      <c r="B31" s="17"/>
-      <c r="C31" s="10"/>
-      <c r="D31" s="22" t="s">
-        <v>887</v>
+      <c r="B31" s="19"/>
+      <c r="C31" s="22"/>
+      <c r="D31" s="11" t="s">
+        <v>825</v>
       </c>
       <c r="E31" s="6" t="s">
-        <v>609</v>
+        <v>592</v>
       </c>
       <c r="F31" s="6" t="s">
         <v>32</v>
@@ -4254,30 +3892,16 @@
       <c r="K31" s="6"/>
       <c r="L31" s="6"/>
       <c r="M31" s="6"/>
-      <c r="N31" s="15"/>
-      <c r="P31" s="1"/>
-      <c r="Q31" s="1" t="s">
-        <v>609</v>
-      </c>
-      <c r="R31" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="S31" s="1" t="s">
-        <v>277</v>
-      </c>
-      <c r="T31" s="1" t="s">
-        <v>462</v>
-      </c>
-    </row>
-    <row r="32" spans="1:20" x14ac:dyDescent="0.25">
+    </row>
+    <row r="32" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A32" s="6">
         <v>31</v>
       </c>
-      <c r="B32" s="17"/>
-      <c r="C32" s="10"/>
-      <c r="D32" s="22"/>
+      <c r="B32" s="19"/>
+      <c r="C32" s="22"/>
+      <c r="D32" s="11"/>
       <c r="E32" s="6" t="s">
-        <v>610</v>
+        <v>593</v>
       </c>
       <c r="F32" s="6" t="s">
         <v>33</v>
@@ -4295,30 +3919,16 @@
       <c r="K32" s="6"/>
       <c r="L32" s="6"/>
       <c r="M32" s="6"/>
-      <c r="N32" s="15"/>
-      <c r="P32" s="1"/>
-      <c r="Q32" s="1" t="s">
-        <v>610</v>
-      </c>
-      <c r="R32" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="S32" s="1" t="s">
-        <v>278</v>
-      </c>
-      <c r="T32" s="1" t="s">
-        <v>462</v>
-      </c>
-    </row>
-    <row r="33" spans="1:20" x14ac:dyDescent="0.25">
+    </row>
+    <row r="33" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A33" s="6">
         <v>32</v>
       </c>
-      <c r="B33" s="17"/>
-      <c r="C33" s="10"/>
-      <c r="D33" s="22"/>
+      <c r="B33" s="19"/>
+      <c r="C33" s="22"/>
+      <c r="D33" s="11"/>
       <c r="E33" s="6" t="s">
-        <v>611</v>
+        <v>594</v>
       </c>
       <c r="F33" s="6" t="s">
         <v>34</v>
@@ -4336,29 +3946,16 @@
       <c r="K33" s="6"/>
       <c r="L33" s="6"/>
       <c r="M33" s="6"/>
-      <c r="N33" s="15"/>
-      <c r="Q33" s="1" t="s">
-        <v>611</v>
-      </c>
-      <c r="R33" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="S33" s="1" t="s">
-        <v>279</v>
-      </c>
-      <c r="T33" s="1" t="s">
-        <v>462</v>
-      </c>
-    </row>
-    <row r="34" spans="1:20" x14ac:dyDescent="0.25">
+    </row>
+    <row r="34" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A34" s="6">
         <v>33</v>
       </c>
-      <c r="B34" s="17"/>
-      <c r="C34" s="10"/>
-      <c r="D34" s="22"/>
+      <c r="B34" s="19"/>
+      <c r="C34" s="22"/>
+      <c r="D34" s="11"/>
       <c r="E34" s="6" t="s">
-        <v>612</v>
+        <v>595</v>
       </c>
       <c r="F34" s="6" t="s">
         <v>35</v>
@@ -4376,29 +3973,16 @@
       <c r="K34" s="6"/>
       <c r="L34" s="6"/>
       <c r="M34" s="6"/>
-      <c r="N34" s="15"/>
-      <c r="Q34" s="1" t="s">
-        <v>612</v>
-      </c>
-      <c r="R34" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="S34" s="1" t="s">
-        <v>280</v>
-      </c>
-      <c r="T34" s="1" t="s">
-        <v>462</v>
-      </c>
-    </row>
-    <row r="35" spans="1:20" x14ac:dyDescent="0.25">
+    </row>
+    <row r="35" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A35" s="6">
         <v>34</v>
       </c>
-      <c r="B35" s="17"/>
-      <c r="C35" s="10"/>
-      <c r="D35" s="22"/>
+      <c r="B35" s="19"/>
+      <c r="C35" s="22"/>
+      <c r="D35" s="11"/>
       <c r="E35" s="6" t="s">
-        <v>613</v>
+        <v>596</v>
       </c>
       <c r="F35" s="6" t="s">
         <v>36</v>
@@ -4416,29 +4000,16 @@
       <c r="K35" s="6"/>
       <c r="L35" s="6"/>
       <c r="M35" s="6"/>
-      <c r="N35" s="15"/>
-      <c r="Q35" s="1" t="s">
-        <v>613</v>
-      </c>
-      <c r="R35" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="S35" s="1" t="s">
-        <v>281</v>
-      </c>
-      <c r="T35" s="1" t="s">
-        <v>462</v>
-      </c>
-    </row>
-    <row r="36" spans="1:20" x14ac:dyDescent="0.25">
+    </row>
+    <row r="36" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A36" s="6">
         <v>35</v>
       </c>
-      <c r="B36" s="17"/>
-      <c r="C36" s="10"/>
-      <c r="D36" s="22"/>
+      <c r="B36" s="19"/>
+      <c r="C36" s="22"/>
+      <c r="D36" s="11"/>
       <c r="E36" s="6" t="s">
-        <v>614</v>
+        <v>597</v>
       </c>
       <c r="F36" s="6" t="s">
         <v>37</v>
@@ -4456,31 +4027,18 @@
       <c r="K36" s="6"/>
       <c r="L36" s="6"/>
       <c r="M36" s="6"/>
-      <c r="N36" s="15"/>
-      <c r="Q36" s="1" t="s">
-        <v>614</v>
-      </c>
-      <c r="R36" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="S36" s="1" t="s">
-        <v>282</v>
-      </c>
-      <c r="T36" s="1" t="s">
-        <v>462</v>
-      </c>
-    </row>
-    <row r="37" spans="1:20" ht="28.5" x14ac:dyDescent="0.25">
+    </row>
+    <row r="37" spans="1:13" ht="28.5" x14ac:dyDescent="0.25">
       <c r="A37" s="5">
         <v>36</v>
       </c>
-      <c r="B37" s="17"/>
-      <c r="C37" s="10"/>
-      <c r="D37" s="22" t="s">
-        <v>888</v>
+      <c r="B37" s="19"/>
+      <c r="C37" s="22"/>
+      <c r="D37" s="11" t="s">
+        <v>826</v>
       </c>
       <c r="E37" s="5" t="s">
-        <v>615</v>
+        <v>598</v>
       </c>
       <c r="F37" s="5" t="s">
         <v>38</v>
@@ -4498,29 +4056,16 @@
       <c r="K37" s="5"/>
       <c r="L37" s="5"/>
       <c r="M37" s="5"/>
-      <c r="N37" s="15"/>
-      <c r="Q37" s="1" t="s">
-        <v>615</v>
-      </c>
-      <c r="R37" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="S37" s="1" t="s">
-        <v>283</v>
-      </c>
-      <c r="T37" s="1" t="s">
-        <v>462</v>
-      </c>
-    </row>
-    <row r="38" spans="1:20" x14ac:dyDescent="0.25">
+    </row>
+    <row r="38" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A38" s="5">
         <v>37</v>
       </c>
-      <c r="B38" s="17"/>
-      <c r="C38" s="10"/>
-      <c r="D38" s="22"/>
+      <c r="B38" s="19"/>
+      <c r="C38" s="22"/>
+      <c r="D38" s="11"/>
       <c r="E38" s="5" t="s">
-        <v>616</v>
+        <v>599</v>
       </c>
       <c r="F38" s="5" t="s">
         <v>39</v>
@@ -4538,29 +4083,16 @@
       <c r="K38" s="5"/>
       <c r="L38" s="5"/>
       <c r="M38" s="5"/>
-      <c r="N38" s="15"/>
-      <c r="Q38" s="1" t="s">
-        <v>616</v>
-      </c>
-      <c r="R38" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="S38" s="1" t="s">
-        <v>284</v>
-      </c>
-      <c r="T38" s="1" t="s">
-        <v>462</v>
-      </c>
-    </row>
-    <row r="39" spans="1:20" x14ac:dyDescent="0.25">
+    </row>
+    <row r="39" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A39" s="5">
         <v>38</v>
       </c>
-      <c r="B39" s="17"/>
-      <c r="C39" s="10"/>
-      <c r="D39" s="22"/>
+      <c r="B39" s="19"/>
+      <c r="C39" s="22"/>
+      <c r="D39" s="11"/>
       <c r="E39" s="5" t="s">
-        <v>617</v>
+        <v>600</v>
       </c>
       <c r="F39" s="5" t="s">
         <v>40</v>
@@ -4578,29 +4110,16 @@
       <c r="K39" s="5"/>
       <c r="L39" s="5"/>
       <c r="M39" s="5"/>
-      <c r="N39" s="15"/>
-      <c r="Q39" s="1" t="s">
-        <v>617</v>
-      </c>
-      <c r="R39" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="S39" s="1" t="s">
-        <v>285</v>
-      </c>
-      <c r="T39" s="1" t="s">
-        <v>462</v>
-      </c>
-    </row>
-    <row r="40" spans="1:20" x14ac:dyDescent="0.25">
+    </row>
+    <row r="40" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A40" s="5">
         <v>39</v>
       </c>
-      <c r="B40" s="17"/>
-      <c r="C40" s="10"/>
-      <c r="D40" s="22"/>
+      <c r="B40" s="19"/>
+      <c r="C40" s="22"/>
+      <c r="D40" s="11"/>
       <c r="E40" s="5" t="s">
-        <v>618</v>
+        <v>601</v>
       </c>
       <c r="F40" s="5" t="s">
         <v>41</v>
@@ -4618,29 +4137,16 @@
       <c r="K40" s="5"/>
       <c r="L40" s="5"/>
       <c r="M40" s="5"/>
-      <c r="N40" s="15"/>
-      <c r="Q40" s="1" t="s">
-        <v>618</v>
-      </c>
-      <c r="R40" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="S40" s="1" t="s">
-        <v>286</v>
-      </c>
-      <c r="T40" s="1" t="s">
-        <v>462</v>
-      </c>
-    </row>
-    <row r="41" spans="1:20" x14ac:dyDescent="0.25">
+    </row>
+    <row r="41" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A41" s="5">
         <v>40</v>
       </c>
-      <c r="B41" s="17"/>
-      <c r="C41" s="10"/>
-      <c r="D41" s="22"/>
+      <c r="B41" s="19"/>
+      <c r="C41" s="22"/>
+      <c r="D41" s="11"/>
       <c r="E41" s="5" t="s">
-        <v>619</v>
+        <v>602</v>
       </c>
       <c r="F41" s="5" t="s">
         <v>42</v>
@@ -4658,29 +4164,16 @@
       <c r="K41" s="5"/>
       <c r="L41" s="5"/>
       <c r="M41" s="5"/>
-      <c r="N41" s="15"/>
-      <c r="Q41" s="1" t="s">
-        <v>619</v>
-      </c>
-      <c r="R41" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="S41" s="1" t="s">
-        <v>287</v>
-      </c>
-      <c r="T41" s="1" t="s">
-        <v>462</v>
-      </c>
-    </row>
-    <row r="42" spans="1:20" x14ac:dyDescent="0.25">
+    </row>
+    <row r="42" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A42" s="5">
         <v>41</v>
       </c>
-      <c r="B42" s="17"/>
-      <c r="C42" s="10"/>
-      <c r="D42" s="22"/>
+      <c r="B42" s="19"/>
+      <c r="C42" s="22"/>
+      <c r="D42" s="11"/>
       <c r="E42" s="5" t="s">
-        <v>620</v>
+        <v>603</v>
       </c>
       <c r="F42" s="5" t="s">
         <v>43</v>
@@ -4698,29 +4191,16 @@
       <c r="K42" s="5"/>
       <c r="L42" s="5"/>
       <c r="M42" s="5"/>
-      <c r="N42" s="15"/>
-      <c r="Q42" s="1" t="s">
-        <v>620</v>
-      </c>
-      <c r="R42" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="S42" s="1" t="s">
-        <v>288</v>
-      </c>
-      <c r="T42" s="1" t="s">
-        <v>462</v>
-      </c>
-    </row>
-    <row r="43" spans="1:20" x14ac:dyDescent="0.25">
+    </row>
+    <row r="43" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A43" s="5">
         <v>42</v>
       </c>
-      <c r="B43" s="17"/>
-      <c r="C43" s="10"/>
-      <c r="D43" s="22"/>
+      <c r="B43" s="19"/>
+      <c r="C43" s="22"/>
+      <c r="D43" s="11"/>
       <c r="E43" s="5" t="s">
-        <v>621</v>
+        <v>604</v>
       </c>
       <c r="F43" s="5" t="s">
         <v>44</v>
@@ -4738,29 +4218,16 @@
       <c r="K43" s="5"/>
       <c r="L43" s="5"/>
       <c r="M43" s="5"/>
-      <c r="N43" s="15"/>
-      <c r="Q43" s="1" t="s">
-        <v>621</v>
-      </c>
-      <c r="R43" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="S43" s="1" t="s">
-        <v>289</v>
-      </c>
-      <c r="T43" s="1" t="s">
-        <v>462</v>
-      </c>
-    </row>
-    <row r="44" spans="1:20" x14ac:dyDescent="0.25">
+    </row>
+    <row r="44" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A44" s="5">
         <v>43</v>
       </c>
-      <c r="B44" s="17"/>
-      <c r="C44" s="10"/>
-      <c r="D44" s="22"/>
+      <c r="B44" s="19"/>
+      <c r="C44" s="22"/>
+      <c r="D44" s="11"/>
       <c r="E44" s="5" t="s">
-        <v>622</v>
+        <v>605</v>
       </c>
       <c r="F44" s="5" t="s">
         <v>45</v>
@@ -4778,31 +4245,18 @@
       <c r="K44" s="5"/>
       <c r="L44" s="5"/>
       <c r="M44" s="5"/>
-      <c r="N44" s="15"/>
-      <c r="Q44" s="1" t="s">
-        <v>622</v>
-      </c>
-      <c r="R44" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="S44" s="1" t="s">
-        <v>290</v>
-      </c>
-      <c r="T44" s="1" t="s">
-        <v>462</v>
-      </c>
-    </row>
-    <row r="45" spans="1:20" x14ac:dyDescent="0.25">
+    </row>
+    <row r="45" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A45" s="6">
         <v>44</v>
       </c>
-      <c r="B45" s="17"/>
-      <c r="C45" s="10"/>
-      <c r="D45" s="22" t="s">
-        <v>889</v>
+      <c r="B45" s="19"/>
+      <c r="C45" s="22"/>
+      <c r="D45" s="11" t="s">
+        <v>827</v>
       </c>
       <c r="E45" s="6" t="s">
-        <v>623</v>
+        <v>606</v>
       </c>
       <c r="F45" s="6" t="s">
         <v>46</v>
@@ -4820,29 +4274,16 @@
       <c r="K45" s="6"/>
       <c r="L45" s="6"/>
       <c r="M45" s="6"/>
-      <c r="N45" s="15"/>
-      <c r="Q45" s="1" t="s">
-        <v>623</v>
-      </c>
-      <c r="R45" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="S45" s="1" t="s">
-        <v>291</v>
-      </c>
-      <c r="T45" s="1" t="s">
-        <v>462</v>
-      </c>
-    </row>
-    <row r="46" spans="1:20" x14ac:dyDescent="0.25">
+    </row>
+    <row r="46" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A46" s="6">
         <v>45</v>
       </c>
-      <c r="B46" s="17"/>
-      <c r="C46" s="10"/>
-      <c r="D46" s="22"/>
+      <c r="B46" s="19"/>
+      <c r="C46" s="22"/>
+      <c r="D46" s="11"/>
       <c r="E46" s="6" t="s">
-        <v>624</v>
+        <v>607</v>
       </c>
       <c r="F46" s="6" t="s">
         <v>47</v>
@@ -4860,29 +4301,16 @@
       <c r="K46" s="6"/>
       <c r="L46" s="6"/>
       <c r="M46" s="6"/>
-      <c r="N46" s="15"/>
-      <c r="Q46" s="1" t="s">
-        <v>624</v>
-      </c>
-      <c r="R46" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="S46" s="1" t="s">
-        <v>292</v>
-      </c>
-      <c r="T46" s="1" t="s">
-        <v>462</v>
-      </c>
-    </row>
-    <row r="47" spans="1:20" x14ac:dyDescent="0.25">
+    </row>
+    <row r="47" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A47" s="6">
         <v>46</v>
       </c>
-      <c r="B47" s="17"/>
-      <c r="C47" s="10"/>
-      <c r="D47" s="22"/>
+      <c r="B47" s="19"/>
+      <c r="C47" s="22"/>
+      <c r="D47" s="11"/>
       <c r="E47" s="6" t="s">
-        <v>625</v>
+        <v>608</v>
       </c>
       <c r="F47" s="6" t="s">
         <v>48</v>
@@ -4900,29 +4328,16 @@
       <c r="K47" s="6"/>
       <c r="L47" s="6"/>
       <c r="M47" s="6"/>
-      <c r="N47" s="15"/>
-      <c r="Q47" s="1" t="s">
-        <v>625</v>
-      </c>
-      <c r="R47" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="S47" s="1" t="s">
-        <v>293</v>
-      </c>
-      <c r="T47" s="1" t="s">
-        <v>462</v>
-      </c>
-    </row>
-    <row r="48" spans="1:20" x14ac:dyDescent="0.25">
+    </row>
+    <row r="48" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A48" s="6">
         <v>47</v>
       </c>
-      <c r="B48" s="17"/>
-      <c r="C48" s="10"/>
-      <c r="D48" s="22"/>
+      <c r="B48" s="19"/>
+      <c r="C48" s="22"/>
+      <c r="D48" s="11"/>
       <c r="E48" s="6" t="s">
-        <v>626</v>
+        <v>609</v>
       </c>
       <c r="F48" s="6" t="s">
         <v>49</v>
@@ -4940,29 +4355,16 @@
       <c r="K48" s="6"/>
       <c r="L48" s="6"/>
       <c r="M48" s="6"/>
-      <c r="N48" s="15"/>
-      <c r="Q48" s="1" t="s">
-        <v>626</v>
-      </c>
-      <c r="R48" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="S48" s="1" t="s">
-        <v>294</v>
-      </c>
-      <c r="T48" s="1" t="s">
-        <v>462</v>
-      </c>
-    </row>
-    <row r="49" spans="1:20" x14ac:dyDescent="0.25">
+    </row>
+    <row r="49" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A49" s="6">
         <v>48</v>
       </c>
-      <c r="B49" s="17"/>
-      <c r="C49" s="10"/>
-      <c r="D49" s="22"/>
+      <c r="B49" s="19"/>
+      <c r="C49" s="22"/>
+      <c r="D49" s="11"/>
       <c r="E49" s="6" t="s">
-        <v>627</v>
+        <v>610</v>
       </c>
       <c r="F49" s="6" t="s">
         <v>50</v>
@@ -4980,29 +4382,16 @@
       <c r="K49" s="6"/>
       <c r="L49" s="6"/>
       <c r="M49" s="6"/>
-      <c r="N49" s="15"/>
-      <c r="Q49" s="1" t="s">
-        <v>627</v>
-      </c>
-      <c r="R49" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="S49" s="1" t="s">
-        <v>295</v>
-      </c>
-      <c r="T49" s="1" t="s">
-        <v>462</v>
-      </c>
-    </row>
-    <row r="50" spans="1:20" x14ac:dyDescent="0.25">
+    </row>
+    <row r="50" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A50" s="6">
         <v>49</v>
       </c>
-      <c r="B50" s="17"/>
-      <c r="C50" s="10"/>
-      <c r="D50" s="22"/>
+      <c r="B50" s="19"/>
+      <c r="C50" s="22"/>
+      <c r="D50" s="11"/>
       <c r="E50" s="6" t="s">
-        <v>628</v>
+        <v>611</v>
       </c>
       <c r="F50" s="6" t="s">
         <v>51</v>
@@ -5020,29 +4409,16 @@
       <c r="K50" s="6"/>
       <c r="L50" s="6"/>
       <c r="M50" s="6"/>
-      <c r="N50" s="15"/>
-      <c r="Q50" s="1" t="s">
-        <v>628</v>
-      </c>
-      <c r="R50" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="S50" s="1" t="s">
-        <v>296</v>
-      </c>
-      <c r="T50" s="1" t="s">
-        <v>462</v>
-      </c>
-    </row>
-    <row r="51" spans="1:20" x14ac:dyDescent="0.25">
+    </row>
+    <row r="51" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A51" s="6">
         <v>50</v>
       </c>
-      <c r="B51" s="17"/>
-      <c r="C51" s="10"/>
-      <c r="D51" s="22"/>
+      <c r="B51" s="19"/>
+      <c r="C51" s="22"/>
+      <c r="D51" s="11"/>
       <c r="E51" s="6" t="s">
-        <v>629</v>
+        <v>612</v>
       </c>
       <c r="F51" s="6" t="s">
         <v>52</v>
@@ -5060,29 +4436,16 @@
       <c r="K51" s="6"/>
       <c r="L51" s="6"/>
       <c r="M51" s="6"/>
-      <c r="N51" s="15"/>
-      <c r="Q51" s="1" t="s">
-        <v>629</v>
-      </c>
-      <c r="R51" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="S51" s="1" t="s">
-        <v>297</v>
-      </c>
-      <c r="T51" s="1" t="s">
-        <v>462</v>
-      </c>
-    </row>
-    <row r="52" spans="1:20" x14ac:dyDescent="0.25">
+    </row>
+    <row r="52" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A52" s="6">
         <v>51</v>
       </c>
-      <c r="B52" s="17"/>
-      <c r="C52" s="10"/>
-      <c r="D52" s="22"/>
+      <c r="B52" s="19"/>
+      <c r="C52" s="22"/>
+      <c r="D52" s="11"/>
       <c r="E52" s="6" t="s">
-        <v>630</v>
+        <v>613</v>
       </c>
       <c r="F52" s="6" t="s">
         <v>53</v>
@@ -5100,31 +4463,18 @@
       <c r="K52" s="6"/>
       <c r="L52" s="6"/>
       <c r="M52" s="6"/>
-      <c r="N52" s="15"/>
-      <c r="Q52" s="1" t="s">
-        <v>630</v>
-      </c>
-      <c r="R52" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="S52" s="1" t="s">
-        <v>298</v>
-      </c>
-      <c r="T52" s="1" t="s">
-        <v>462</v>
-      </c>
-    </row>
-    <row r="53" spans="1:20" x14ac:dyDescent="0.25">
+    </row>
+    <row r="53" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A53" s="5">
         <v>52</v>
       </c>
-      <c r="B53" s="17"/>
-      <c r="C53" s="10"/>
-      <c r="D53" s="22" t="s">
-        <v>890</v>
+      <c r="B53" s="19"/>
+      <c r="C53" s="22"/>
+      <c r="D53" s="11" t="s">
+        <v>828</v>
       </c>
       <c r="E53" s="5" t="s">
-        <v>631</v>
+        <v>614</v>
       </c>
       <c r="F53" s="5" t="s">
         <v>54</v>
@@ -5142,29 +4492,16 @@
       <c r="K53" s="5"/>
       <c r="L53" s="5"/>
       <c r="M53" s="5"/>
-      <c r="N53" s="15"/>
-      <c r="Q53" s="1" t="s">
-        <v>631</v>
-      </c>
-      <c r="R53" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="S53" s="1" t="s">
-        <v>299</v>
-      </c>
-      <c r="T53" s="1" t="s">
-        <v>462</v>
-      </c>
-    </row>
-    <row r="54" spans="1:20" x14ac:dyDescent="0.25">
+    </row>
+    <row r="54" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A54" s="5">
         <v>53</v>
       </c>
-      <c r="B54" s="17"/>
-      <c r="C54" s="10"/>
-      <c r="D54" s="22"/>
+      <c r="B54" s="19"/>
+      <c r="C54" s="22"/>
+      <c r="D54" s="11"/>
       <c r="E54" s="5" t="s">
-        <v>632</v>
+        <v>615</v>
       </c>
       <c r="F54" s="5" t="s">
         <v>55</v>
@@ -5182,29 +4519,16 @@
       <c r="K54" s="5"/>
       <c r="L54" s="5"/>
       <c r="M54" s="5"/>
-      <c r="N54" s="15"/>
-      <c r="Q54" s="1" t="s">
-        <v>632</v>
-      </c>
-      <c r="R54" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="S54" s="1" t="s">
-        <v>300</v>
-      </c>
-      <c r="T54" s="1" t="s">
-        <v>462</v>
-      </c>
-    </row>
-    <row r="55" spans="1:20" x14ac:dyDescent="0.25">
+    </row>
+    <row r="55" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A55" s="5">
         <v>54</v>
       </c>
-      <c r="B55" s="17"/>
-      <c r="C55" s="10"/>
-      <c r="D55" s="22"/>
+      <c r="B55" s="19"/>
+      <c r="C55" s="22"/>
+      <c r="D55" s="11"/>
       <c r="E55" s="5" t="s">
-        <v>633</v>
+        <v>616</v>
       </c>
       <c r="F55" s="5" t="s">
         <v>56</v>
@@ -5222,29 +4546,16 @@
       <c r="K55" s="5"/>
       <c r="L55" s="5"/>
       <c r="M55" s="5"/>
-      <c r="N55" s="15"/>
-      <c r="Q55" s="1" t="s">
-        <v>633</v>
-      </c>
-      <c r="R55" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="S55" s="1" t="s">
-        <v>301</v>
-      </c>
-      <c r="T55" s="1" t="s">
-        <v>462</v>
-      </c>
-    </row>
-    <row r="56" spans="1:20" x14ac:dyDescent="0.25">
+    </row>
+    <row r="56" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A56" s="5">
         <v>55</v>
       </c>
-      <c r="B56" s="17"/>
-      <c r="C56" s="10"/>
-      <c r="D56" s="22"/>
+      <c r="B56" s="19"/>
+      <c r="C56" s="22"/>
+      <c r="D56" s="11"/>
       <c r="E56" s="5" t="s">
-        <v>634</v>
+        <v>617</v>
       </c>
       <c r="F56" s="5" t="s">
         <v>57</v>
@@ -5262,29 +4573,16 @@
       <c r="K56" s="5"/>
       <c r="L56" s="5"/>
       <c r="M56" s="5"/>
-      <c r="N56" s="15"/>
-      <c r="Q56" s="1" t="s">
-        <v>634</v>
-      </c>
-      <c r="R56" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="S56" s="1" t="s">
-        <v>302</v>
-      </c>
-      <c r="T56" s="1" t="s">
-        <v>462</v>
-      </c>
-    </row>
-    <row r="57" spans="1:20" x14ac:dyDescent="0.25">
+    </row>
+    <row r="57" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A57" s="5">
         <v>56</v>
       </c>
-      <c r="B57" s="17"/>
-      <c r="C57" s="10"/>
-      <c r="D57" s="22"/>
+      <c r="B57" s="19"/>
+      <c r="C57" s="22"/>
+      <c r="D57" s="11"/>
       <c r="E57" s="5" t="s">
-        <v>635</v>
+        <v>618</v>
       </c>
       <c r="F57" s="5" t="s">
         <v>58</v>
@@ -5302,31 +4600,18 @@
       <c r="K57" s="5"/>
       <c r="L57" s="5"/>
       <c r="M57" s="5"/>
-      <c r="N57" s="15"/>
-      <c r="Q57" s="1" t="s">
-        <v>635</v>
-      </c>
-      <c r="R57" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="S57" s="1" t="s">
-        <v>303</v>
-      </c>
-      <c r="T57" s="1" t="s">
-        <v>462</v>
-      </c>
-    </row>
-    <row r="58" spans="1:20" x14ac:dyDescent="0.25">
+    </row>
+    <row r="58" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A58" s="6">
         <v>57</v>
       </c>
-      <c r="B58" s="17"/>
-      <c r="C58" s="10"/>
-      <c r="D58" s="22" t="s">
-        <v>891</v>
+      <c r="B58" s="19"/>
+      <c r="C58" s="22"/>
+      <c r="D58" s="11" t="s">
+        <v>829</v>
       </c>
       <c r="E58" s="6" t="s">
-        <v>636</v>
+        <v>619</v>
       </c>
       <c r="F58" s="6" t="s">
         <v>59</v>
@@ -5344,29 +4629,16 @@
       <c r="K58" s="6"/>
       <c r="L58" s="6"/>
       <c r="M58" s="6"/>
-      <c r="N58" s="15"/>
-      <c r="Q58" s="1" t="s">
-        <v>636</v>
-      </c>
-      <c r="R58" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="S58" s="1" t="s">
-        <v>304</v>
-      </c>
-      <c r="T58" s="1" t="s">
-        <v>462</v>
-      </c>
-    </row>
-    <row r="59" spans="1:20" x14ac:dyDescent="0.25">
+    </row>
+    <row r="59" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A59" s="6">
         <v>58</v>
       </c>
-      <c r="B59" s="17"/>
-      <c r="C59" s="11"/>
-      <c r="D59" s="22"/>
+      <c r="B59" s="19"/>
+      <c r="C59" s="23"/>
+      <c r="D59" s="11"/>
       <c r="E59" s="6" t="s">
-        <v>637</v>
+        <v>620</v>
       </c>
       <c r="F59" s="6" t="s">
         <v>60</v>
@@ -5384,33 +4656,20 @@
       <c r="K59" s="6"/>
       <c r="L59" s="6"/>
       <c r="M59" s="6"/>
-      <c r="N59" s="15"/>
-      <c r="Q59" s="1" t="s">
-        <v>637</v>
-      </c>
-      <c r="R59" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="S59" s="1" t="s">
-        <v>305</v>
-      </c>
-      <c r="T59" s="1" t="s">
-        <v>462</v>
-      </c>
-    </row>
-    <row r="60" spans="1:20" x14ac:dyDescent="0.25">
+    </row>
+    <row r="60" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A60" s="5">
         <v>59</v>
       </c>
-      <c r="B60" s="17"/>
-      <c r="C60" s="22" t="s">
-        <v>892</v>
-      </c>
-      <c r="D60" s="22" t="s">
-        <v>893</v>
+      <c r="B60" s="19"/>
+      <c r="C60" s="11" t="s">
+        <v>830</v>
+      </c>
+      <c r="D60" s="11" t="s">
+        <v>831</v>
       </c>
       <c r="E60" s="5" t="s">
-        <v>638</v>
+        <v>621</v>
       </c>
       <c r="F60" s="5" t="s">
         <v>61</v>
@@ -5428,29 +4687,16 @@
       <c r="K60" s="5"/>
       <c r="L60" s="5"/>
       <c r="M60" s="5"/>
-      <c r="N60" s="15"/>
-      <c r="Q60" s="1" t="s">
-        <v>638</v>
-      </c>
-      <c r="R60" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="S60" s="1" t="s">
-        <v>306</v>
-      </c>
-      <c r="T60" s="1" t="s">
-        <v>639</v>
-      </c>
-    </row>
-    <row r="61" spans="1:20" x14ac:dyDescent="0.25">
+    </row>
+    <row r="61" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A61" s="5">
         <v>60</v>
       </c>
-      <c r="B61" s="17"/>
-      <c r="C61" s="22"/>
-      <c r="D61" s="22"/>
+      <c r="B61" s="19"/>
+      <c r="C61" s="11"/>
+      <c r="D61" s="11"/>
       <c r="E61" s="5" t="s">
-        <v>640</v>
+        <v>622</v>
       </c>
       <c r="F61" s="5" t="s">
         <v>62</v>
@@ -5468,30 +4714,16 @@
       <c r="K61" s="5"/>
       <c r="L61" s="5"/>
       <c r="M61" s="5"/>
-      <c r="N61" s="15"/>
-      <c r="P61" s="1"/>
-      <c r="Q61" s="1" t="s">
-        <v>640</v>
-      </c>
-      <c r="R61" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="S61" s="1" t="s">
-        <v>307</v>
-      </c>
-      <c r="T61" s="1" t="s">
-        <v>639</v>
-      </c>
-    </row>
-    <row r="62" spans="1:20" x14ac:dyDescent="0.25">
+    </row>
+    <row r="62" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A62" s="5">
         <v>61</v>
       </c>
-      <c r="B62" s="17"/>
-      <c r="C62" s="22"/>
-      <c r="D62" s="22"/>
+      <c r="B62" s="19"/>
+      <c r="C62" s="11"/>
+      <c r="D62" s="11"/>
       <c r="E62" s="5" t="s">
-        <v>641</v>
+        <v>623</v>
       </c>
       <c r="F62" s="5" t="s">
         <v>63</v>
@@ -5509,29 +4741,16 @@
       <c r="K62" s="5"/>
       <c r="L62" s="5"/>
       <c r="M62" s="5"/>
-      <c r="N62" s="15"/>
-      <c r="Q62" s="1" t="s">
-        <v>641</v>
-      </c>
-      <c r="R62" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="S62" s="1" t="s">
-        <v>308</v>
-      </c>
-      <c r="T62" s="1" t="s">
-        <v>639</v>
-      </c>
-    </row>
-    <row r="63" spans="1:20" x14ac:dyDescent="0.25">
+    </row>
+    <row r="63" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A63" s="5">
         <v>62</v>
       </c>
-      <c r="B63" s="17"/>
-      <c r="C63" s="22"/>
-      <c r="D63" s="22"/>
+      <c r="B63" s="19"/>
+      <c r="C63" s="11"/>
+      <c r="D63" s="11"/>
       <c r="E63" s="5" t="s">
-        <v>642</v>
+        <v>624</v>
       </c>
       <c r="F63" s="5" t="s">
         <v>64</v>
@@ -5549,29 +4768,16 @@
       <c r="K63" s="5"/>
       <c r="L63" s="5"/>
       <c r="M63" s="5"/>
-      <c r="N63" s="15"/>
-      <c r="Q63" s="1" t="s">
-        <v>642</v>
-      </c>
-      <c r="R63" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="S63" s="1" t="s">
-        <v>309</v>
-      </c>
-      <c r="T63" s="1" t="s">
-        <v>639</v>
-      </c>
-    </row>
-    <row r="64" spans="1:20" x14ac:dyDescent="0.25">
+    </row>
+    <row r="64" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A64" s="5">
         <v>63</v>
       </c>
-      <c r="B64" s="17"/>
-      <c r="C64" s="22"/>
-      <c r="D64" s="22"/>
+      <c r="B64" s="19"/>
+      <c r="C64" s="11"/>
+      <c r="D64" s="11"/>
       <c r="E64" s="5" t="s">
-        <v>643</v>
+        <v>625</v>
       </c>
       <c r="F64" s="5" t="s">
         <v>65</v>
@@ -5589,31 +4795,18 @@
       <c r="K64" s="5"/>
       <c r="L64" s="5"/>
       <c r="M64" s="5"/>
-      <c r="N64" s="15"/>
-      <c r="Q64" s="1" t="s">
-        <v>643</v>
-      </c>
-      <c r="R64" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="S64" s="1" t="s">
-        <v>310</v>
-      </c>
-      <c r="T64" s="1" t="s">
-        <v>639</v>
-      </c>
-    </row>
-    <row r="65" spans="1:20" x14ac:dyDescent="0.25">
+    </row>
+    <row r="65" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A65" s="6">
         <v>64</v>
       </c>
-      <c r="B65" s="17"/>
-      <c r="C65" s="22"/>
-      <c r="D65" s="22" t="s">
-        <v>894</v>
+      <c r="B65" s="19"/>
+      <c r="C65" s="11"/>
+      <c r="D65" s="11" t="s">
+        <v>832</v>
       </c>
       <c r="E65" s="6" t="s">
-        <v>644</v>
+        <v>626</v>
       </c>
       <c r="F65" s="6" t="s">
         <v>66</v>
@@ -5631,29 +4824,16 @@
       <c r="K65" s="6"/>
       <c r="L65" s="6"/>
       <c r="M65" s="6"/>
-      <c r="N65" s="15"/>
-      <c r="Q65" s="1" t="s">
-        <v>644</v>
-      </c>
-      <c r="R65" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="S65" s="1" t="s">
-        <v>311</v>
-      </c>
-      <c r="T65" s="1" t="s">
-        <v>639</v>
-      </c>
-    </row>
-    <row r="66" spans="1:20" x14ac:dyDescent="0.25">
+    </row>
+    <row r="66" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A66" s="6">
         <v>65</v>
       </c>
-      <c r="B66" s="17"/>
-      <c r="C66" s="22"/>
-      <c r="D66" s="22"/>
+      <c r="B66" s="19"/>
+      <c r="C66" s="11"/>
+      <c r="D66" s="11"/>
       <c r="E66" s="6" t="s">
-        <v>645</v>
+        <v>627</v>
       </c>
       <c r="F66" s="6" t="s">
         <v>67</v>
@@ -5671,29 +4851,16 @@
       <c r="K66" s="6"/>
       <c r="L66" s="6"/>
       <c r="M66" s="6"/>
-      <c r="N66" s="15"/>
-      <c r="Q66" s="1" t="s">
-        <v>645</v>
-      </c>
-      <c r="R66" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="S66" s="1" t="s">
-        <v>312</v>
-      </c>
-      <c r="T66" s="1" t="s">
-        <v>639</v>
-      </c>
-    </row>
-    <row r="67" spans="1:20" x14ac:dyDescent="0.25">
+    </row>
+    <row r="67" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A67" s="6">
         <v>66</v>
       </c>
-      <c r="B67" s="17"/>
-      <c r="C67" s="22"/>
-      <c r="D67" s="22"/>
+      <c r="B67" s="19"/>
+      <c r="C67" s="11"/>
+      <c r="D67" s="11"/>
       <c r="E67" s="6" t="s">
-        <v>646</v>
+        <v>628</v>
       </c>
       <c r="F67" s="6" t="s">
         <v>68</v>
@@ -5711,29 +4878,16 @@
       <c r="K67" s="6"/>
       <c r="L67" s="6"/>
       <c r="M67" s="6"/>
-      <c r="N67" s="15"/>
-      <c r="Q67" s="1" t="s">
-        <v>646</v>
-      </c>
-      <c r="R67" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="S67" s="1" t="s">
-        <v>313</v>
-      </c>
-      <c r="T67" s="1" t="s">
-        <v>639</v>
-      </c>
-    </row>
-    <row r="68" spans="1:20" x14ac:dyDescent="0.25">
+    </row>
+    <row r="68" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A68" s="6">
         <v>67</v>
       </c>
-      <c r="B68" s="17"/>
-      <c r="C68" s="22"/>
-      <c r="D68" s="22"/>
+      <c r="B68" s="19"/>
+      <c r="C68" s="11"/>
+      <c r="D68" s="11"/>
       <c r="E68" s="6" t="s">
-        <v>647</v>
+        <v>629</v>
       </c>
       <c r="F68" s="6" t="s">
         <v>69</v>
@@ -5751,29 +4905,16 @@
       <c r="K68" s="6"/>
       <c r="L68" s="6"/>
       <c r="M68" s="6"/>
-      <c r="N68" s="15"/>
-      <c r="Q68" s="1" t="s">
-        <v>647</v>
-      </c>
-      <c r="R68" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="S68" s="1" t="s">
-        <v>314</v>
-      </c>
-      <c r="T68" s="1" t="s">
-        <v>639</v>
-      </c>
-    </row>
-    <row r="69" spans="1:20" x14ac:dyDescent="0.25">
+    </row>
+    <row r="69" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A69" s="6">
         <v>68</v>
       </c>
-      <c r="B69" s="17"/>
-      <c r="C69" s="22"/>
-      <c r="D69" s="22"/>
+      <c r="B69" s="19"/>
+      <c r="C69" s="11"/>
+      <c r="D69" s="11"/>
       <c r="E69" s="6" t="s">
-        <v>648</v>
+        <v>630</v>
       </c>
       <c r="F69" s="6" t="s">
         <v>70</v>
@@ -5791,33 +4932,20 @@
       <c r="K69" s="6"/>
       <c r="L69" s="6"/>
       <c r="M69" s="6"/>
-      <c r="N69" s="15"/>
-      <c r="Q69" s="1" t="s">
-        <v>648</v>
-      </c>
-      <c r="R69" s="1" t="s">
-        <v>70</v>
-      </c>
-      <c r="S69" s="1" t="s">
-        <v>315</v>
-      </c>
-      <c r="T69" s="1" t="s">
-        <v>639</v>
-      </c>
-    </row>
-    <row r="70" spans="1:20" x14ac:dyDescent="0.25">
+    </row>
+    <row r="70" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A70" s="5">
         <v>69</v>
       </c>
-      <c r="B70" s="17"/>
-      <c r="C70" s="22" t="s">
-        <v>895</v>
-      </c>
-      <c r="D70" s="22" t="s">
-        <v>895</v>
+      <c r="B70" s="19"/>
+      <c r="C70" s="11" t="s">
+        <v>833</v>
+      </c>
+      <c r="D70" s="11" t="s">
+        <v>833</v>
       </c>
       <c r="E70" s="5" t="s">
-        <v>649</v>
+        <v>631</v>
       </c>
       <c r="F70" s="5" t="s">
         <v>71</v>
@@ -5835,29 +4963,16 @@
       <c r="K70" s="5"/>
       <c r="L70" s="5"/>
       <c r="M70" s="5"/>
-      <c r="N70" s="15"/>
-      <c r="Q70" s="1" t="s">
-        <v>649</v>
-      </c>
-      <c r="R70" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="S70" s="1" t="s">
-        <v>650</v>
-      </c>
-      <c r="T70" s="1" t="s">
-        <v>639</v>
-      </c>
-    </row>
-    <row r="71" spans="1:20" x14ac:dyDescent="0.25">
+    </row>
+    <row r="71" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A71" s="5">
         <v>70</v>
       </c>
-      <c r="B71" s="17"/>
-      <c r="C71" s="22"/>
-      <c r="D71" s="22"/>
+      <c r="B71" s="19"/>
+      <c r="C71" s="11"/>
+      <c r="D71" s="11"/>
       <c r="E71" s="5" t="s">
-        <v>651</v>
+        <v>632</v>
       </c>
       <c r="F71" s="5" t="s">
         <v>72</v>
@@ -5875,29 +4990,16 @@
       <c r="K71" s="5"/>
       <c r="L71" s="5"/>
       <c r="M71" s="5"/>
-      <c r="N71" s="15"/>
-      <c r="Q71" s="1" t="s">
-        <v>651</v>
-      </c>
-      <c r="R71" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="S71" s="1" t="s">
-        <v>652</v>
-      </c>
-      <c r="T71" s="1" t="s">
-        <v>639</v>
-      </c>
-    </row>
-    <row r="72" spans="1:20" x14ac:dyDescent="0.25">
+    </row>
+    <row r="72" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A72" s="5">
         <v>71</v>
       </c>
-      <c r="B72" s="17"/>
-      <c r="C72" s="22"/>
-      <c r="D72" s="22"/>
+      <c r="B72" s="19"/>
+      <c r="C72" s="11"/>
+      <c r="D72" s="11"/>
       <c r="E72" s="5" t="s">
-        <v>653</v>
+        <v>633</v>
       </c>
       <c r="F72" s="5" t="s">
         <v>73</v>
@@ -5915,29 +5017,16 @@
       <c r="K72" s="5"/>
       <c r="L72" s="5"/>
       <c r="M72" s="5"/>
-      <c r="N72" s="15"/>
-      <c r="Q72" s="1" t="s">
-        <v>653</v>
-      </c>
-      <c r="R72" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="S72" s="1" t="s">
-        <v>654</v>
-      </c>
-      <c r="T72" s="1" t="s">
-        <v>639</v>
-      </c>
-    </row>
-    <row r="73" spans="1:20" x14ac:dyDescent="0.25">
+    </row>
+    <row r="73" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A73" s="5">
         <v>72</v>
       </c>
-      <c r="B73" s="17"/>
-      <c r="C73" s="22"/>
-      <c r="D73" s="22"/>
+      <c r="B73" s="19"/>
+      <c r="C73" s="11"/>
+      <c r="D73" s="11"/>
       <c r="E73" s="5" t="s">
-        <v>655</v>
+        <v>634</v>
       </c>
       <c r="F73" s="5" t="s">
         <v>74</v>
@@ -5955,29 +5044,16 @@
       <c r="K73" s="5"/>
       <c r="L73" s="5"/>
       <c r="M73" s="5"/>
-      <c r="N73" s="15"/>
-      <c r="Q73" s="1" t="s">
-        <v>655</v>
-      </c>
-      <c r="R73" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="S73" s="1" t="s">
-        <v>656</v>
-      </c>
-      <c r="T73" s="1" t="s">
-        <v>639</v>
-      </c>
-    </row>
-    <row r="74" spans="1:20" x14ac:dyDescent="0.25">
+    </row>
+    <row r="74" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A74" s="5">
         <v>73</v>
       </c>
-      <c r="B74" s="17"/>
-      <c r="C74" s="22"/>
-      <c r="D74" s="22"/>
+      <c r="B74" s="19"/>
+      <c r="C74" s="11"/>
+      <c r="D74" s="11"/>
       <c r="E74" s="5" t="s">
-        <v>657</v>
+        <v>635</v>
       </c>
       <c r="F74" s="5" t="s">
         <v>75</v>
@@ -5995,29 +5071,16 @@
       <c r="K74" s="5"/>
       <c r="L74" s="5"/>
       <c r="M74" s="5"/>
-      <c r="N74" s="15"/>
-      <c r="Q74" s="1" t="s">
-        <v>657</v>
-      </c>
-      <c r="R74" s="1" t="s">
-        <v>75</v>
-      </c>
-      <c r="S74" s="1" t="s">
-        <v>658</v>
-      </c>
-      <c r="T74" s="1" t="s">
-        <v>639</v>
-      </c>
-    </row>
-    <row r="75" spans="1:20" x14ac:dyDescent="0.25">
+    </row>
+    <row r="75" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A75" s="5">
         <v>74</v>
       </c>
-      <c r="B75" s="17"/>
-      <c r="C75" s="22"/>
-      <c r="D75" s="22"/>
+      <c r="B75" s="19"/>
+      <c r="C75" s="11"/>
+      <c r="D75" s="11"/>
       <c r="E75" s="5" t="s">
-        <v>659</v>
+        <v>636</v>
       </c>
       <c r="F75" s="5" t="s">
         <v>76</v>
@@ -6035,29 +5098,16 @@
       <c r="K75" s="5"/>
       <c r="L75" s="5"/>
       <c r="M75" s="5"/>
-      <c r="N75" s="15"/>
-      <c r="Q75" s="1" t="s">
-        <v>659</v>
-      </c>
-      <c r="R75" s="1" t="s">
-        <v>76</v>
-      </c>
-      <c r="S75" s="1" t="s">
-        <v>660</v>
-      </c>
-      <c r="T75" s="1" t="s">
-        <v>639</v>
-      </c>
-    </row>
-    <row r="76" spans="1:20" x14ac:dyDescent="0.25">
+    </row>
+    <row r="76" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A76" s="5">
         <v>75</v>
       </c>
-      <c r="B76" s="17"/>
-      <c r="C76" s="22"/>
-      <c r="D76" s="22"/>
+      <c r="B76" s="19"/>
+      <c r="C76" s="11"/>
+      <c r="D76" s="11"/>
       <c r="E76" s="5" t="s">
-        <v>661</v>
+        <v>637</v>
       </c>
       <c r="F76" s="5" t="s">
         <v>77</v>
@@ -6075,29 +5125,16 @@
       <c r="K76" s="5"/>
       <c r="L76" s="5"/>
       <c r="M76" s="5"/>
-      <c r="N76" s="15"/>
-      <c r="Q76" s="1" t="s">
-        <v>661</v>
-      </c>
-      <c r="R76" s="1" t="s">
-        <v>77</v>
-      </c>
-      <c r="S76" s="1" t="s">
-        <v>662</v>
-      </c>
-      <c r="T76" s="1" t="s">
-        <v>639</v>
-      </c>
-    </row>
-    <row r="77" spans="1:20" x14ac:dyDescent="0.25">
+    </row>
+    <row r="77" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A77" s="5">
         <v>76</v>
       </c>
-      <c r="B77" s="17"/>
-      <c r="C77" s="22"/>
-      <c r="D77" s="22"/>
+      <c r="B77" s="19"/>
+      <c r="C77" s="11"/>
+      <c r="D77" s="11"/>
       <c r="E77" s="5" t="s">
-        <v>663</v>
+        <v>638</v>
       </c>
       <c r="F77" s="5" t="s">
         <v>78</v>
@@ -6115,29 +5152,16 @@
       <c r="K77" s="5"/>
       <c r="L77" s="5"/>
       <c r="M77" s="5"/>
-      <c r="N77" s="15"/>
-      <c r="Q77" s="1" t="s">
-        <v>663</v>
-      </c>
-      <c r="R77" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="S77" s="1" t="s">
-        <v>664</v>
-      </c>
-      <c r="T77" s="1" t="s">
-        <v>639</v>
-      </c>
-    </row>
-    <row r="78" spans="1:20" x14ac:dyDescent="0.25">
+    </row>
+    <row r="78" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A78" s="5">
         <v>77</v>
       </c>
-      <c r="B78" s="17"/>
-      <c r="C78" s="22"/>
-      <c r="D78" s="22"/>
+      <c r="B78" s="19"/>
+      <c r="C78" s="11"/>
+      <c r="D78" s="11"/>
       <c r="E78" s="5" t="s">
-        <v>665</v>
+        <v>639</v>
       </c>
       <c r="F78" s="5" t="s">
         <v>79</v>
@@ -6155,33 +5179,20 @@
       <c r="K78" s="5"/>
       <c r="L78" s="5"/>
       <c r="M78" s="5"/>
-      <c r="N78" s="15"/>
-      <c r="Q78" s="1" t="s">
-        <v>665</v>
-      </c>
-      <c r="R78" s="1" t="s">
-        <v>79</v>
-      </c>
-      <c r="S78" s="1" t="s">
-        <v>666</v>
-      </c>
-      <c r="T78" s="1" t="s">
-        <v>639</v>
-      </c>
-    </row>
-    <row r="79" spans="1:20" x14ac:dyDescent="0.25">
+    </row>
+    <row r="79" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A79" s="6">
         <v>78</v>
       </c>
-      <c r="B79" s="17"/>
-      <c r="C79" s="22" t="s">
-        <v>896</v>
-      </c>
-      <c r="D79" s="22" t="s">
-        <v>896</v>
+      <c r="B79" s="19"/>
+      <c r="C79" s="11" t="s">
+        <v>834</v>
+      </c>
+      <c r="D79" s="11" t="s">
+        <v>834</v>
       </c>
       <c r="E79" s="6" t="s">
-        <v>667</v>
+        <v>640</v>
       </c>
       <c r="F79" s="6" t="s">
         <v>80</v>
@@ -6199,29 +5210,16 @@
       <c r="K79" s="6"/>
       <c r="L79" s="6"/>
       <c r="M79" s="6"/>
-      <c r="N79" s="15"/>
-      <c r="Q79" s="1" t="s">
-        <v>667</v>
-      </c>
-      <c r="R79" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="S79" s="1" t="s">
-        <v>668</v>
-      </c>
-      <c r="T79" s="1" t="s">
-        <v>639</v>
-      </c>
-    </row>
-    <row r="80" spans="1:20" x14ac:dyDescent="0.25">
+    </row>
+    <row r="80" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A80" s="6">
         <v>79</v>
       </c>
-      <c r="B80" s="17"/>
-      <c r="C80" s="22"/>
-      <c r="D80" s="22"/>
+      <c r="B80" s="19"/>
+      <c r="C80" s="11"/>
+      <c r="D80" s="11"/>
       <c r="E80" s="6" t="s">
-        <v>669</v>
+        <v>641</v>
       </c>
       <c r="F80" s="6" t="s">
         <v>81</v>
@@ -6239,29 +5237,16 @@
       <c r="K80" s="6"/>
       <c r="L80" s="6"/>
       <c r="M80" s="6"/>
-      <c r="N80" s="15"/>
-      <c r="Q80" s="1" t="s">
-        <v>669</v>
-      </c>
-      <c r="R80" s="1" t="s">
-        <v>81</v>
-      </c>
-      <c r="S80" s="1" t="s">
-        <v>670</v>
-      </c>
-      <c r="T80" s="1" t="s">
-        <v>639</v>
-      </c>
-    </row>
-    <row r="81" spans="1:20" x14ac:dyDescent="0.25">
+    </row>
+    <row r="81" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A81" s="6">
         <v>80</v>
       </c>
-      <c r="B81" s="17"/>
-      <c r="C81" s="22"/>
-      <c r="D81" s="22"/>
+      <c r="B81" s="19"/>
+      <c r="C81" s="11"/>
+      <c r="D81" s="11"/>
       <c r="E81" s="6" t="s">
-        <v>671</v>
+        <v>642</v>
       </c>
       <c r="F81" s="6" t="s">
         <v>82</v>
@@ -6279,29 +5264,16 @@
       <c r="K81" s="6"/>
       <c r="L81" s="6"/>
       <c r="M81" s="6"/>
-      <c r="N81" s="15"/>
-      <c r="Q81" s="1" t="s">
-        <v>671</v>
-      </c>
-      <c r="R81" s="1" t="s">
-        <v>82</v>
-      </c>
-      <c r="S81" s="1" t="s">
-        <v>672</v>
-      </c>
-      <c r="T81" s="1" t="s">
-        <v>639</v>
-      </c>
-    </row>
-    <row r="82" spans="1:20" x14ac:dyDescent="0.25">
+    </row>
+    <row r="82" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A82" s="6">
         <v>81</v>
       </c>
-      <c r="B82" s="17"/>
-      <c r="C82" s="22"/>
-      <c r="D82" s="22"/>
+      <c r="B82" s="19"/>
+      <c r="C82" s="11"/>
+      <c r="D82" s="11"/>
       <c r="E82" s="6" t="s">
-        <v>673</v>
+        <v>643</v>
       </c>
       <c r="F82" s="6" t="s">
         <v>83</v>
@@ -6319,29 +5291,16 @@
       <c r="K82" s="6"/>
       <c r="L82" s="6"/>
       <c r="M82" s="6"/>
-      <c r="N82" s="15"/>
-      <c r="Q82" s="1" t="s">
-        <v>673</v>
-      </c>
-      <c r="R82" s="1" t="s">
-        <v>83</v>
-      </c>
-      <c r="S82" s="1" t="s">
-        <v>674</v>
-      </c>
-      <c r="T82" s="1" t="s">
-        <v>639</v>
-      </c>
-    </row>
-    <row r="83" spans="1:20" x14ac:dyDescent="0.25">
+    </row>
+    <row r="83" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A83" s="6">
         <v>82</v>
       </c>
-      <c r="B83" s="17"/>
-      <c r="C83" s="22"/>
-      <c r="D83" s="22"/>
+      <c r="B83" s="19"/>
+      <c r="C83" s="11"/>
+      <c r="D83" s="11"/>
       <c r="E83" s="6" t="s">
-        <v>675</v>
+        <v>644</v>
       </c>
       <c r="F83" s="6" t="s">
         <v>84</v>
@@ -6359,29 +5318,16 @@
       <c r="K83" s="6"/>
       <c r="L83" s="6"/>
       <c r="M83" s="6"/>
-      <c r="N83" s="15"/>
-      <c r="Q83" s="1" t="s">
-        <v>675</v>
-      </c>
-      <c r="R83" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="S83" s="1" t="s">
-        <v>676</v>
-      </c>
-      <c r="T83" s="1" t="s">
-        <v>639</v>
-      </c>
-    </row>
-    <row r="84" spans="1:20" x14ac:dyDescent="0.25">
+    </row>
+    <row r="84" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A84" s="6">
         <v>83</v>
       </c>
-      <c r="B84" s="17"/>
-      <c r="C84" s="22"/>
-      <c r="D84" s="22"/>
+      <c r="B84" s="19"/>
+      <c r="C84" s="11"/>
+      <c r="D84" s="11"/>
       <c r="E84" s="6" t="s">
-        <v>677</v>
+        <v>645</v>
       </c>
       <c r="F84" s="6" t="s">
         <v>85</v>
@@ -6399,31 +5345,18 @@
       <c r="K84" s="6"/>
       <c r="L84" s="6"/>
       <c r="M84" s="6"/>
-      <c r="N84" s="15"/>
-      <c r="Q84" s="1" t="s">
-        <v>677</v>
-      </c>
-      <c r="R84" s="1" t="s">
-        <v>85</v>
-      </c>
-      <c r="S84" s="1" t="s">
-        <v>678</v>
-      </c>
-      <c r="T84" s="1" t="s">
-        <v>639</v>
-      </c>
-    </row>
-    <row r="85" spans="1:20" x14ac:dyDescent="0.25">
+    </row>
+    <row r="85" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A85" s="5">
         <v>84</v>
       </c>
-      <c r="B85" s="17"/>
-      <c r="C85" s="22" t="s">
-        <v>897</v>
-      </c>
-      <c r="D85" s="22"/>
+      <c r="B85" s="19"/>
+      <c r="C85" s="11" t="s">
+        <v>835</v>
+      </c>
+      <c r="D85" s="11"/>
       <c r="E85" s="5" t="s">
-        <v>679</v>
+        <v>646</v>
       </c>
       <c r="F85" s="5" t="s">
         <v>86</v>
@@ -6441,29 +5374,16 @@
       <c r="K85" s="5"/>
       <c r="L85" s="5"/>
       <c r="M85" s="5"/>
-      <c r="N85" s="15"/>
-      <c r="Q85" s="1" t="s">
-        <v>679</v>
-      </c>
-      <c r="R85" s="1" t="s">
-        <v>86</v>
-      </c>
-      <c r="S85" s="1" t="s">
-        <v>331</v>
-      </c>
-      <c r="T85" s="1" t="s">
-        <v>639</v>
-      </c>
-    </row>
-    <row r="86" spans="1:20" x14ac:dyDescent="0.25">
+    </row>
+    <row r="86" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A86" s="5">
         <v>85</v>
       </c>
-      <c r="B86" s="17"/>
-      <c r="C86" s="22"/>
-      <c r="D86" s="22"/>
+      <c r="B86" s="19"/>
+      <c r="C86" s="11"/>
+      <c r="D86" s="11"/>
       <c r="E86" s="5" t="s">
-        <v>680</v>
+        <v>647</v>
       </c>
       <c r="F86" s="5" t="s">
         <v>87</v>
@@ -6481,29 +5401,16 @@
       <c r="K86" s="5"/>
       <c r="L86" s="5"/>
       <c r="M86" s="5"/>
-      <c r="N86" s="15"/>
-      <c r="Q86" s="1" t="s">
-        <v>680</v>
-      </c>
-      <c r="R86" s="1" t="s">
-        <v>87</v>
-      </c>
-      <c r="S86" s="1" t="s">
-        <v>332</v>
-      </c>
-      <c r="T86" s="1" t="s">
-        <v>639</v>
-      </c>
-    </row>
-    <row r="87" spans="1:20" x14ac:dyDescent="0.25">
+    </row>
+    <row r="87" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A87" s="5">
         <v>86</v>
       </c>
-      <c r="B87" s="17"/>
-      <c r="C87" s="22"/>
-      <c r="D87" s="22"/>
+      <c r="B87" s="19"/>
+      <c r="C87" s="11"/>
+      <c r="D87" s="11"/>
       <c r="E87" s="5" t="s">
-        <v>681</v>
+        <v>648</v>
       </c>
       <c r="F87" s="5" t="s">
         <v>88</v>
@@ -6521,29 +5428,16 @@
       <c r="K87" s="5"/>
       <c r="L87" s="5"/>
       <c r="M87" s="5"/>
-      <c r="N87" s="15"/>
-      <c r="Q87" s="1" t="s">
-        <v>681</v>
-      </c>
-      <c r="R87" s="1" t="s">
-        <v>88</v>
-      </c>
-      <c r="S87" s="1" t="s">
-        <v>333</v>
-      </c>
-      <c r="T87" s="1" t="s">
-        <v>639</v>
-      </c>
-    </row>
-    <row r="88" spans="1:20" x14ac:dyDescent="0.25">
+    </row>
+    <row r="88" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A88" s="5">
         <v>87</v>
       </c>
-      <c r="B88" s="17"/>
-      <c r="C88" s="22"/>
-      <c r="D88" s="22"/>
+      <c r="B88" s="19"/>
+      <c r="C88" s="11"/>
+      <c r="D88" s="11"/>
       <c r="E88" s="5" t="s">
-        <v>682</v>
+        <v>649</v>
       </c>
       <c r="F88" s="5" t="s">
         <v>89</v>
@@ -6561,29 +5455,16 @@
       <c r="K88" s="5"/>
       <c r="L88" s="5"/>
       <c r="M88" s="5"/>
-      <c r="N88" s="15"/>
-      <c r="Q88" s="1" t="s">
-        <v>682</v>
-      </c>
-      <c r="R88" s="1" t="s">
-        <v>89</v>
-      </c>
-      <c r="S88" s="1" t="s">
-        <v>334</v>
-      </c>
-      <c r="T88" s="1" t="s">
-        <v>639</v>
-      </c>
-    </row>
-    <row r="89" spans="1:20" x14ac:dyDescent="0.25">
+    </row>
+    <row r="89" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A89" s="5">
         <v>88</v>
       </c>
-      <c r="B89" s="17"/>
-      <c r="C89" s="22"/>
-      <c r="D89" s="22"/>
+      <c r="B89" s="19"/>
+      <c r="C89" s="11"/>
+      <c r="D89" s="11"/>
       <c r="E89" s="5" t="s">
-        <v>683</v>
+        <v>650</v>
       </c>
       <c r="F89" s="5" t="s">
         <v>90</v>
@@ -6601,31 +5482,18 @@
       <c r="K89" s="5"/>
       <c r="L89" s="5"/>
       <c r="M89" s="5"/>
-      <c r="N89" s="15"/>
-      <c r="Q89" s="1" t="s">
-        <v>683</v>
-      </c>
-      <c r="R89" s="1" t="s">
-        <v>90</v>
-      </c>
-      <c r="S89" s="1" t="s">
-        <v>335</v>
-      </c>
-      <c r="T89" s="1" t="s">
-        <v>639</v>
-      </c>
-    </row>
-    <row r="90" spans="1:20" x14ac:dyDescent="0.25">
+    </row>
+    <row r="90" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A90" s="6">
         <v>89</v>
       </c>
-      <c r="B90" s="17"/>
-      <c r="C90" s="22" t="s">
-        <v>898</v>
-      </c>
-      <c r="D90" s="22"/>
+      <c r="B90" s="19"/>
+      <c r="C90" s="11" t="s">
+        <v>836</v>
+      </c>
+      <c r="D90" s="11"/>
       <c r="E90" s="6" t="s">
-        <v>684</v>
+        <v>651</v>
       </c>
       <c r="F90" s="6" t="s">
         <v>91</v>
@@ -6643,33 +5511,20 @@
       <c r="K90" s="6"/>
       <c r="L90" s="6"/>
       <c r="M90" s="6"/>
-      <c r="N90" s="15"/>
-      <c r="Q90" s="1" t="s">
-        <v>684</v>
-      </c>
-      <c r="R90" s="1" t="s">
-        <v>91</v>
-      </c>
-      <c r="S90" s="1" t="s">
-        <v>336</v>
-      </c>
-      <c r="T90" s="1" t="s">
-        <v>639</v>
-      </c>
-    </row>
-    <row r="91" spans="1:20" x14ac:dyDescent="0.25">
+    </row>
+    <row r="91" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A91" s="5">
         <v>90</v>
       </c>
-      <c r="B91" s="17"/>
-      <c r="C91" s="22" t="s">
-        <v>899</v>
-      </c>
-      <c r="D91" s="22" t="s">
-        <v>900</v>
+      <c r="B91" s="19"/>
+      <c r="C91" s="11" t="s">
+        <v>837</v>
+      </c>
+      <c r="D91" s="11" t="s">
+        <v>838</v>
       </c>
       <c r="E91" s="5" t="s">
-        <v>687</v>
+        <v>654</v>
       </c>
       <c r="F91" s="5" t="s">
         <v>92</v>
@@ -6687,29 +5542,16 @@
       <c r="K91" s="5"/>
       <c r="L91" s="5"/>
       <c r="M91" s="5"/>
-      <c r="N91" s="15"/>
-      <c r="Q91" s="1" t="s">
-        <v>687</v>
-      </c>
-      <c r="R91" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="S91" s="1" t="s">
-        <v>688</v>
-      </c>
-      <c r="T91" s="1" t="s">
-        <v>639</v>
-      </c>
-    </row>
-    <row r="92" spans="1:20" x14ac:dyDescent="0.25">
+    </row>
+    <row r="92" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A92" s="5">
         <v>91</v>
       </c>
-      <c r="B92" s="17"/>
-      <c r="C92" s="22"/>
-      <c r="D92" s="22"/>
+      <c r="B92" s="19"/>
+      <c r="C92" s="11"/>
+      <c r="D92" s="11"/>
       <c r="E92" s="5" t="s">
-        <v>689</v>
+        <v>655</v>
       </c>
       <c r="F92" s="5" t="s">
         <v>93</v>
@@ -6727,29 +5569,16 @@
       <c r="K92" s="5"/>
       <c r="L92" s="5"/>
       <c r="M92" s="5"/>
-      <c r="N92" s="15"/>
-      <c r="Q92" s="1" t="s">
-        <v>689</v>
-      </c>
-      <c r="R92" s="1" t="s">
-        <v>93</v>
-      </c>
-      <c r="S92" s="1" t="s">
-        <v>690</v>
-      </c>
-      <c r="T92" s="1" t="s">
-        <v>639</v>
-      </c>
-    </row>
-    <row r="93" spans="1:20" x14ac:dyDescent="0.25">
+    </row>
+    <row r="93" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A93" s="5">
         <v>92</v>
       </c>
-      <c r="B93" s="17"/>
-      <c r="C93" s="22"/>
-      <c r="D93" s="22"/>
+      <c r="B93" s="19"/>
+      <c r="C93" s="11"/>
+      <c r="D93" s="11"/>
       <c r="E93" s="5" t="s">
-        <v>691</v>
+        <v>656</v>
       </c>
       <c r="F93" s="5" t="s">
         <v>94</v>
@@ -6767,31 +5596,18 @@
       <c r="K93" s="5"/>
       <c r="L93" s="5"/>
       <c r="M93" s="5"/>
-      <c r="N93" s="15"/>
-      <c r="Q93" s="1" t="s">
-        <v>691</v>
-      </c>
-      <c r="R93" s="1" t="s">
-        <v>94</v>
-      </c>
-      <c r="S93" s="1" t="s">
-        <v>692</v>
-      </c>
-      <c r="T93" s="1" t="s">
-        <v>639</v>
-      </c>
-    </row>
-    <row r="94" spans="1:20" x14ac:dyDescent="0.25">
+    </row>
+    <row r="94" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A94" s="6">
         <v>93</v>
       </c>
-      <c r="B94" s="17"/>
-      <c r="C94" s="22"/>
-      <c r="D94" s="22" t="s">
-        <v>901</v>
+      <c r="B94" s="19"/>
+      <c r="C94" s="11"/>
+      <c r="D94" s="11" t="s">
+        <v>839</v>
       </c>
       <c r="E94" s="6" t="s">
-        <v>693</v>
+        <v>657</v>
       </c>
       <c r="F94" s="6" t="s">
         <v>95</v>
@@ -6809,29 +5625,16 @@
       <c r="K94" s="6"/>
       <c r="L94" s="6"/>
       <c r="M94" s="6"/>
-      <c r="N94" s="15"/>
-      <c r="Q94" s="1" t="s">
-        <v>693</v>
-      </c>
-      <c r="R94" s="1" t="s">
-        <v>95</v>
-      </c>
-      <c r="S94" s="1" t="s">
-        <v>694</v>
-      </c>
-      <c r="T94" s="1" t="s">
-        <v>639</v>
-      </c>
-    </row>
-    <row r="95" spans="1:20" x14ac:dyDescent="0.25">
+    </row>
+    <row r="95" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A95" s="6">
         <v>94</v>
       </c>
-      <c r="B95" s="17"/>
-      <c r="C95" s="22"/>
-      <c r="D95" s="22"/>
+      <c r="B95" s="19"/>
+      <c r="C95" s="11"/>
+      <c r="D95" s="11"/>
       <c r="E95" s="6" t="s">
-        <v>695</v>
+        <v>658</v>
       </c>
       <c r="F95" s="6" t="s">
         <v>96</v>
@@ -6849,29 +5652,16 @@
       <c r="K95" s="6"/>
       <c r="L95" s="6"/>
       <c r="M95" s="6"/>
-      <c r="N95" s="15"/>
-      <c r="Q95" s="1" t="s">
-        <v>695</v>
-      </c>
-      <c r="R95" s="1" t="s">
-        <v>96</v>
-      </c>
-      <c r="S95" s="1" t="s">
-        <v>696</v>
-      </c>
-      <c r="T95" s="1" t="s">
-        <v>639</v>
-      </c>
-    </row>
-    <row r="96" spans="1:20" x14ac:dyDescent="0.25">
+    </row>
+    <row r="96" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A96" s="6">
         <v>95</v>
       </c>
-      <c r="B96" s="17"/>
-      <c r="C96" s="22"/>
-      <c r="D96" s="22"/>
+      <c r="B96" s="19"/>
+      <c r="C96" s="11"/>
+      <c r="D96" s="11"/>
       <c r="E96" s="6" t="s">
-        <v>697</v>
+        <v>659</v>
       </c>
       <c r="F96" s="6" t="s">
         <v>97</v>
@@ -6889,29 +5679,16 @@
       <c r="K96" s="6"/>
       <c r="L96" s="6"/>
       <c r="M96" s="6"/>
-      <c r="N96" s="15"/>
-      <c r="Q96" s="1" t="s">
-        <v>697</v>
-      </c>
-      <c r="R96" s="1" t="s">
-        <v>97</v>
-      </c>
-      <c r="S96" s="1" t="s">
-        <v>698</v>
-      </c>
-      <c r="T96" s="1" t="s">
-        <v>639</v>
-      </c>
-    </row>
-    <row r="97" spans="1:20" x14ac:dyDescent="0.25">
+    </row>
+    <row r="97" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A97" s="6">
         <v>96</v>
       </c>
-      <c r="B97" s="17"/>
-      <c r="C97" s="22"/>
-      <c r="D97" s="22"/>
+      <c r="B97" s="19"/>
+      <c r="C97" s="11"/>
+      <c r="D97" s="11"/>
       <c r="E97" s="6" t="s">
-        <v>699</v>
+        <v>660</v>
       </c>
       <c r="F97" s="6" t="s">
         <v>98</v>
@@ -6929,29 +5706,16 @@
       <c r="K97" s="6"/>
       <c r="L97" s="6"/>
       <c r="M97" s="6"/>
-      <c r="N97" s="15"/>
-      <c r="Q97" s="1" t="s">
-        <v>699</v>
-      </c>
-      <c r="R97" s="1" t="s">
-        <v>98</v>
-      </c>
-      <c r="S97" s="1" t="s">
-        <v>700</v>
-      </c>
-      <c r="T97" s="1" t="s">
-        <v>639</v>
-      </c>
-    </row>
-    <row r="98" spans="1:20" x14ac:dyDescent="0.25">
+    </row>
+    <row r="98" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A98" s="6">
         <v>97</v>
       </c>
-      <c r="B98" s="17"/>
-      <c r="C98" s="22"/>
-      <c r="D98" s="22"/>
+      <c r="B98" s="19"/>
+      <c r="C98" s="11"/>
+      <c r="D98" s="11"/>
       <c r="E98" s="6" t="s">
-        <v>701</v>
+        <v>661</v>
       </c>
       <c r="F98" s="6" t="s">
         <v>99</v>
@@ -6969,29 +5733,16 @@
       <c r="K98" s="6"/>
       <c r="L98" s="6"/>
       <c r="M98" s="6"/>
-      <c r="N98" s="15"/>
-      <c r="Q98" s="1" t="s">
-        <v>701</v>
-      </c>
-      <c r="R98" s="1" t="s">
-        <v>99</v>
-      </c>
-      <c r="S98" s="1" t="s">
-        <v>702</v>
-      </c>
-      <c r="T98" s="1" t="s">
-        <v>639</v>
-      </c>
-    </row>
-    <row r="99" spans="1:20" x14ac:dyDescent="0.25">
+    </row>
+    <row r="99" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A99" s="6">
         <v>98</v>
       </c>
-      <c r="B99" s="17"/>
-      <c r="C99" s="22"/>
-      <c r="D99" s="22"/>
+      <c r="B99" s="19"/>
+      <c r="C99" s="11"/>
+      <c r="D99" s="11"/>
       <c r="E99" s="6" t="s">
-        <v>703</v>
+        <v>662</v>
       </c>
       <c r="F99" s="6" t="s">
         <v>100</v>
@@ -7009,31 +5760,18 @@
       <c r="K99" s="6"/>
       <c r="L99" s="6"/>
       <c r="M99" s="6"/>
-      <c r="N99" s="15"/>
-      <c r="Q99" s="1" t="s">
-        <v>703</v>
-      </c>
-      <c r="R99" s="1" t="s">
-        <v>100</v>
-      </c>
-      <c r="S99" s="1" t="s">
-        <v>704</v>
-      </c>
-      <c r="T99" s="1" t="s">
-        <v>639</v>
-      </c>
-    </row>
-    <row r="100" spans="1:20" x14ac:dyDescent="0.25">
+    </row>
+    <row r="100" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A100" s="5">
         <v>99</v>
       </c>
-      <c r="B100" s="17"/>
-      <c r="C100" s="22"/>
-      <c r="D100" s="22" t="s">
-        <v>902</v>
+      <c r="B100" s="19"/>
+      <c r="C100" s="11"/>
+      <c r="D100" s="11" t="s">
+        <v>840</v>
       </c>
       <c r="E100" s="5" t="s">
-        <v>705</v>
+        <v>663</v>
       </c>
       <c r="F100" s="5" t="s">
         <v>101</v>
@@ -7051,29 +5789,16 @@
       <c r="K100" s="5"/>
       <c r="L100" s="5"/>
       <c r="M100" s="5"/>
-      <c r="N100" s="15"/>
-      <c r="Q100" s="1" t="s">
-        <v>705</v>
-      </c>
-      <c r="R100" s="1" t="s">
-        <v>101</v>
-      </c>
-      <c r="S100" s="1" t="s">
-        <v>346</v>
-      </c>
-      <c r="T100" s="1" t="s">
-        <v>639</v>
-      </c>
-    </row>
-    <row r="101" spans="1:20" x14ac:dyDescent="0.25">
+    </row>
+    <row r="101" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A101" s="5">
         <v>100</v>
       </c>
-      <c r="B101" s="17"/>
-      <c r="C101" s="22"/>
-      <c r="D101" s="22"/>
+      <c r="B101" s="19"/>
+      <c r="C101" s="11"/>
+      <c r="D101" s="11"/>
       <c r="E101" s="5" t="s">
-        <v>706</v>
+        <v>664</v>
       </c>
       <c r="F101" s="5" t="s">
         <v>102</v>
@@ -7091,29 +5816,16 @@
       <c r="K101" s="5"/>
       <c r="L101" s="5"/>
       <c r="M101" s="5"/>
-      <c r="N101" s="15"/>
-      <c r="Q101" s="1" t="s">
-        <v>706</v>
-      </c>
-      <c r="R101" s="1" t="s">
-        <v>102</v>
-      </c>
-      <c r="S101" s="1" t="s">
-        <v>707</v>
-      </c>
-      <c r="T101" s="1" t="s">
-        <v>639</v>
-      </c>
-    </row>
-    <row r="102" spans="1:20" x14ac:dyDescent="0.25">
+    </row>
+    <row r="102" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A102" s="5">
         <v>101</v>
       </c>
-      <c r="B102" s="17"/>
-      <c r="C102" s="22"/>
-      <c r="D102" s="22"/>
+      <c r="B102" s="19"/>
+      <c r="C102" s="11"/>
+      <c r="D102" s="11"/>
       <c r="E102" s="5" t="s">
-        <v>708</v>
+        <v>665</v>
       </c>
       <c r="F102" s="5" t="s">
         <v>103</v>
@@ -7131,29 +5843,16 @@
       <c r="K102" s="5"/>
       <c r="L102" s="5"/>
       <c r="M102" s="5"/>
-      <c r="N102" s="15"/>
-      <c r="Q102" s="1" t="s">
-        <v>708</v>
-      </c>
-      <c r="R102" s="1" t="s">
-        <v>103</v>
-      </c>
-      <c r="S102" s="1" t="s">
-        <v>348</v>
-      </c>
-      <c r="T102" s="1" t="s">
-        <v>639</v>
-      </c>
-    </row>
-    <row r="103" spans="1:20" x14ac:dyDescent="0.25">
+    </row>
+    <row r="103" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A103" s="5">
         <v>102</v>
       </c>
-      <c r="B103" s="17"/>
-      <c r="C103" s="22"/>
-      <c r="D103" s="22"/>
+      <c r="B103" s="19"/>
+      <c r="C103" s="11"/>
+      <c r="D103" s="11"/>
       <c r="E103" s="5" t="s">
-        <v>709</v>
+        <v>666</v>
       </c>
       <c r="F103" s="5" t="s">
         <v>104</v>
@@ -7171,29 +5870,16 @@
       <c r="K103" s="5"/>
       <c r="L103" s="5"/>
       <c r="M103" s="5"/>
-      <c r="N103" s="15"/>
-      <c r="Q103" s="1" t="s">
-        <v>709</v>
-      </c>
-      <c r="R103" s="1" t="s">
-        <v>104</v>
-      </c>
-      <c r="S103" s="1" t="s">
-        <v>349</v>
-      </c>
-      <c r="T103" s="1" t="s">
-        <v>639</v>
-      </c>
-    </row>
-    <row r="104" spans="1:20" x14ac:dyDescent="0.25">
+    </row>
+    <row r="104" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A104" s="5">
         <v>103</v>
       </c>
-      <c r="B104" s="17"/>
-      <c r="C104" s="22"/>
-      <c r="D104" s="22"/>
+      <c r="B104" s="19"/>
+      <c r="C104" s="11"/>
+      <c r="D104" s="11"/>
       <c r="E104" s="5" t="s">
-        <v>710</v>
+        <v>667</v>
       </c>
       <c r="F104" s="5" t="s">
         <v>105</v>
@@ -7211,29 +5897,16 @@
       <c r="K104" s="5"/>
       <c r="L104" s="5"/>
       <c r="M104" s="5"/>
-      <c r="N104" s="15"/>
-      <c r="Q104" s="1" t="s">
-        <v>710</v>
-      </c>
-      <c r="R104" s="1" t="s">
-        <v>105</v>
-      </c>
-      <c r="S104" s="1" t="s">
-        <v>350</v>
-      </c>
-      <c r="T104" s="1" t="s">
-        <v>639</v>
-      </c>
-    </row>
-    <row r="105" spans="1:20" x14ac:dyDescent="0.25">
+    </row>
+    <row r="105" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A105" s="5">
         <v>104</v>
       </c>
-      <c r="B105" s="17"/>
-      <c r="C105" s="22"/>
-      <c r="D105" s="22"/>
+      <c r="B105" s="19"/>
+      <c r="C105" s="11"/>
+      <c r="D105" s="11"/>
       <c r="E105" s="5" t="s">
-        <v>711</v>
+        <v>668</v>
       </c>
       <c r="F105" s="5" t="s">
         <v>106</v>
@@ -7251,31 +5924,18 @@
       <c r="K105" s="5"/>
       <c r="L105" s="5"/>
       <c r="M105" s="5"/>
-      <c r="N105" s="15"/>
-      <c r="Q105" s="1" t="s">
-        <v>711</v>
-      </c>
-      <c r="R105" s="1" t="s">
-        <v>106</v>
-      </c>
-      <c r="S105" s="1" t="s">
-        <v>351</v>
-      </c>
-      <c r="T105" s="1" t="s">
-        <v>639</v>
-      </c>
-    </row>
-    <row r="106" spans="1:20" x14ac:dyDescent="0.25">
+    </row>
+    <row r="106" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A106" s="6">
         <v>105</v>
       </c>
-      <c r="B106" s="17"/>
-      <c r="C106" s="22"/>
-      <c r="D106" s="22" t="s">
-        <v>903</v>
+      <c r="B106" s="19"/>
+      <c r="C106" s="11"/>
+      <c r="D106" s="11" t="s">
+        <v>841</v>
       </c>
       <c r="E106" s="6" t="s">
-        <v>712</v>
+        <v>669</v>
       </c>
       <c r="F106" s="6" t="s">
         <v>107</v>
@@ -7293,29 +5953,16 @@
       <c r="K106" s="6"/>
       <c r="L106" s="6"/>
       <c r="M106" s="6"/>
-      <c r="N106" s="15"/>
-      <c r="Q106" s="1" t="s">
-        <v>712</v>
-      </c>
-      <c r="R106" s="1" t="s">
-        <v>107</v>
-      </c>
-      <c r="S106" s="1" t="s">
-        <v>352</v>
-      </c>
-      <c r="T106" s="1" t="s">
-        <v>639</v>
-      </c>
-    </row>
-    <row r="107" spans="1:20" x14ac:dyDescent="0.25">
+    </row>
+    <row r="107" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A107" s="6">
         <v>106</v>
       </c>
-      <c r="B107" s="17"/>
-      <c r="C107" s="22"/>
-      <c r="D107" s="22"/>
+      <c r="B107" s="19"/>
+      <c r="C107" s="11"/>
+      <c r="D107" s="11"/>
       <c r="E107" s="6" t="s">
-        <v>713</v>
+        <v>670</v>
       </c>
       <c r="F107" s="6" t="s">
         <v>108</v>
@@ -7333,29 +5980,16 @@
       <c r="K107" s="6"/>
       <c r="L107" s="6"/>
       <c r="M107" s="6"/>
-      <c r="N107" s="15"/>
-      <c r="Q107" s="1" t="s">
-        <v>713</v>
-      </c>
-      <c r="R107" s="1" t="s">
-        <v>108</v>
-      </c>
-      <c r="S107" s="1" t="s">
-        <v>714</v>
-      </c>
-      <c r="T107" s="1" t="s">
-        <v>639</v>
-      </c>
-    </row>
-    <row r="108" spans="1:20" x14ac:dyDescent="0.25">
+    </row>
+    <row r="108" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A108" s="6">
         <v>107</v>
       </c>
-      <c r="B108" s="17"/>
-      <c r="C108" s="22"/>
-      <c r="D108" s="22"/>
+      <c r="B108" s="19"/>
+      <c r="C108" s="11"/>
+      <c r="D108" s="11"/>
       <c r="E108" s="6" t="s">
-        <v>715</v>
+        <v>671</v>
       </c>
       <c r="F108" s="6" t="s">
         <v>109</v>
@@ -7373,29 +6007,16 @@
       <c r="K108" s="6"/>
       <c r="L108" s="6"/>
       <c r="M108" s="6"/>
-      <c r="N108" s="15"/>
-      <c r="Q108" s="1" t="s">
-        <v>715</v>
-      </c>
-      <c r="R108" s="1" t="s">
-        <v>109</v>
-      </c>
-      <c r="S108" s="1" t="s">
-        <v>354</v>
-      </c>
-      <c r="T108" s="1" t="s">
-        <v>639</v>
-      </c>
-    </row>
-    <row r="109" spans="1:20" x14ac:dyDescent="0.25">
+    </row>
+    <row r="109" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A109" s="6">
         <v>108</v>
       </c>
-      <c r="B109" s="17"/>
-      <c r="C109" s="22"/>
-      <c r="D109" s="22"/>
+      <c r="B109" s="19"/>
+      <c r="C109" s="11"/>
+      <c r="D109" s="11"/>
       <c r="E109" s="6" t="s">
-        <v>716</v>
+        <v>672</v>
       </c>
       <c r="F109" s="6" t="s">
         <v>110</v>
@@ -7413,29 +6034,16 @@
       <c r="K109" s="6"/>
       <c r="L109" s="6"/>
       <c r="M109" s="6"/>
-      <c r="N109" s="15"/>
-      <c r="Q109" s="1" t="s">
-        <v>716</v>
-      </c>
-      <c r="R109" s="1" t="s">
-        <v>110</v>
-      </c>
-      <c r="S109" s="1" t="s">
-        <v>355</v>
-      </c>
-      <c r="T109" s="1" t="s">
-        <v>639</v>
-      </c>
-    </row>
-    <row r="110" spans="1:20" x14ac:dyDescent="0.25">
+    </row>
+    <row r="110" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A110" s="6">
         <v>109</v>
       </c>
-      <c r="B110" s="17"/>
-      <c r="C110" s="22"/>
-      <c r="D110" s="22"/>
+      <c r="B110" s="19"/>
+      <c r="C110" s="11"/>
+      <c r="D110" s="11"/>
       <c r="E110" s="6" t="s">
-        <v>717</v>
+        <v>673</v>
       </c>
       <c r="F110" s="6" t="s">
         <v>111</v>
@@ -7453,29 +6061,16 @@
       <c r="K110" s="6"/>
       <c r="L110" s="6"/>
       <c r="M110" s="6"/>
-      <c r="N110" s="15"/>
-      <c r="Q110" s="1" t="s">
-        <v>717</v>
-      </c>
-      <c r="R110" s="1" t="s">
-        <v>111</v>
-      </c>
-      <c r="S110" s="1" t="s">
-        <v>356</v>
-      </c>
-      <c r="T110" s="1" t="s">
-        <v>639</v>
-      </c>
-    </row>
-    <row r="111" spans="1:20" x14ac:dyDescent="0.25">
+    </row>
+    <row r="111" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A111" s="6">
         <v>110</v>
       </c>
-      <c r="B111" s="17"/>
-      <c r="C111" s="22"/>
-      <c r="D111" s="22"/>
+      <c r="B111" s="19"/>
+      <c r="C111" s="11"/>
+      <c r="D111" s="11"/>
       <c r="E111" s="6" t="s">
-        <v>718</v>
+        <v>674</v>
       </c>
       <c r="F111" s="6" t="s">
         <v>112</v>
@@ -7493,31 +6088,18 @@
       <c r="K111" s="6"/>
       <c r="L111" s="6"/>
       <c r="M111" s="6"/>
-      <c r="N111" s="15"/>
-      <c r="Q111" s="1" t="s">
-        <v>718</v>
-      </c>
-      <c r="R111" s="1" t="s">
-        <v>112</v>
-      </c>
-      <c r="S111" s="1" t="s">
-        <v>357</v>
-      </c>
-      <c r="T111" s="1" t="s">
-        <v>639</v>
-      </c>
-    </row>
-    <row r="112" spans="1:20" x14ac:dyDescent="0.25">
+    </row>
+    <row r="112" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A112" s="5">
         <v>111</v>
       </c>
-      <c r="B112" s="17"/>
-      <c r="C112" s="22"/>
-      <c r="D112" s="22" t="s">
-        <v>904</v>
+      <c r="B112" s="19"/>
+      <c r="C112" s="11"/>
+      <c r="D112" s="11" t="s">
+        <v>842</v>
       </c>
       <c r="E112" s="5" t="s">
-        <v>719</v>
+        <v>675</v>
       </c>
       <c r="F112" s="5" t="s">
         <v>113</v>
@@ -7535,29 +6117,16 @@
       <c r="K112" s="5"/>
       <c r="L112" s="5"/>
       <c r="M112" s="5"/>
-      <c r="N112" s="15"/>
-      <c r="Q112" s="1" t="s">
-        <v>719</v>
-      </c>
-      <c r="R112" s="1" t="s">
-        <v>113</v>
-      </c>
-      <c r="S112" s="1" t="s">
-        <v>720</v>
-      </c>
-      <c r="T112" s="1" t="s">
-        <v>639</v>
-      </c>
-    </row>
-    <row r="113" spans="1:20" x14ac:dyDescent="0.25">
+    </row>
+    <row r="113" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A113" s="5">
         <v>112</v>
       </c>
-      <c r="B113" s="17"/>
-      <c r="C113" s="22"/>
-      <c r="D113" s="22"/>
+      <c r="B113" s="19"/>
+      <c r="C113" s="11"/>
+      <c r="D113" s="11"/>
       <c r="E113" s="5" t="s">
-        <v>721</v>
+        <v>676</v>
       </c>
       <c r="F113" s="5" t="s">
         <v>114</v>
@@ -7575,29 +6144,16 @@
       <c r="K113" s="5"/>
       <c r="L113" s="5"/>
       <c r="M113" s="5"/>
-      <c r="N113" s="15"/>
-      <c r="Q113" s="1" t="s">
-        <v>721</v>
-      </c>
-      <c r="R113" s="1" t="s">
-        <v>114</v>
-      </c>
-      <c r="S113" s="1" t="s">
-        <v>722</v>
-      </c>
-      <c r="T113" s="1" t="s">
-        <v>639</v>
-      </c>
-    </row>
-    <row r="114" spans="1:20" x14ac:dyDescent="0.25">
+    </row>
+    <row r="114" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A114" s="5">
         <v>113</v>
       </c>
-      <c r="B114" s="17"/>
-      <c r="C114" s="22"/>
-      <c r="D114" s="22"/>
+      <c r="B114" s="19"/>
+      <c r="C114" s="11"/>
+      <c r="D114" s="11"/>
       <c r="E114" s="5" t="s">
-        <v>723</v>
+        <v>677</v>
       </c>
       <c r="F114" s="5" t="s">
         <v>115</v>
@@ -7615,29 +6171,16 @@
       <c r="K114" s="5"/>
       <c r="L114" s="5"/>
       <c r="M114" s="5"/>
-      <c r="N114" s="15"/>
-      <c r="Q114" s="1" t="s">
-        <v>723</v>
-      </c>
-      <c r="R114" s="1" t="s">
-        <v>115</v>
-      </c>
-      <c r="S114" s="1" t="s">
-        <v>724</v>
-      </c>
-      <c r="T114" s="1" t="s">
-        <v>639</v>
-      </c>
-    </row>
-    <row r="115" spans="1:20" x14ac:dyDescent="0.25">
+    </row>
+    <row r="115" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A115" s="5">
         <v>114</v>
       </c>
-      <c r="B115" s="17"/>
-      <c r="C115" s="22"/>
-      <c r="D115" s="22"/>
+      <c r="B115" s="19"/>
+      <c r="C115" s="11"/>
+      <c r="D115" s="11"/>
       <c r="E115" s="5" t="s">
-        <v>725</v>
+        <v>678</v>
       </c>
       <c r="F115" s="5" t="s">
         <v>116</v>
@@ -7655,33 +6198,20 @@
       <c r="K115" s="5"/>
       <c r="L115" s="5"/>
       <c r="M115" s="5"/>
-      <c r="N115" s="15"/>
-      <c r="Q115" s="1" t="s">
-        <v>725</v>
-      </c>
-      <c r="R115" s="1" t="s">
-        <v>116</v>
-      </c>
-      <c r="S115" s="1" t="s">
-        <v>726</v>
-      </c>
-      <c r="T115" s="1" t="s">
-        <v>639</v>
-      </c>
-    </row>
-    <row r="116" spans="1:20" x14ac:dyDescent="0.25">
+    </row>
+    <row r="116" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A116" s="6">
         <v>115</v>
       </c>
-      <c r="B116" s="17"/>
-      <c r="C116" s="22" t="s">
-        <v>905</v>
-      </c>
-      <c r="D116" s="22" t="s">
-        <v>906</v>
+      <c r="B116" s="19"/>
+      <c r="C116" s="11" t="s">
+        <v>843</v>
+      </c>
+      <c r="D116" s="11" t="s">
+        <v>844</v>
       </c>
       <c r="E116" s="6" t="s">
-        <v>727</v>
+        <v>679</v>
       </c>
       <c r="F116" s="6" t="s">
         <v>117</v>
@@ -7699,31 +6229,18 @@
       <c r="K116" s="6"/>
       <c r="L116" s="6"/>
       <c r="M116" s="6"/>
-      <c r="N116" s="15"/>
-      <c r="Q116" s="1" t="s">
-        <v>727</v>
-      </c>
-      <c r="R116" s="1" t="s">
-        <v>117</v>
-      </c>
-      <c r="S116" s="1" t="s">
-        <v>728</v>
-      </c>
-      <c r="T116" s="1" t="s">
-        <v>639</v>
-      </c>
-    </row>
-    <row r="117" spans="1:20" x14ac:dyDescent="0.25">
+    </row>
+    <row r="117" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A117" s="5">
         <v>116</v>
       </c>
-      <c r="B117" s="17"/>
-      <c r="C117" s="22"/>
-      <c r="D117" s="22" t="s">
-        <v>907</v>
+      <c r="B117" s="19"/>
+      <c r="C117" s="11"/>
+      <c r="D117" s="11" t="s">
+        <v>845</v>
       </c>
       <c r="E117" s="5" t="s">
-        <v>729</v>
+        <v>680</v>
       </c>
       <c r="F117" s="5" t="s">
         <v>118</v>
@@ -7741,29 +6258,16 @@
       <c r="K117" s="5"/>
       <c r="L117" s="5"/>
       <c r="M117" s="5"/>
-      <c r="N117" s="15"/>
-      <c r="Q117" s="1" t="s">
-        <v>729</v>
-      </c>
-      <c r="R117" s="1" t="s">
-        <v>118</v>
-      </c>
-      <c r="S117" s="1" t="s">
-        <v>730</v>
-      </c>
-      <c r="T117" s="1" t="s">
-        <v>639</v>
-      </c>
-    </row>
-    <row r="118" spans="1:20" x14ac:dyDescent="0.25">
+    </row>
+    <row r="118" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A118" s="5">
         <v>117</v>
       </c>
-      <c r="B118" s="17"/>
-      <c r="C118" s="22"/>
-      <c r="D118" s="22"/>
+      <c r="B118" s="19"/>
+      <c r="C118" s="11"/>
+      <c r="D118" s="11"/>
       <c r="E118" s="5" t="s">
-        <v>731</v>
+        <v>681</v>
       </c>
       <c r="F118" s="5" t="s">
         <v>119</v>
@@ -7781,29 +6285,16 @@
       <c r="K118" s="5"/>
       <c r="L118" s="5"/>
       <c r="M118" s="5"/>
-      <c r="N118" s="15"/>
-      <c r="Q118" s="1" t="s">
-        <v>731</v>
-      </c>
-      <c r="R118" s="1" t="s">
-        <v>119</v>
-      </c>
-      <c r="S118" s="1" t="s">
-        <v>732</v>
-      </c>
-      <c r="T118" s="1" t="s">
-        <v>639</v>
-      </c>
-    </row>
-    <row r="119" spans="1:20" x14ac:dyDescent="0.25">
+    </row>
+    <row r="119" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A119" s="5">
         <v>118</v>
       </c>
-      <c r="B119" s="17"/>
-      <c r="C119" s="22"/>
-      <c r="D119" s="22"/>
+      <c r="B119" s="19"/>
+      <c r="C119" s="11"/>
+      <c r="D119" s="11"/>
       <c r="E119" s="5" t="s">
-        <v>733</v>
+        <v>682</v>
       </c>
       <c r="F119" s="5" t="s">
         <v>120</v>
@@ -7821,29 +6312,16 @@
       <c r="K119" s="5"/>
       <c r="L119" s="5"/>
       <c r="M119" s="5"/>
-      <c r="N119" s="15"/>
-      <c r="Q119" s="1" t="s">
-        <v>733</v>
-      </c>
-      <c r="R119" s="1" t="s">
-        <v>120</v>
-      </c>
-      <c r="S119" s="1" t="s">
-        <v>734</v>
-      </c>
-      <c r="T119" s="1" t="s">
-        <v>639</v>
-      </c>
-    </row>
-    <row r="120" spans="1:20" x14ac:dyDescent="0.25">
+    </row>
+    <row r="120" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A120" s="5">
         <v>119</v>
       </c>
-      <c r="B120" s="17"/>
-      <c r="C120" s="22"/>
-      <c r="D120" s="22"/>
+      <c r="B120" s="19"/>
+      <c r="C120" s="11"/>
+      <c r="D120" s="11"/>
       <c r="E120" s="5" t="s">
-        <v>735</v>
+        <v>683</v>
       </c>
       <c r="F120" s="5" t="s">
         <v>121</v>
@@ -7861,33 +6339,20 @@
       <c r="K120" s="5"/>
       <c r="L120" s="5"/>
       <c r="M120" s="5"/>
-      <c r="N120" s="15"/>
-      <c r="Q120" s="1" t="s">
-        <v>735</v>
-      </c>
-      <c r="R120" s="1" t="s">
-        <v>121</v>
-      </c>
-      <c r="S120" s="1" t="s">
-        <v>736</v>
-      </c>
-      <c r="T120" s="1" t="s">
-        <v>639</v>
-      </c>
-    </row>
-    <row r="121" spans="1:20" x14ac:dyDescent="0.25">
+    </row>
+    <row r="121" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A121" s="6">
         <v>120</v>
       </c>
-      <c r="B121" s="17"/>
-      <c r="C121" s="22" t="s">
-        <v>908</v>
-      </c>
-      <c r="D121" s="22" t="s">
-        <v>908</v>
+      <c r="B121" s="19"/>
+      <c r="C121" s="11" t="s">
+        <v>846</v>
+      </c>
+      <c r="D121" s="11" t="s">
+        <v>846</v>
       </c>
       <c r="E121" s="6" t="s">
-        <v>737</v>
+        <v>684</v>
       </c>
       <c r="F121" s="6" t="s">
         <v>122</v>
@@ -7905,29 +6370,16 @@
       <c r="K121" s="6"/>
       <c r="L121" s="6"/>
       <c r="M121" s="6"/>
-      <c r="N121" s="15"/>
-      <c r="Q121" s="1" t="s">
-        <v>737</v>
-      </c>
-      <c r="R121" s="1" t="s">
-        <v>122</v>
-      </c>
-      <c r="S121" s="1" t="s">
-        <v>738</v>
-      </c>
-      <c r="T121" s="1" t="s">
-        <v>639</v>
-      </c>
-    </row>
-    <row r="122" spans="1:20" x14ac:dyDescent="0.25">
+    </row>
+    <row r="122" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A122" s="6">
         <v>121</v>
       </c>
-      <c r="B122" s="17"/>
-      <c r="C122" s="22"/>
-      <c r="D122" s="22"/>
+      <c r="B122" s="19"/>
+      <c r="C122" s="11"/>
+      <c r="D122" s="11"/>
       <c r="E122" s="6" t="s">
-        <v>739</v>
+        <v>685</v>
       </c>
       <c r="F122" s="6" t="s">
         <v>123</v>
@@ -7945,29 +6397,16 @@
       <c r="K122" s="6"/>
       <c r="L122" s="6"/>
       <c r="M122" s="6"/>
-      <c r="N122" s="15"/>
-      <c r="Q122" s="1" t="s">
-        <v>739</v>
-      </c>
-      <c r="R122" s="1" t="s">
-        <v>123</v>
-      </c>
-      <c r="S122" s="1" t="s">
-        <v>740</v>
-      </c>
-      <c r="T122" s="1" t="s">
-        <v>639</v>
-      </c>
-    </row>
-    <row r="123" spans="1:20" x14ac:dyDescent="0.25">
+    </row>
+    <row r="123" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A123" s="6">
         <v>122</v>
       </c>
-      <c r="B123" s="17"/>
-      <c r="C123" s="22"/>
-      <c r="D123" s="22"/>
+      <c r="B123" s="19"/>
+      <c r="C123" s="11"/>
+      <c r="D123" s="11"/>
       <c r="E123" s="6" t="s">
-        <v>741</v>
+        <v>686</v>
       </c>
       <c r="F123" s="6" t="s">
         <v>124</v>
@@ -7985,31 +6424,18 @@
       <c r="K123" s="6"/>
       <c r="L123" s="6"/>
       <c r="M123" s="6"/>
-      <c r="N123" s="15"/>
-      <c r="Q123" s="1" t="s">
-        <v>741</v>
-      </c>
-      <c r="R123" s="1" t="s">
-        <v>124</v>
-      </c>
-      <c r="S123" s="1" t="s">
-        <v>742</v>
-      </c>
-      <c r="T123" s="1" t="s">
-        <v>639</v>
-      </c>
-    </row>
-    <row r="124" spans="1:20" x14ac:dyDescent="0.25">
+    </row>
+    <row r="124" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A124" s="5">
         <v>123</v>
       </c>
-      <c r="B124" s="17"/>
-      <c r="C124" s="22" t="s">
-        <v>909</v>
-      </c>
-      <c r="D124" s="22"/>
+      <c r="B124" s="19"/>
+      <c r="C124" s="11" t="s">
+        <v>847</v>
+      </c>
+      <c r="D124" s="11"/>
       <c r="E124" s="5" t="s">
-        <v>743</v>
+        <v>687</v>
       </c>
       <c r="F124" s="5" t="s">
         <v>125</v>
@@ -8027,31 +6453,18 @@
       <c r="K124" s="5"/>
       <c r="L124" s="5"/>
       <c r="M124" s="5"/>
-      <c r="N124" s="15"/>
-      <c r="Q124" s="1" t="s">
-        <v>743</v>
-      </c>
-      <c r="R124" s="1" t="s">
-        <v>125</v>
-      </c>
-      <c r="S124" s="1" t="s">
-        <v>370</v>
-      </c>
-      <c r="T124" s="1" t="s">
-        <v>462</v>
-      </c>
-    </row>
-    <row r="125" spans="1:20" x14ac:dyDescent="0.25">
+    </row>
+    <row r="125" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A125" s="6">
         <v>124</v>
       </c>
-      <c r="B125" s="17"/>
-      <c r="C125" s="22" t="s">
-        <v>910</v>
-      </c>
-      <c r="D125" s="22"/>
+      <c r="B125" s="19"/>
+      <c r="C125" s="11" t="s">
+        <v>848</v>
+      </c>
+      <c r="D125" s="11"/>
       <c r="E125" s="6" t="s">
-        <v>744</v>
+        <v>688</v>
       </c>
       <c r="F125" s="6" t="s">
         <v>126</v>
@@ -8069,29 +6482,16 @@
       <c r="K125" s="6"/>
       <c r="L125" s="6"/>
       <c r="M125" s="6"/>
-      <c r="N125" s="15"/>
-      <c r="Q125" s="1" t="s">
-        <v>744</v>
-      </c>
-      <c r="R125" s="1" t="s">
-        <v>126</v>
-      </c>
-      <c r="S125" s="1" t="s">
-        <v>745</v>
-      </c>
-      <c r="T125" s="1" t="s">
-        <v>639</v>
-      </c>
-    </row>
-    <row r="126" spans="1:20" x14ac:dyDescent="0.25">
+    </row>
+    <row r="126" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A126" s="6">
         <v>125</v>
       </c>
-      <c r="B126" s="17"/>
-      <c r="C126" s="22"/>
-      <c r="D126" s="22"/>
+      <c r="B126" s="19"/>
+      <c r="C126" s="11"/>
+      <c r="D126" s="11"/>
       <c r="E126" s="6" t="s">
-        <v>746</v>
+        <v>689</v>
       </c>
       <c r="F126" s="6" t="s">
         <v>127</v>
@@ -8109,29 +6509,16 @@
       <c r="K126" s="6"/>
       <c r="L126" s="6"/>
       <c r="M126" s="6"/>
-      <c r="N126" s="15"/>
-      <c r="Q126" s="1" t="s">
-        <v>746</v>
-      </c>
-      <c r="R126" s="1" t="s">
-        <v>127</v>
-      </c>
-      <c r="S126" s="1" t="s">
-        <v>747</v>
-      </c>
-      <c r="T126" s="1" t="s">
-        <v>639</v>
-      </c>
-    </row>
-    <row r="127" spans="1:20" x14ac:dyDescent="0.25">
+    </row>
+    <row r="127" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A127" s="6">
         <v>126</v>
       </c>
-      <c r="B127" s="17"/>
-      <c r="C127" s="22"/>
-      <c r="D127" s="22"/>
+      <c r="B127" s="19"/>
+      <c r="C127" s="11"/>
+      <c r="D127" s="11"/>
       <c r="E127" s="6" t="s">
-        <v>748</v>
+        <v>690</v>
       </c>
       <c r="F127" s="6" t="s">
         <v>128</v>
@@ -8149,29 +6536,16 @@
       <c r="K127" s="6"/>
       <c r="L127" s="6"/>
       <c r="M127" s="6"/>
-      <c r="N127" s="15"/>
-      <c r="Q127" s="1" t="s">
-        <v>748</v>
-      </c>
-      <c r="R127" s="1" t="s">
-        <v>128</v>
-      </c>
-      <c r="S127" s="1" t="s">
-        <v>749</v>
-      </c>
-      <c r="T127" s="1" t="s">
-        <v>639</v>
-      </c>
-    </row>
-    <row r="128" spans="1:20" x14ac:dyDescent="0.25">
+    </row>
+    <row r="128" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A128" s="6">
         <v>127</v>
       </c>
-      <c r="B128" s="17"/>
-      <c r="C128" s="22"/>
-      <c r="D128" s="22"/>
+      <c r="B128" s="19"/>
+      <c r="C128" s="11"/>
+      <c r="D128" s="11"/>
       <c r="E128" s="6" t="s">
-        <v>750</v>
+        <v>691</v>
       </c>
       <c r="F128" s="6" t="s">
         <v>129</v>
@@ -8189,29 +6563,16 @@
       <c r="K128" s="6"/>
       <c r="L128" s="6"/>
       <c r="M128" s="6"/>
-      <c r="N128" s="15"/>
-      <c r="Q128" s="1" t="s">
-        <v>750</v>
-      </c>
-      <c r="R128" s="1" t="s">
-        <v>129</v>
-      </c>
-      <c r="S128" s="1" t="s">
-        <v>751</v>
-      </c>
-      <c r="T128" s="1" t="s">
-        <v>639</v>
-      </c>
-    </row>
-    <row r="129" spans="1:20" x14ac:dyDescent="0.25">
+    </row>
+    <row r="129" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A129" s="6">
         <v>128</v>
       </c>
-      <c r="B129" s="17"/>
-      <c r="C129" s="22"/>
-      <c r="D129" s="22"/>
+      <c r="B129" s="19"/>
+      <c r="C129" s="11"/>
+      <c r="D129" s="11"/>
       <c r="E129" s="6" t="s">
-        <v>752</v>
+        <v>692</v>
       </c>
       <c r="F129" s="6" t="s">
         <v>130</v>
@@ -8229,31 +6590,18 @@
       <c r="K129" s="6"/>
       <c r="L129" s="6"/>
       <c r="M129" s="6"/>
-      <c r="N129" s="15"/>
-      <c r="Q129" s="1" t="s">
-        <v>752</v>
-      </c>
-      <c r="R129" s="1" t="s">
-        <v>130</v>
-      </c>
-      <c r="S129" s="1" t="s">
-        <v>753</v>
-      </c>
-      <c r="T129" s="1" t="s">
-        <v>639</v>
-      </c>
-    </row>
-    <row r="130" spans="1:20" x14ac:dyDescent="0.25">
+    </row>
+    <row r="130" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A130" s="5">
         <v>129</v>
       </c>
-      <c r="B130" s="17"/>
-      <c r="C130" s="22" t="s">
-        <v>911</v>
-      </c>
-      <c r="D130" s="22"/>
+      <c r="B130" s="19"/>
+      <c r="C130" s="11" t="s">
+        <v>849</v>
+      </c>
+      <c r="D130" s="11"/>
       <c r="E130" s="5" t="s">
-        <v>754</v>
+        <v>693</v>
       </c>
       <c r="F130" s="5" t="s">
         <v>131</v>
@@ -8271,27 +6619,16 @@
       <c r="K130" s="5"/>
       <c r="L130" s="5"/>
       <c r="M130" s="5"/>
-      <c r="N130" s="15"/>
-      <c r="Q130" s="1" t="s">
-        <v>754</v>
-      </c>
-      <c r="R130" s="1" t="s">
-        <v>374</v>
-      </c>
-      <c r="S130" s="1"/>
-      <c r="T130" s="1" t="s">
-        <v>639</v>
-      </c>
-    </row>
-    <row r="131" spans="1:20" x14ac:dyDescent="0.25">
+    </row>
+    <row r="131" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A131" s="5">
         <v>130</v>
       </c>
-      <c r="B131" s="17"/>
-      <c r="C131" s="22"/>
-      <c r="D131" s="22"/>
+      <c r="B131" s="19"/>
+      <c r="C131" s="11"/>
+      <c r="D131" s="11"/>
       <c r="E131" s="5" t="s">
-        <v>755</v>
+        <v>694</v>
       </c>
       <c r="F131" s="5" t="s">
         <v>132</v>
@@ -8309,27 +6646,16 @@
       <c r="K131" s="5"/>
       <c r="L131" s="5"/>
       <c r="M131" s="5"/>
-      <c r="N131" s="15"/>
-      <c r="Q131" s="1" t="s">
-        <v>755</v>
-      </c>
-      <c r="R131" s="1" t="s">
-        <v>375</v>
-      </c>
-      <c r="S131" s="1"/>
-      <c r="T131" s="1" t="s">
-        <v>639</v>
-      </c>
-    </row>
-    <row r="132" spans="1:20" x14ac:dyDescent="0.25">
+    </row>
+    <row r="132" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A132" s="5">
         <v>131</v>
       </c>
-      <c r="B132" s="17"/>
-      <c r="C132" s="22"/>
-      <c r="D132" s="22"/>
+      <c r="B132" s="19"/>
+      <c r="C132" s="11"/>
+      <c r="D132" s="11"/>
       <c r="E132" s="5" t="s">
-        <v>756</v>
+        <v>695</v>
       </c>
       <c r="F132" s="5" t="s">
         <v>133</v>
@@ -8347,23 +6673,16 @@
       <c r="K132" s="5"/>
       <c r="L132" s="5"/>
       <c r="M132" s="5"/>
-      <c r="N132" s="15"/>
-      <c r="Q132" s="1" t="s">
-        <v>756</v>
-      </c>
-      <c r="R132" s="1" t="s">
-        <v>376</v>
-      </c>
-    </row>
-    <row r="133" spans="1:20" x14ac:dyDescent="0.25">
+    </row>
+    <row r="133" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A133" s="5">
         <v>132</v>
       </c>
-      <c r="B133" s="17"/>
-      <c r="C133" s="22"/>
-      <c r="D133" s="22"/>
+      <c r="B133" s="19"/>
+      <c r="C133" s="11"/>
+      <c r="D133" s="11"/>
       <c r="E133" s="5" t="s">
-        <v>757</v>
+        <v>696</v>
       </c>
       <c r="F133" s="5" t="s">
         <v>134</v>
@@ -8381,23 +6700,16 @@
       <c r="K133" s="5"/>
       <c r="L133" s="5"/>
       <c r="M133" s="5"/>
-      <c r="N133" s="15"/>
-      <c r="Q133" s="1" t="s">
-        <v>757</v>
-      </c>
-      <c r="R133" s="1" t="s">
-        <v>377</v>
-      </c>
-    </row>
-    <row r="134" spans="1:20" x14ac:dyDescent="0.25">
+    </row>
+    <row r="134" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A134" s="5">
         <v>133</v>
       </c>
-      <c r="B134" s="17"/>
-      <c r="C134" s="22"/>
-      <c r="D134" s="22"/>
+      <c r="B134" s="19"/>
+      <c r="C134" s="11"/>
+      <c r="D134" s="11"/>
       <c r="E134" s="5" t="s">
-        <v>758</v>
+        <v>697</v>
       </c>
       <c r="F134" s="5" t="s">
         <v>135</v>
@@ -8415,23 +6727,16 @@
       <c r="K134" s="5"/>
       <c r="L134" s="5"/>
       <c r="M134" s="5"/>
-      <c r="N134" s="15"/>
-      <c r="Q134" s="1" t="s">
-        <v>758</v>
-      </c>
-      <c r="R134" s="1" t="s">
-        <v>378</v>
-      </c>
-    </row>
-    <row r="135" spans="1:20" x14ac:dyDescent="0.25">
+    </row>
+    <row r="135" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A135" s="5">
         <v>134</v>
       </c>
-      <c r="B135" s="17"/>
-      <c r="C135" s="22"/>
-      <c r="D135" s="22"/>
+      <c r="B135" s="19"/>
+      <c r="C135" s="11"/>
+      <c r="D135" s="11"/>
       <c r="E135" s="5" t="s">
-        <v>759</v>
+        <v>698</v>
       </c>
       <c r="F135" s="5" t="s">
         <v>136</v>
@@ -8449,23 +6754,16 @@
       <c r="K135" s="5"/>
       <c r="L135" s="5"/>
       <c r="M135" s="5"/>
-      <c r="N135" s="15"/>
-      <c r="Q135" s="1" t="s">
-        <v>759</v>
-      </c>
-      <c r="R135" s="1" t="s">
-        <v>379</v>
-      </c>
-    </row>
-    <row r="136" spans="1:20" x14ac:dyDescent="0.25">
+    </row>
+    <row r="136" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A136" s="5">
         <v>135</v>
       </c>
-      <c r="B136" s="17"/>
-      <c r="C136" s="22"/>
-      <c r="D136" s="22"/>
+      <c r="B136" s="19"/>
+      <c r="C136" s="11"/>
+      <c r="D136" s="11"/>
       <c r="E136" s="5" t="s">
-        <v>760</v>
+        <v>699</v>
       </c>
       <c r="F136" s="5" t="s">
         <v>137</v>
@@ -8483,23 +6781,16 @@
       <c r="K136" s="5"/>
       <c r="L136" s="5"/>
       <c r="M136" s="5"/>
-      <c r="N136" s="15"/>
-      <c r="Q136" s="1" t="s">
-        <v>760</v>
-      </c>
-      <c r="R136" s="1" t="s">
-        <v>380</v>
-      </c>
-    </row>
-    <row r="137" spans="1:20" x14ac:dyDescent="0.25">
+    </row>
+    <row r="137" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A137" s="5">
         <v>136</v>
       </c>
-      <c r="B137" s="17"/>
-      <c r="C137" s="22"/>
-      <c r="D137" s="22"/>
+      <c r="B137" s="19"/>
+      <c r="C137" s="11"/>
+      <c r="D137" s="11"/>
       <c r="E137" s="5" t="s">
-        <v>761</v>
+        <v>700</v>
       </c>
       <c r="F137" s="5" t="s">
         <v>138</v>
@@ -8517,23 +6808,16 @@
       <c r="K137" s="5"/>
       <c r="L137" s="5"/>
       <c r="M137" s="5"/>
-      <c r="N137" s="15"/>
-      <c r="Q137" s="1" t="s">
-        <v>761</v>
-      </c>
-      <c r="R137" s="1" t="s">
-        <v>381</v>
-      </c>
-    </row>
-    <row r="138" spans="1:20" x14ac:dyDescent="0.25">
+    </row>
+    <row r="138" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A138" s="6">
         <v>137</v>
       </c>
-      <c r="B138" s="17"/>
-      <c r="C138" s="22"/>
-      <c r="D138" s="22"/>
+      <c r="B138" s="19"/>
+      <c r="C138" s="11"/>
+      <c r="D138" s="11"/>
       <c r="E138" s="6" t="s">
-        <v>762</v>
+        <v>701</v>
       </c>
       <c r="F138" s="6" t="s">
         <v>139</v>
@@ -8551,23 +6835,16 @@
       <c r="K138" s="6"/>
       <c r="L138" s="6"/>
       <c r="M138" s="6"/>
-      <c r="N138" s="15"/>
-      <c r="Q138" s="1" t="s">
-        <v>762</v>
-      </c>
-      <c r="R138" s="1" t="s">
-        <v>382</v>
-      </c>
-    </row>
-    <row r="139" spans="1:20" x14ac:dyDescent="0.25">
+    </row>
+    <row r="139" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A139" s="6">
         <v>138</v>
       </c>
-      <c r="B139" s="17"/>
-      <c r="C139" s="22"/>
-      <c r="D139" s="22"/>
+      <c r="B139" s="19"/>
+      <c r="C139" s="11"/>
+      <c r="D139" s="11"/>
       <c r="E139" s="6" t="s">
-        <v>763</v>
+        <v>702</v>
       </c>
       <c r="F139" s="6" t="s">
         <v>140</v>
@@ -8585,23 +6862,16 @@
       <c r="K139" s="6"/>
       <c r="L139" s="6"/>
       <c r="M139" s="6"/>
-      <c r="N139" s="15"/>
-      <c r="Q139" s="1" t="s">
-        <v>763</v>
-      </c>
-      <c r="R139" s="1" t="s">
-        <v>383</v>
-      </c>
-    </row>
-    <row r="140" spans="1:20" x14ac:dyDescent="0.25">
+    </row>
+    <row r="140" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A140" s="6">
         <v>139</v>
       </c>
-      <c r="B140" s="17"/>
-      <c r="C140" s="22"/>
-      <c r="D140" s="22"/>
+      <c r="B140" s="19"/>
+      <c r="C140" s="11"/>
+      <c r="D140" s="11"/>
       <c r="E140" s="6" t="s">
-        <v>764</v>
+        <v>703</v>
       </c>
       <c r="F140" s="6" t="s">
         <v>141</v>
@@ -8619,23 +6889,16 @@
       <c r="K140" s="6"/>
       <c r="L140" s="6"/>
       <c r="M140" s="6"/>
-      <c r="N140" s="15"/>
-      <c r="Q140" s="1" t="s">
-        <v>764</v>
-      </c>
-      <c r="R140" s="1" t="s">
-        <v>384</v>
-      </c>
-    </row>
-    <row r="141" spans="1:20" x14ac:dyDescent="0.25">
+    </row>
+    <row r="141" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A141" s="6">
         <v>140</v>
       </c>
-      <c r="B141" s="17"/>
-      <c r="C141" s="22"/>
-      <c r="D141" s="22"/>
+      <c r="B141" s="19"/>
+      <c r="C141" s="11"/>
+      <c r="D141" s="11"/>
       <c r="E141" s="6" t="s">
-        <v>765</v>
+        <v>704</v>
       </c>
       <c r="F141" s="6" t="s">
         <v>142</v>
@@ -8653,23 +6916,16 @@
       <c r="K141" s="6"/>
       <c r="L141" s="6"/>
       <c r="M141" s="6"/>
-      <c r="N141" s="15"/>
-      <c r="Q141" s="1" t="s">
-        <v>765</v>
-      </c>
-      <c r="R141" s="1" t="s">
-        <v>385</v>
-      </c>
-    </row>
-    <row r="142" spans="1:20" x14ac:dyDescent="0.25">
+    </row>
+    <row r="142" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A142" s="6">
         <v>141</v>
       </c>
-      <c r="B142" s="17"/>
-      <c r="C142" s="22"/>
-      <c r="D142" s="22"/>
+      <c r="B142" s="19"/>
+      <c r="C142" s="11"/>
+      <c r="D142" s="11"/>
       <c r="E142" s="6" t="s">
-        <v>766</v>
+        <v>705</v>
       </c>
       <c r="F142" s="6" t="s">
         <v>143</v>
@@ -8687,23 +6943,16 @@
       <c r="K142" s="6"/>
       <c r="L142" s="6"/>
       <c r="M142" s="6"/>
-      <c r="N142" s="15"/>
-      <c r="Q142" s="1" t="s">
-        <v>766</v>
-      </c>
-      <c r="R142" s="1" t="s">
-        <v>386</v>
-      </c>
-    </row>
-    <row r="143" spans="1:20" x14ac:dyDescent="0.25">
+    </row>
+    <row r="143" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A143" s="6">
         <v>142</v>
       </c>
-      <c r="B143" s="17"/>
-      <c r="C143" s="22"/>
-      <c r="D143" s="22"/>
+      <c r="B143" s="19"/>
+      <c r="C143" s="11"/>
+      <c r="D143" s="11"/>
       <c r="E143" s="6" t="s">
-        <v>767</v>
+        <v>706</v>
       </c>
       <c r="F143" s="6" t="s">
         <v>144</v>
@@ -8721,23 +6970,16 @@
       <c r="K143" s="6"/>
       <c r="L143" s="6"/>
       <c r="M143" s="6"/>
-      <c r="N143" s="15"/>
-      <c r="Q143" s="1" t="s">
-        <v>767</v>
-      </c>
-      <c r="R143" s="1" t="s">
-        <v>387</v>
-      </c>
-    </row>
-    <row r="144" spans="1:20" x14ac:dyDescent="0.25">
+    </row>
+    <row r="144" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A144" s="5">
         <v>143</v>
       </c>
-      <c r="B144" s="17"/>
-      <c r="C144" s="22"/>
-      <c r="D144" s="22"/>
+      <c r="B144" s="19"/>
+      <c r="C144" s="11"/>
+      <c r="D144" s="11"/>
       <c r="E144" s="5" t="s">
-        <v>768</v>
+        <v>707</v>
       </c>
       <c r="F144" s="5" t="s">
         <v>145</v>
@@ -8755,23 +6997,16 @@
       <c r="K144" s="5"/>
       <c r="L144" s="5"/>
       <c r="M144" s="5"/>
-      <c r="N144" s="15"/>
-      <c r="Q144" s="1" t="s">
-        <v>768</v>
-      </c>
-      <c r="R144" s="1" t="s">
-        <v>388</v>
-      </c>
-    </row>
-    <row r="145" spans="1:18" x14ac:dyDescent="0.25">
+    </row>
+    <row r="145" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A145" s="5">
         <v>144</v>
       </c>
-      <c r="B145" s="17"/>
-      <c r="C145" s="22"/>
-      <c r="D145" s="22"/>
+      <c r="B145" s="19"/>
+      <c r="C145" s="11"/>
+      <c r="D145" s="11"/>
       <c r="E145" s="5" t="s">
-        <v>769</v>
+        <v>708</v>
       </c>
       <c r="F145" s="5" t="s">
         <v>146</v>
@@ -8789,25 +7024,18 @@
       <c r="K145" s="5"/>
       <c r="L145" s="5"/>
       <c r="M145" s="5"/>
-      <c r="N145" s="15"/>
-      <c r="Q145" s="1" t="s">
-        <v>769</v>
-      </c>
-      <c r="R145" s="1" t="s">
-        <v>389</v>
-      </c>
-    </row>
-    <row r="146" spans="1:18" x14ac:dyDescent="0.25">
+    </row>
+    <row r="146" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A146" s="6">
         <v>145</v>
       </c>
-      <c r="B146" s="17"/>
-      <c r="C146" s="22" t="s">
-        <v>912</v>
-      </c>
-      <c r="D146" s="22"/>
+      <c r="B146" s="19"/>
+      <c r="C146" s="11" t="s">
+        <v>850</v>
+      </c>
+      <c r="D146" s="11"/>
       <c r="E146" s="6" t="s">
-        <v>770</v>
+        <v>709</v>
       </c>
       <c r="F146" s="6" t="s">
         <v>147</v>
@@ -8825,25 +7053,18 @@
       <c r="K146" s="6"/>
       <c r="L146" s="6"/>
       <c r="M146" s="6"/>
-      <c r="N146" s="15"/>
-      <c r="Q146" s="1" t="s">
-        <v>770</v>
-      </c>
-      <c r="R146" s="1" t="s">
-        <v>390</v>
-      </c>
-    </row>
-    <row r="147" spans="1:18" x14ac:dyDescent="0.25">
+    </row>
+    <row r="147" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A147" s="5">
         <v>146</v>
       </c>
-      <c r="B147" s="17"/>
-      <c r="C147" s="22" t="s">
-        <v>913</v>
-      </c>
-      <c r="D147" s="22"/>
+      <c r="B147" s="19"/>
+      <c r="C147" s="11" t="s">
+        <v>851</v>
+      </c>
+      <c r="D147" s="11"/>
       <c r="E147" s="5" t="s">
-        <v>771</v>
+        <v>710</v>
       </c>
       <c r="F147" s="5" t="s">
         <v>148</v>
@@ -8861,23 +7082,16 @@
       <c r="K147" s="5"/>
       <c r="L147" s="5"/>
       <c r="M147" s="5"/>
-      <c r="N147" s="15"/>
-      <c r="Q147" s="1" t="s">
-        <v>771</v>
-      </c>
-      <c r="R147" s="1" t="s">
-        <v>391</v>
-      </c>
-    </row>
-    <row r="148" spans="1:18" x14ac:dyDescent="0.25">
+    </row>
+    <row r="148" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A148" s="5">
         <v>147</v>
       </c>
-      <c r="B148" s="17"/>
-      <c r="C148" s="22"/>
-      <c r="D148" s="22"/>
+      <c r="B148" s="19"/>
+      <c r="C148" s="11"/>
+      <c r="D148" s="11"/>
       <c r="E148" s="5" t="s">
-        <v>772</v>
+        <v>711</v>
       </c>
       <c r="F148" s="5" t="s">
         <v>149</v>
@@ -8895,23 +7109,16 @@
       <c r="K148" s="5"/>
       <c r="L148" s="5"/>
       <c r="M148" s="5"/>
-      <c r="N148" s="15"/>
-      <c r="Q148" s="1" t="s">
-        <v>772</v>
-      </c>
-      <c r="R148" s="1" t="s">
-        <v>392</v>
-      </c>
-    </row>
-    <row r="149" spans="1:18" x14ac:dyDescent="0.25">
+    </row>
+    <row r="149" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A149" s="5">
         <v>148</v>
       </c>
-      <c r="B149" s="17"/>
-      <c r="C149" s="22"/>
-      <c r="D149" s="22"/>
+      <c r="B149" s="19"/>
+      <c r="C149" s="11"/>
+      <c r="D149" s="11"/>
       <c r="E149" s="5" t="s">
-        <v>773</v>
+        <v>712</v>
       </c>
       <c r="F149" s="5" t="s">
         <v>150</v>
@@ -8929,23 +7136,16 @@
       <c r="K149" s="5"/>
       <c r="L149" s="5"/>
       <c r="M149" s="5"/>
-      <c r="N149" s="15"/>
-      <c r="Q149" s="1" t="s">
-        <v>773</v>
-      </c>
-      <c r="R149" s="1" t="s">
-        <v>393</v>
-      </c>
-    </row>
-    <row r="150" spans="1:18" x14ac:dyDescent="0.25">
+    </row>
+    <row r="150" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A150" s="5">
         <v>149</v>
       </c>
-      <c r="B150" s="17"/>
-      <c r="C150" s="22"/>
-      <c r="D150" s="22"/>
+      <c r="B150" s="19"/>
+      <c r="C150" s="11"/>
+      <c r="D150" s="11"/>
       <c r="E150" s="5" t="s">
-        <v>774</v>
+        <v>713</v>
       </c>
       <c r="F150" s="5" t="s">
         <v>151</v>
@@ -8963,23 +7163,16 @@
       <c r="K150" s="5"/>
       <c r="L150" s="5"/>
       <c r="M150" s="5"/>
-      <c r="N150" s="15"/>
-      <c r="Q150" s="1" t="s">
-        <v>774</v>
-      </c>
-      <c r="R150" s="1" t="s">
-        <v>394</v>
-      </c>
-    </row>
-    <row r="151" spans="1:18" x14ac:dyDescent="0.25">
+    </row>
+    <row r="151" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A151" s="5">
         <v>150</v>
       </c>
-      <c r="B151" s="17"/>
-      <c r="C151" s="22"/>
-      <c r="D151" s="22"/>
+      <c r="B151" s="19"/>
+      <c r="C151" s="11"/>
+      <c r="D151" s="11"/>
       <c r="E151" s="5" t="s">
-        <v>775</v>
+        <v>714</v>
       </c>
       <c r="F151" s="5" t="s">
         <v>152</v>
@@ -8997,23 +7190,16 @@
       <c r="K151" s="5"/>
       <c r="L151" s="5"/>
       <c r="M151" s="5"/>
-      <c r="N151" s="15"/>
-      <c r="Q151" s="1" t="s">
-        <v>775</v>
-      </c>
-      <c r="R151" s="1" t="s">
-        <v>395</v>
-      </c>
-    </row>
-    <row r="152" spans="1:18" x14ac:dyDescent="0.25">
+    </row>
+    <row r="152" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A152" s="5">
         <v>151</v>
       </c>
-      <c r="B152" s="17"/>
-      <c r="C152" s="22"/>
-      <c r="D152" s="22"/>
+      <c r="B152" s="19"/>
+      <c r="C152" s="11"/>
+      <c r="D152" s="11"/>
       <c r="E152" s="5" t="s">
-        <v>776</v>
+        <v>715</v>
       </c>
       <c r="F152" s="5" t="s">
         <v>153</v>
@@ -9031,23 +7217,16 @@
       <c r="K152" s="5"/>
       <c r="L152" s="5"/>
       <c r="M152" s="5"/>
-      <c r="N152" s="15"/>
-      <c r="Q152" s="1" t="s">
-        <v>776</v>
-      </c>
-      <c r="R152" s="1" t="s">
-        <v>396</v>
-      </c>
-    </row>
-    <row r="153" spans="1:18" x14ac:dyDescent="0.25">
+    </row>
+    <row r="153" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A153" s="5">
         <v>152</v>
       </c>
-      <c r="B153" s="17"/>
-      <c r="C153" s="22"/>
-      <c r="D153" s="22"/>
+      <c r="B153" s="19"/>
+      <c r="C153" s="11"/>
+      <c r="D153" s="11"/>
       <c r="E153" s="5" t="s">
-        <v>777</v>
+        <v>716</v>
       </c>
       <c r="F153" s="5" t="s">
         <v>154</v>
@@ -9065,23 +7244,16 @@
       <c r="K153" s="5"/>
       <c r="L153" s="5"/>
       <c r="M153" s="5"/>
-      <c r="N153" s="15"/>
-      <c r="Q153" s="1" t="s">
-        <v>777</v>
-      </c>
-      <c r="R153" s="1" t="s">
-        <v>397</v>
-      </c>
-    </row>
-    <row r="154" spans="1:18" x14ac:dyDescent="0.25">
+    </row>
+    <row r="154" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A154" s="5">
         <v>153</v>
       </c>
-      <c r="B154" s="17"/>
-      <c r="C154" s="22"/>
-      <c r="D154" s="22"/>
+      <c r="B154" s="19"/>
+      <c r="C154" s="11"/>
+      <c r="D154" s="11"/>
       <c r="E154" s="5" t="s">
-        <v>778</v>
+        <v>717</v>
       </c>
       <c r="F154" s="5" t="s">
         <v>155</v>
@@ -9099,25 +7271,18 @@
       <c r="K154" s="5"/>
       <c r="L154" s="5"/>
       <c r="M154" s="5"/>
-      <c r="N154" s="15"/>
-      <c r="Q154" s="1" t="s">
-        <v>778</v>
-      </c>
-      <c r="R154" s="1" t="s">
-        <v>398</v>
-      </c>
-    </row>
-    <row r="155" spans="1:18" x14ac:dyDescent="0.25">
+    </row>
+    <row r="155" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A155" s="6">
         <v>154</v>
       </c>
-      <c r="B155" s="17"/>
-      <c r="C155" s="22" t="s">
-        <v>914</v>
-      </c>
-      <c r="D155" s="22"/>
+      <c r="B155" s="19"/>
+      <c r="C155" s="11" t="s">
+        <v>852</v>
+      </c>
+      <c r="D155" s="11"/>
       <c r="E155" s="6" t="s">
-        <v>685</v>
+        <v>652</v>
       </c>
       <c r="F155" s="6" t="s">
         <v>156</v>
@@ -9135,20 +7300,18 @@
       <c r="K155" s="6"/>
       <c r="L155" s="6"/>
       <c r="M155" s="6"/>
-      <c r="N155" s="15"/>
-      <c r="R155" s="1"/>
-    </row>
-    <row r="156" spans="1:18" x14ac:dyDescent="0.25">
+    </row>
+    <row r="156" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A156" s="5">
         <v>155</v>
       </c>
-      <c r="B156" s="17"/>
-      <c r="C156" s="22" t="s">
-        <v>915</v>
-      </c>
-      <c r="D156" s="22"/>
+      <c r="B156" s="19"/>
+      <c r="C156" s="11" t="s">
+        <v>853</v>
+      </c>
+      <c r="D156" s="11"/>
       <c r="E156" s="5" t="s">
-        <v>686</v>
+        <v>653</v>
       </c>
       <c r="F156" s="5" t="s">
         <v>157</v>
@@ -9166,26 +7329,18 @@
       <c r="K156" s="5"/>
       <c r="L156" s="5"/>
       <c r="M156" s="5"/>
-      <c r="N156" s="15"/>
-      <c r="P156" s="1" t="s">
-        <v>779</v>
-      </c>
-      <c r="Q156" s="1" t="s">
-        <v>607</v>
-      </c>
-      <c r="R156" s="1"/>
-    </row>
-    <row r="157" spans="1:18" x14ac:dyDescent="0.25">
+    </row>
+    <row r="157" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A157" s="7">
         <v>156</v>
       </c>
-      <c r="B157" s="18" t="s">
+      <c r="B157" s="20" t="s">
         <v>567</v>
       </c>
-      <c r="C157" s="23"/>
-      <c r="D157" s="23"/>
+      <c r="C157" s="12"/>
+      <c r="D157" s="12"/>
       <c r="E157" s="7" t="s">
-        <v>780</v>
+        <v>718</v>
       </c>
       <c r="F157" s="7" t="s">
         <v>158</v>
@@ -9203,24 +7358,16 @@
       <c r="K157" s="7"/>
       <c r="L157" s="7"/>
       <c r="M157" s="7"/>
-      <c r="N157" s="15"/>
-      <c r="P157" s="1" t="s">
-        <v>158</v>
-      </c>
-      <c r="Q157" s="1" t="s">
-        <v>780</v>
-      </c>
-      <c r="R157" s="1"/>
-    </row>
-    <row r="158" spans="1:18" x14ac:dyDescent="0.25">
+    </row>
+    <row r="158" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A158" s="7">
         <v>157</v>
       </c>
-      <c r="B158" s="18"/>
-      <c r="C158" s="23"/>
-      <c r="D158" s="23"/>
+      <c r="B158" s="20"/>
+      <c r="C158" s="12"/>
+      <c r="D158" s="12"/>
       <c r="E158" s="7" t="s">
-        <v>781</v>
+        <v>719</v>
       </c>
       <c r="F158" s="7" t="s">
         <v>159</v>
@@ -9238,24 +7385,16 @@
       <c r="K158" s="7"/>
       <c r="L158" s="7"/>
       <c r="M158" s="7"/>
-      <c r="N158" s="15"/>
-      <c r="P158" s="1" t="s">
-        <v>159</v>
-      </c>
-      <c r="Q158" s="1" t="s">
-        <v>781</v>
-      </c>
-      <c r="R158" s="1"/>
-    </row>
-    <row r="159" spans="1:18" x14ac:dyDescent="0.25">
+    </row>
+    <row r="159" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A159" s="7">
         <v>158</v>
       </c>
-      <c r="B159" s="18"/>
-      <c r="C159" s="23"/>
-      <c r="D159" s="23"/>
+      <c r="B159" s="20"/>
+      <c r="C159" s="12"/>
+      <c r="D159" s="12"/>
       <c r="E159" s="7" t="s">
-        <v>782</v>
+        <v>720</v>
       </c>
       <c r="F159" s="7" t="s">
         <v>160</v>
@@ -9273,24 +7412,16 @@
       <c r="K159" s="7"/>
       <c r="L159" s="7"/>
       <c r="M159" s="7"/>
-      <c r="N159" s="15"/>
-      <c r="P159" s="1" t="s">
-        <v>160</v>
-      </c>
-      <c r="Q159" s="1" t="s">
-        <v>782</v>
-      </c>
-      <c r="R159" s="1"/>
-    </row>
-    <row r="160" spans="1:18" x14ac:dyDescent="0.25">
+    </row>
+    <row r="160" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A160" s="7">
         <v>159</v>
       </c>
-      <c r="B160" s="18"/>
-      <c r="C160" s="23"/>
-      <c r="D160" s="23"/>
+      <c r="B160" s="20"/>
+      <c r="C160" s="12"/>
+      <c r="D160" s="12"/>
       <c r="E160" s="7" t="s">
-        <v>783</v>
+        <v>721</v>
       </c>
       <c r="F160" s="7" t="s">
         <v>161</v>
@@ -9308,24 +7439,16 @@
       <c r="K160" s="7"/>
       <c r="L160" s="7"/>
       <c r="M160" s="7"/>
-      <c r="N160" s="15"/>
-      <c r="P160" s="1" t="s">
-        <v>161</v>
-      </c>
-      <c r="Q160" s="1" t="s">
-        <v>783</v>
-      </c>
-      <c r="R160" s="1"/>
-    </row>
-    <row r="161" spans="1:17" x14ac:dyDescent="0.25">
+    </row>
+    <row r="161" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A161" s="7">
         <v>160</v>
       </c>
-      <c r="B161" s="18"/>
-      <c r="C161" s="23"/>
-      <c r="D161" s="23"/>
+      <c r="B161" s="20"/>
+      <c r="C161" s="12"/>
+      <c r="D161" s="12"/>
       <c r="E161" s="7" t="s">
-        <v>784</v>
+        <v>722</v>
       </c>
       <c r="F161" s="7" t="s">
         <v>162</v>
@@ -9343,23 +7466,16 @@
       <c r="K161" s="7"/>
       <c r="L161" s="7"/>
       <c r="M161" s="7"/>
-      <c r="N161" s="15"/>
-      <c r="P161" s="1" t="s">
-        <v>162</v>
-      </c>
-      <c r="Q161" s="1" t="s">
-        <v>784</v>
-      </c>
-    </row>
-    <row r="162" spans="1:17" x14ac:dyDescent="0.25">
+    </row>
+    <row r="162" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A162" s="7">
         <v>161</v>
       </c>
-      <c r="B162" s="18"/>
-      <c r="C162" s="23"/>
-      <c r="D162" s="23"/>
+      <c r="B162" s="20"/>
+      <c r="C162" s="12"/>
+      <c r="D162" s="12"/>
       <c r="E162" s="7" t="s">
-        <v>785</v>
+        <v>723</v>
       </c>
       <c r="F162" s="7" t="s">
         <v>163</v>
@@ -9377,23 +7493,16 @@
       <c r="K162" s="7"/>
       <c r="L162" s="7"/>
       <c r="M162" s="7"/>
-      <c r="N162" s="15"/>
-      <c r="P162" s="1" t="s">
-        <v>163</v>
-      </c>
-      <c r="Q162" s="1" t="s">
-        <v>785</v>
-      </c>
-    </row>
-    <row r="163" spans="1:17" x14ac:dyDescent="0.25">
+    </row>
+    <row r="163" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A163" s="7">
         <v>162</v>
       </c>
-      <c r="B163" s="18"/>
-      <c r="C163" s="23"/>
-      <c r="D163" s="23"/>
+      <c r="B163" s="20"/>
+      <c r="C163" s="12"/>
+      <c r="D163" s="12"/>
       <c r="E163" s="7" t="s">
-        <v>786</v>
+        <v>724</v>
       </c>
       <c r="F163" s="7" t="s">
         <v>164</v>
@@ -9411,23 +7520,16 @@
       <c r="K163" s="7"/>
       <c r="L163" s="7"/>
       <c r="M163" s="7"/>
-      <c r="N163" s="15"/>
-      <c r="P163" s="1" t="s">
-        <v>164</v>
-      </c>
-      <c r="Q163" s="1" t="s">
-        <v>786</v>
-      </c>
-    </row>
-    <row r="164" spans="1:17" x14ac:dyDescent="0.25">
+    </row>
+    <row r="164" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A164" s="7">
         <v>163</v>
       </c>
-      <c r="B164" s="18"/>
-      <c r="C164" s="23"/>
-      <c r="D164" s="23"/>
+      <c r="B164" s="20"/>
+      <c r="C164" s="12"/>
+      <c r="D164" s="12"/>
       <c r="E164" s="7" t="s">
-        <v>787</v>
+        <v>725</v>
       </c>
       <c r="F164" s="7" t="s">
         <v>165</v>
@@ -9445,23 +7547,16 @@
       <c r="K164" s="7"/>
       <c r="L164" s="7"/>
       <c r="M164" s="7"/>
-      <c r="N164" s="15"/>
-      <c r="P164" s="1" t="s">
-        <v>165</v>
-      </c>
-      <c r="Q164" s="1" t="s">
-        <v>787</v>
-      </c>
-    </row>
-    <row r="165" spans="1:17" x14ac:dyDescent="0.25">
+    </row>
+    <row r="165" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A165" s="8">
         <v>164</v>
       </c>
-      <c r="B165" s="18"/>
-      <c r="C165" s="23"/>
-      <c r="D165" s="23"/>
+      <c r="B165" s="20"/>
+      <c r="C165" s="12"/>
+      <c r="D165" s="12"/>
       <c r="E165" s="8" t="s">
-        <v>788</v>
+        <v>726</v>
       </c>
       <c r="F165" s="8" t="s">
         <v>166</v>
@@ -9479,23 +7574,16 @@
       <c r="K165" s="8"/>
       <c r="L165" s="8"/>
       <c r="M165" s="8"/>
-      <c r="N165" s="15"/>
-      <c r="P165" s="1" t="s">
-        <v>166</v>
-      </c>
-      <c r="Q165" s="1" t="s">
-        <v>788</v>
-      </c>
-    </row>
-    <row r="166" spans="1:17" x14ac:dyDescent="0.25">
+    </row>
+    <row r="166" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A166" s="8">
         <v>165</v>
       </c>
-      <c r="B166" s="18"/>
-      <c r="C166" s="23"/>
-      <c r="D166" s="23"/>
+      <c r="B166" s="20"/>
+      <c r="C166" s="12"/>
+      <c r="D166" s="12"/>
       <c r="E166" s="8" t="s">
-        <v>789</v>
+        <v>727</v>
       </c>
       <c r="F166" s="8" t="s">
         <v>167</v>
@@ -9513,23 +7601,16 @@
       <c r="K166" s="8"/>
       <c r="L166" s="8"/>
       <c r="M166" s="8"/>
-      <c r="N166" s="15"/>
-      <c r="P166" s="1" t="s">
-        <v>167</v>
-      </c>
-      <c r="Q166" s="1" t="s">
-        <v>789</v>
-      </c>
-    </row>
-    <row r="167" spans="1:17" x14ac:dyDescent="0.25">
+    </row>
+    <row r="167" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A167" s="8">
         <v>166</v>
       </c>
-      <c r="B167" s="18"/>
-      <c r="C167" s="23"/>
-      <c r="D167" s="23"/>
+      <c r="B167" s="20"/>
+      <c r="C167" s="12"/>
+      <c r="D167" s="12"/>
       <c r="E167" s="8" t="s">
-        <v>790</v>
+        <v>728</v>
       </c>
       <c r="F167" s="8" t="s">
         <v>168</v>
@@ -9547,23 +7628,16 @@
       <c r="K167" s="8"/>
       <c r="L167" s="8"/>
       <c r="M167" s="8"/>
-      <c r="N167" s="15"/>
-      <c r="P167" s="1" t="s">
-        <v>168</v>
-      </c>
-      <c r="Q167" s="1" t="s">
-        <v>790</v>
-      </c>
-    </row>
-    <row r="168" spans="1:17" x14ac:dyDescent="0.25">
+    </row>
+    <row r="168" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A168" s="7">
         <v>167</v>
       </c>
-      <c r="B168" s="18"/>
-      <c r="C168" s="23"/>
-      <c r="D168" s="23"/>
+      <c r="B168" s="20"/>
+      <c r="C168" s="12"/>
+      <c r="D168" s="12"/>
       <c r="E168" s="7" t="s">
-        <v>791</v>
+        <v>729</v>
       </c>
       <c r="F168" s="7" t="s">
         <v>169</v>
@@ -9581,23 +7655,16 @@
       <c r="K168" s="7"/>
       <c r="L168" s="7"/>
       <c r="M168" s="7"/>
-      <c r="N168" s="15"/>
-      <c r="P168" s="1" t="s">
-        <v>169</v>
-      </c>
-      <c r="Q168" s="1" t="s">
-        <v>791</v>
-      </c>
-    </row>
-    <row r="169" spans="1:17" x14ac:dyDescent="0.25">
+    </row>
+    <row r="169" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A169" s="7">
         <v>168</v>
       </c>
-      <c r="B169" s="18"/>
-      <c r="C169" s="23"/>
-      <c r="D169" s="23"/>
+      <c r="B169" s="20"/>
+      <c r="C169" s="12"/>
+      <c r="D169" s="12"/>
       <c r="E169" s="7" t="s">
-        <v>792</v>
+        <v>730</v>
       </c>
       <c r="F169" s="7" t="s">
         <v>170</v>
@@ -9615,23 +7682,16 @@
       <c r="K169" s="7"/>
       <c r="L169" s="7"/>
       <c r="M169" s="7"/>
-      <c r="N169" s="15"/>
-      <c r="P169" s="1" t="s">
-        <v>170</v>
-      </c>
-      <c r="Q169" s="1" t="s">
-        <v>792</v>
-      </c>
-    </row>
-    <row r="170" spans="1:17" x14ac:dyDescent="0.25">
+    </row>
+    <row r="170" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A170" s="7">
         <v>169</v>
       </c>
-      <c r="B170" s="18"/>
-      <c r="C170" s="23"/>
-      <c r="D170" s="23"/>
+      <c r="B170" s="20"/>
+      <c r="C170" s="12"/>
+      <c r="D170" s="12"/>
       <c r="E170" s="7" t="s">
-        <v>793</v>
+        <v>731</v>
       </c>
       <c r="F170" s="7" t="s">
         <v>171</v>
@@ -9649,23 +7709,16 @@
       <c r="K170" s="7"/>
       <c r="L170" s="7"/>
       <c r="M170" s="7"/>
-      <c r="N170" s="15"/>
-      <c r="P170" s="1" t="s">
-        <v>171</v>
-      </c>
-      <c r="Q170" s="1" t="s">
-        <v>793</v>
-      </c>
-    </row>
-    <row r="171" spans="1:17" x14ac:dyDescent="0.25">
+    </row>
+    <row r="171" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A171" s="7">
         <v>170</v>
       </c>
-      <c r="B171" s="18"/>
-      <c r="C171" s="23"/>
-      <c r="D171" s="23"/>
+      <c r="B171" s="20"/>
+      <c r="C171" s="12"/>
+      <c r="D171" s="12"/>
       <c r="E171" s="7" t="s">
-        <v>794</v>
+        <v>732</v>
       </c>
       <c r="F171" s="7" t="s">
         <v>172</v>
@@ -9683,23 +7736,16 @@
       <c r="K171" s="7"/>
       <c r="L171" s="7"/>
       <c r="M171" s="7"/>
-      <c r="N171" s="15"/>
-      <c r="P171" s="1" t="s">
-        <v>172</v>
-      </c>
-      <c r="Q171" s="1" t="s">
-        <v>794</v>
-      </c>
-    </row>
-    <row r="172" spans="1:17" x14ac:dyDescent="0.25">
+    </row>
+    <row r="172" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A172" s="7">
         <v>171</v>
       </c>
-      <c r="B172" s="18"/>
-      <c r="C172" s="23"/>
-      <c r="D172" s="23"/>
+      <c r="B172" s="20"/>
+      <c r="C172" s="12"/>
+      <c r="D172" s="12"/>
       <c r="E172" s="7" t="s">
-        <v>795</v>
+        <v>733</v>
       </c>
       <c r="F172" s="7" t="s">
         <v>173</v>
@@ -9717,23 +7763,16 @@
       <c r="K172" s="7"/>
       <c r="L172" s="7"/>
       <c r="M172" s="7"/>
-      <c r="N172" s="15"/>
-      <c r="P172" s="1" t="s">
-        <v>173</v>
-      </c>
-      <c r="Q172" s="1" t="s">
-        <v>795</v>
-      </c>
-    </row>
-    <row r="173" spans="1:17" x14ac:dyDescent="0.25">
+    </row>
+    <row r="173" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A173" s="7">
         <v>172</v>
       </c>
-      <c r="B173" s="18"/>
-      <c r="C173" s="23"/>
-      <c r="D173" s="23"/>
+      <c r="B173" s="20"/>
+      <c r="C173" s="12"/>
+      <c r="D173" s="12"/>
       <c r="E173" s="7" t="s">
-        <v>796</v>
+        <v>734</v>
       </c>
       <c r="F173" s="7" t="s">
         <v>174</v>
@@ -9751,23 +7790,16 @@
       <c r="K173" s="7"/>
       <c r="L173" s="7"/>
       <c r="M173" s="7"/>
-      <c r="N173" s="15"/>
-      <c r="P173" s="1" t="s">
-        <v>174</v>
-      </c>
-      <c r="Q173" s="1" t="s">
-        <v>796</v>
-      </c>
-    </row>
-    <row r="174" spans="1:17" x14ac:dyDescent="0.25">
+    </row>
+    <row r="174" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A174" s="8">
         <v>173</v>
       </c>
-      <c r="B174" s="18"/>
-      <c r="C174" s="23"/>
-      <c r="D174" s="23"/>
+      <c r="B174" s="20"/>
+      <c r="C174" s="12"/>
+      <c r="D174" s="12"/>
       <c r="E174" s="8" t="s">
-        <v>797</v>
+        <v>735</v>
       </c>
       <c r="F174" s="8" t="s">
         <v>175</v>
@@ -9785,23 +7817,16 @@
       <c r="K174" s="8"/>
       <c r="L174" s="8"/>
       <c r="M174" s="8"/>
-      <c r="N174" s="15"/>
-      <c r="P174" s="1" t="s">
-        <v>175</v>
-      </c>
-      <c r="Q174" s="1" t="s">
-        <v>797</v>
-      </c>
-    </row>
-    <row r="175" spans="1:17" x14ac:dyDescent="0.25">
+    </row>
+    <row r="175" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A175" s="8">
         <v>174</v>
       </c>
-      <c r="B175" s="18"/>
-      <c r="C175" s="23"/>
-      <c r="D175" s="23"/>
+      <c r="B175" s="20"/>
+      <c r="C175" s="12"/>
+      <c r="D175" s="12"/>
       <c r="E175" s="8" t="s">
-        <v>798</v>
+        <v>736</v>
       </c>
       <c r="F175" s="8" t="s">
         <v>176</v>
@@ -9819,23 +7844,16 @@
       <c r="K175" s="8"/>
       <c r="L175" s="8"/>
       <c r="M175" s="8"/>
-      <c r="N175" s="15"/>
-      <c r="P175" s="1" t="s">
-        <v>176</v>
-      </c>
-      <c r="Q175" s="1" t="s">
-        <v>798</v>
-      </c>
-    </row>
-    <row r="176" spans="1:17" x14ac:dyDescent="0.25">
+    </row>
+    <row r="176" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A176" s="8">
         <v>175</v>
       </c>
-      <c r="B176" s="18"/>
-      <c r="C176" s="23"/>
-      <c r="D176" s="23"/>
+      <c r="B176" s="20"/>
+      <c r="C176" s="12"/>
+      <c r="D176" s="12"/>
       <c r="E176" s="8" t="s">
-        <v>799</v>
+        <v>737</v>
       </c>
       <c r="F176" s="8" t="s">
         <v>177</v>
@@ -9853,23 +7871,16 @@
       <c r="K176" s="8"/>
       <c r="L176" s="8"/>
       <c r="M176" s="8"/>
-      <c r="N176" s="15"/>
-      <c r="P176" s="1" t="s">
-        <v>177</v>
-      </c>
-      <c r="Q176" s="1" t="s">
-        <v>799</v>
-      </c>
-    </row>
-    <row r="177" spans="1:17" x14ac:dyDescent="0.25">
+    </row>
+    <row r="177" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A177" s="8">
         <v>176</v>
       </c>
-      <c r="B177" s="18"/>
-      <c r="C177" s="23"/>
-      <c r="D177" s="23"/>
+      <c r="B177" s="20"/>
+      <c r="C177" s="12"/>
+      <c r="D177" s="12"/>
       <c r="E177" s="8" t="s">
-        <v>800</v>
+        <v>738</v>
       </c>
       <c r="F177" s="8" t="s">
         <v>178</v>
@@ -9887,23 +7898,16 @@
       <c r="K177" s="8"/>
       <c r="L177" s="8"/>
       <c r="M177" s="8"/>
-      <c r="N177" s="15"/>
-      <c r="P177" s="1" t="s">
-        <v>178</v>
-      </c>
-      <c r="Q177" s="1" t="s">
-        <v>800</v>
-      </c>
-    </row>
-    <row r="178" spans="1:17" x14ac:dyDescent="0.25">
+    </row>
+    <row r="178" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A178" s="8">
         <v>177</v>
       </c>
-      <c r="B178" s="18"/>
-      <c r="C178" s="23"/>
-      <c r="D178" s="23"/>
+      <c r="B178" s="20"/>
+      <c r="C178" s="12"/>
+      <c r="D178" s="12"/>
       <c r="E178" s="8" t="s">
-        <v>801</v>
+        <v>739</v>
       </c>
       <c r="F178" s="8" t="s">
         <v>179</v>
@@ -9921,23 +7925,16 @@
       <c r="K178" s="8"/>
       <c r="L178" s="8"/>
       <c r="M178" s="8"/>
-      <c r="N178" s="15"/>
-      <c r="P178" s="1" t="s">
-        <v>179</v>
-      </c>
-      <c r="Q178" s="1" t="s">
-        <v>801</v>
-      </c>
-    </row>
-    <row r="179" spans="1:17" x14ac:dyDescent="0.25">
+    </row>
+    <row r="179" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A179" s="8">
         <v>178</v>
       </c>
-      <c r="B179" s="18"/>
-      <c r="C179" s="23"/>
-      <c r="D179" s="23"/>
+      <c r="B179" s="20"/>
+      <c r="C179" s="12"/>
+      <c r="D179" s="12"/>
       <c r="E179" s="8" t="s">
-        <v>802</v>
+        <v>740</v>
       </c>
       <c r="F179" s="8" t="s">
         <v>180</v>
@@ -9955,23 +7952,16 @@
       <c r="K179" s="8"/>
       <c r="L179" s="8"/>
       <c r="M179" s="8"/>
-      <c r="N179" s="15"/>
-      <c r="P179" s="1" t="s">
-        <v>180</v>
-      </c>
-      <c r="Q179" s="1" t="s">
-        <v>802</v>
-      </c>
-    </row>
-    <row r="180" spans="1:17" x14ac:dyDescent="0.25">
+    </row>
+    <row r="180" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A180" s="7">
         <v>179</v>
       </c>
-      <c r="B180" s="18"/>
-      <c r="C180" s="23"/>
-      <c r="D180" s="23"/>
+      <c r="B180" s="20"/>
+      <c r="C180" s="12"/>
+      <c r="D180" s="12"/>
       <c r="E180" s="7" t="s">
-        <v>803</v>
+        <v>741</v>
       </c>
       <c r="F180" s="7" t="s">
         <v>181</v>
@@ -9989,23 +7979,16 @@
       <c r="K180" s="7"/>
       <c r="L180" s="7"/>
       <c r="M180" s="7"/>
-      <c r="N180" s="15"/>
-      <c r="P180" s="1" t="s">
-        <v>181</v>
-      </c>
-      <c r="Q180" s="1" t="s">
-        <v>803</v>
-      </c>
-    </row>
-    <row r="181" spans="1:17" x14ac:dyDescent="0.25">
+    </row>
+    <row r="181" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A181" s="7">
         <v>180</v>
       </c>
-      <c r="B181" s="18"/>
-      <c r="C181" s="23"/>
-      <c r="D181" s="23"/>
+      <c r="B181" s="20"/>
+      <c r="C181" s="12"/>
+      <c r="D181" s="12"/>
       <c r="E181" s="7" t="s">
-        <v>804</v>
+        <v>742</v>
       </c>
       <c r="F181" s="7" t="s">
         <v>182</v>
@@ -10023,23 +8006,16 @@
       <c r="K181" s="7"/>
       <c r="L181" s="7"/>
       <c r="M181" s="7"/>
-      <c r="N181" s="15"/>
-      <c r="P181" s="1" t="s">
-        <v>182</v>
-      </c>
-      <c r="Q181" s="1" t="s">
-        <v>804</v>
-      </c>
-    </row>
-    <row r="182" spans="1:17" x14ac:dyDescent="0.25">
+    </row>
+    <row r="182" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A182" s="7">
         <v>181</v>
       </c>
-      <c r="B182" s="18"/>
-      <c r="C182" s="23"/>
-      <c r="D182" s="23"/>
+      <c r="B182" s="20"/>
+      <c r="C182" s="12"/>
+      <c r="D182" s="12"/>
       <c r="E182" s="7" t="s">
-        <v>805</v>
+        <v>743</v>
       </c>
       <c r="F182" s="7" t="s">
         <v>183</v>
@@ -10057,23 +8033,16 @@
       <c r="K182" s="7"/>
       <c r="L182" s="7"/>
       <c r="M182" s="7"/>
-      <c r="N182" s="15"/>
-      <c r="P182" s="1" t="s">
-        <v>183</v>
-      </c>
-      <c r="Q182" s="1" t="s">
-        <v>805</v>
-      </c>
-    </row>
-    <row r="183" spans="1:17" x14ac:dyDescent="0.25">
+    </row>
+    <row r="183" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A183" s="7">
         <v>182</v>
       </c>
-      <c r="B183" s="18"/>
-      <c r="C183" s="23"/>
-      <c r="D183" s="23"/>
+      <c r="B183" s="20"/>
+      <c r="C183" s="12"/>
+      <c r="D183" s="12"/>
       <c r="E183" s="7" t="s">
-        <v>806</v>
+        <v>744</v>
       </c>
       <c r="F183" s="7" t="s">
         <v>184</v>
@@ -10091,23 +8060,16 @@
       <c r="K183" s="7"/>
       <c r="L183" s="7"/>
       <c r="M183" s="7"/>
-      <c r="N183" s="15"/>
-      <c r="P183" s="1" t="s">
-        <v>184</v>
-      </c>
-      <c r="Q183" s="1" t="s">
-        <v>806</v>
-      </c>
-    </row>
-    <row r="184" spans="1:17" x14ac:dyDescent="0.25">
+    </row>
+    <row r="184" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A184" s="7">
         <v>183</v>
       </c>
-      <c r="B184" s="18"/>
-      <c r="C184" s="23"/>
-      <c r="D184" s="23"/>
+      <c r="B184" s="20"/>
+      <c r="C184" s="12"/>
+      <c r="D184" s="12"/>
       <c r="E184" s="7" t="s">
-        <v>807</v>
+        <v>745</v>
       </c>
       <c r="F184" s="7" t="s">
         <v>185</v>
@@ -10125,23 +8087,16 @@
       <c r="K184" s="7"/>
       <c r="L184" s="7"/>
       <c r="M184" s="7"/>
-      <c r="N184" s="15"/>
-      <c r="P184" s="1" t="s">
-        <v>185</v>
-      </c>
-      <c r="Q184" s="1" t="s">
-        <v>807</v>
-      </c>
-    </row>
-    <row r="185" spans="1:17" x14ac:dyDescent="0.25">
+    </row>
+    <row r="185" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A185" s="7">
         <v>184</v>
       </c>
-      <c r="B185" s="18"/>
-      <c r="C185" s="23"/>
-      <c r="D185" s="23"/>
+      <c r="B185" s="20"/>
+      <c r="C185" s="12"/>
+      <c r="D185" s="12"/>
       <c r="E185" s="7" t="s">
-        <v>808</v>
+        <v>746</v>
       </c>
       <c r="F185" s="7" t="s">
         <v>186</v>
@@ -10159,23 +8114,16 @@
       <c r="K185" s="7"/>
       <c r="L185" s="7"/>
       <c r="M185" s="7"/>
-      <c r="N185" s="15"/>
-      <c r="P185" s="1" t="s">
-        <v>186</v>
-      </c>
-      <c r="Q185" s="1" t="s">
-        <v>808</v>
-      </c>
-    </row>
-    <row r="186" spans="1:17" x14ac:dyDescent="0.25">
+    </row>
+    <row r="186" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A186" s="8">
         <v>185</v>
       </c>
-      <c r="B186" s="18"/>
-      <c r="C186" s="23"/>
-      <c r="D186" s="23"/>
+      <c r="B186" s="20"/>
+      <c r="C186" s="12"/>
+      <c r="D186" s="12"/>
       <c r="E186" s="8" t="s">
-        <v>809</v>
+        <v>747</v>
       </c>
       <c r="F186" s="8" t="s">
         <v>187</v>
@@ -10193,23 +8141,16 @@
       <c r="K186" s="8"/>
       <c r="L186" s="8"/>
       <c r="M186" s="8"/>
-      <c r="N186" s="15"/>
-      <c r="P186" s="1" t="s">
-        <v>187</v>
-      </c>
-      <c r="Q186" s="1" t="s">
-        <v>809</v>
-      </c>
-    </row>
-    <row r="187" spans="1:17" x14ac:dyDescent="0.25">
+    </row>
+    <row r="187" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A187" s="7">
         <v>186</v>
       </c>
-      <c r="B187" s="18"/>
-      <c r="C187" s="23"/>
-      <c r="D187" s="23"/>
+      <c r="B187" s="20"/>
+      <c r="C187" s="12"/>
+      <c r="D187" s="12"/>
       <c r="E187" s="7" t="s">
-        <v>810</v>
+        <v>748</v>
       </c>
       <c r="F187" s="7" t="s">
         <v>188</v>
@@ -10227,23 +8168,16 @@
       <c r="K187" s="7"/>
       <c r="L187" s="7"/>
       <c r="M187" s="7"/>
-      <c r="N187" s="15"/>
-      <c r="P187" s="1" t="s">
-        <v>188</v>
-      </c>
-      <c r="Q187" s="1" t="s">
-        <v>810</v>
-      </c>
-    </row>
-    <row r="188" spans="1:17" x14ac:dyDescent="0.25">
+    </row>
+    <row r="188" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A188" s="8">
         <v>187</v>
       </c>
-      <c r="B188" s="18"/>
-      <c r="C188" s="23"/>
-      <c r="D188" s="23"/>
+      <c r="B188" s="20"/>
+      <c r="C188" s="12"/>
+      <c r="D188" s="12"/>
       <c r="E188" s="8" t="s">
-        <v>811</v>
+        <v>749</v>
       </c>
       <c r="F188" s="8" t="s">
         <v>189</v>
@@ -10261,23 +8195,16 @@
       <c r="K188" s="8"/>
       <c r="L188" s="8"/>
       <c r="M188" s="8"/>
-      <c r="N188" s="15"/>
-      <c r="P188" s="1" t="s">
-        <v>189</v>
-      </c>
-      <c r="Q188" s="1" t="s">
-        <v>811</v>
-      </c>
-    </row>
-    <row r="189" spans="1:17" x14ac:dyDescent="0.25">
+    </row>
+    <row r="189" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A189" s="8">
         <v>188</v>
       </c>
-      <c r="B189" s="18"/>
-      <c r="C189" s="23"/>
-      <c r="D189" s="23"/>
+      <c r="B189" s="20"/>
+      <c r="C189" s="12"/>
+      <c r="D189" s="12"/>
       <c r="E189" s="8" t="s">
-        <v>812</v>
+        <v>750</v>
       </c>
       <c r="F189" s="8" t="s">
         <v>190</v>
@@ -10295,23 +8222,16 @@
       <c r="K189" s="8"/>
       <c r="L189" s="8"/>
       <c r="M189" s="8"/>
-      <c r="N189" s="15"/>
-      <c r="P189" s="1" t="s">
-        <v>190</v>
-      </c>
-      <c r="Q189" s="1" t="s">
-        <v>812</v>
-      </c>
-    </row>
-    <row r="190" spans="1:17" x14ac:dyDescent="0.25">
+    </row>
+    <row r="190" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A190" s="8">
         <v>189</v>
       </c>
-      <c r="B190" s="18"/>
-      <c r="C190" s="23"/>
-      <c r="D190" s="23"/>
+      <c r="B190" s="20"/>
+      <c r="C190" s="12"/>
+      <c r="D190" s="12"/>
       <c r="E190" s="8" t="s">
-        <v>813</v>
+        <v>751</v>
       </c>
       <c r="F190" s="8" t="s">
         <v>191</v>
@@ -10329,23 +8249,16 @@
       <c r="K190" s="8"/>
       <c r="L190" s="8"/>
       <c r="M190" s="8"/>
-      <c r="N190" s="15"/>
-      <c r="P190" s="1" t="s">
-        <v>191</v>
-      </c>
-      <c r="Q190" s="1" t="s">
-        <v>813</v>
-      </c>
-    </row>
-    <row r="191" spans="1:17" x14ac:dyDescent="0.25">
+    </row>
+    <row r="191" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A191" s="7">
         <v>190</v>
       </c>
-      <c r="B191" s="18"/>
-      <c r="C191" s="23"/>
-      <c r="D191" s="23"/>
+      <c r="B191" s="20"/>
+      <c r="C191" s="12"/>
+      <c r="D191" s="12"/>
       <c r="E191" s="7" t="s">
-        <v>814</v>
+        <v>752</v>
       </c>
       <c r="F191" s="7" t="s">
         <v>192</v>
@@ -10363,23 +8276,16 @@
       <c r="K191" s="7"/>
       <c r="L191" s="7"/>
       <c r="M191" s="7"/>
-      <c r="N191" s="15"/>
-      <c r="P191" s="1" t="s">
-        <v>192</v>
-      </c>
-      <c r="Q191" s="1" t="s">
-        <v>814</v>
-      </c>
-    </row>
-    <row r="192" spans="1:17" x14ac:dyDescent="0.25">
+    </row>
+    <row r="192" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A192" s="7">
         <v>191</v>
       </c>
-      <c r="B192" s="18"/>
-      <c r="C192" s="23"/>
-      <c r="D192" s="23"/>
+      <c r="B192" s="20"/>
+      <c r="C192" s="12"/>
+      <c r="D192" s="12"/>
       <c r="E192" s="7" t="s">
-        <v>815</v>
+        <v>753</v>
       </c>
       <c r="F192" s="7" t="s">
         <v>193</v>
@@ -10397,23 +8303,16 @@
       <c r="K192" s="7"/>
       <c r="L192" s="7"/>
       <c r="M192" s="7"/>
-      <c r="N192" s="15"/>
-      <c r="P192" s="1" t="s">
-        <v>193</v>
-      </c>
-      <c r="Q192" s="1" t="s">
-        <v>815</v>
-      </c>
-    </row>
-    <row r="193" spans="1:17" x14ac:dyDescent="0.25">
+    </row>
+    <row r="193" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A193" s="8">
         <v>192</v>
       </c>
-      <c r="B193" s="18"/>
-      <c r="C193" s="23"/>
-      <c r="D193" s="23"/>
+      <c r="B193" s="20"/>
+      <c r="C193" s="12"/>
+      <c r="D193" s="12"/>
       <c r="E193" s="8" t="s">
-        <v>816</v>
+        <v>754</v>
       </c>
       <c r="F193" s="8" t="s">
         <v>194</v>
@@ -10431,23 +8330,16 @@
       <c r="K193" s="8"/>
       <c r="L193" s="8"/>
       <c r="M193" s="8"/>
-      <c r="N193" s="15"/>
-      <c r="P193" s="1" t="s">
-        <v>194</v>
-      </c>
-      <c r="Q193" s="1" t="s">
-        <v>816</v>
-      </c>
-    </row>
-    <row r="194" spans="1:17" x14ac:dyDescent="0.25">
+    </row>
+    <row r="194" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A194" s="8">
         <v>193</v>
       </c>
-      <c r="B194" s="18"/>
-      <c r="C194" s="23"/>
-      <c r="D194" s="23"/>
+      <c r="B194" s="20"/>
+      <c r="C194" s="12"/>
+      <c r="D194" s="12"/>
       <c r="E194" s="8" t="s">
-        <v>817</v>
+        <v>755</v>
       </c>
       <c r="F194" s="8" t="s">
         <v>195</v>
@@ -10465,23 +8357,16 @@
       <c r="K194" s="8"/>
       <c r="L194" s="8"/>
       <c r="M194" s="8"/>
-      <c r="N194" s="15"/>
-      <c r="P194" s="1" t="s">
-        <v>195</v>
-      </c>
-      <c r="Q194" s="1" t="s">
-        <v>817</v>
-      </c>
-    </row>
-    <row r="195" spans="1:17" x14ac:dyDescent="0.25">
+    </row>
+    <row r="195" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A195" s="8">
         <v>194</v>
       </c>
-      <c r="B195" s="18"/>
-      <c r="C195" s="23"/>
-      <c r="D195" s="23"/>
+      <c r="B195" s="20"/>
+      <c r="C195" s="12"/>
+      <c r="D195" s="12"/>
       <c r="E195" s="8" t="s">
-        <v>818</v>
+        <v>756</v>
       </c>
       <c r="F195" s="8" t="s">
         <v>196</v>
@@ -10499,23 +8384,16 @@
       <c r="K195" s="8"/>
       <c r="L195" s="8"/>
       <c r="M195" s="8"/>
-      <c r="N195" s="15"/>
-      <c r="P195" s="1" t="s">
-        <v>196</v>
-      </c>
-      <c r="Q195" s="1" t="s">
-        <v>818</v>
-      </c>
-    </row>
-    <row r="196" spans="1:17" x14ac:dyDescent="0.25">
+    </row>
+    <row r="196" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A196" s="8">
         <v>195</v>
       </c>
-      <c r="B196" s="18"/>
-      <c r="C196" s="23"/>
-      <c r="D196" s="23"/>
+      <c r="B196" s="20"/>
+      <c r="C196" s="12"/>
+      <c r="D196" s="12"/>
       <c r="E196" s="8" t="s">
-        <v>819</v>
+        <v>757</v>
       </c>
       <c r="F196" s="8" t="s">
         <v>197</v>
@@ -10533,23 +8411,16 @@
       <c r="K196" s="8"/>
       <c r="L196" s="8"/>
       <c r="M196" s="8"/>
-      <c r="N196" s="15"/>
-      <c r="P196" s="1" t="s">
-        <v>197</v>
-      </c>
-      <c r="Q196" s="1" t="s">
-        <v>819</v>
-      </c>
-    </row>
-    <row r="197" spans="1:17" x14ac:dyDescent="0.25">
+    </row>
+    <row r="197" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A197" s="8">
         <v>196</v>
       </c>
-      <c r="B197" s="18"/>
-      <c r="C197" s="23"/>
-      <c r="D197" s="23"/>
+      <c r="B197" s="20"/>
+      <c r="C197" s="12"/>
+      <c r="D197" s="12"/>
       <c r="E197" s="8" t="s">
-        <v>820</v>
+        <v>758</v>
       </c>
       <c r="F197" s="8" t="s">
         <v>198</v>
@@ -10567,23 +8438,16 @@
       <c r="K197" s="8"/>
       <c r="L197" s="8"/>
       <c r="M197" s="8"/>
-      <c r="N197" s="15"/>
-      <c r="P197" s="1" t="s">
-        <v>198</v>
-      </c>
-      <c r="Q197" s="1" t="s">
-        <v>820</v>
-      </c>
-    </row>
-    <row r="198" spans="1:17" x14ac:dyDescent="0.25">
+    </row>
+    <row r="198" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A198" s="8">
         <v>197</v>
       </c>
-      <c r="B198" s="18"/>
-      <c r="C198" s="23"/>
-      <c r="D198" s="23"/>
+      <c r="B198" s="20"/>
+      <c r="C198" s="12"/>
+      <c r="D198" s="12"/>
       <c r="E198" s="8" t="s">
-        <v>821</v>
+        <v>759</v>
       </c>
       <c r="F198" s="8" t="s">
         <v>199</v>
@@ -10601,23 +8465,16 @@
       <c r="K198" s="8"/>
       <c r="L198" s="8"/>
       <c r="M198" s="8"/>
-      <c r="N198" s="15"/>
-      <c r="P198" s="1" t="s">
-        <v>199</v>
-      </c>
-      <c r="Q198" s="1" t="s">
-        <v>821</v>
-      </c>
-    </row>
-    <row r="199" spans="1:17" x14ac:dyDescent="0.25">
+    </row>
+    <row r="199" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A199" s="7">
         <v>198</v>
       </c>
-      <c r="B199" s="18"/>
-      <c r="C199" s="23"/>
-      <c r="D199" s="23"/>
+      <c r="B199" s="20"/>
+      <c r="C199" s="12"/>
+      <c r="D199" s="12"/>
       <c r="E199" s="7" t="s">
-        <v>822</v>
+        <v>760</v>
       </c>
       <c r="F199" s="7" t="s">
         <v>200</v>
@@ -10635,23 +8492,16 @@
       <c r="K199" s="7"/>
       <c r="L199" s="7"/>
       <c r="M199" s="7"/>
-      <c r="N199" s="15"/>
-      <c r="P199" s="1" t="s">
-        <v>200</v>
-      </c>
-      <c r="Q199" s="1" t="s">
-        <v>822</v>
-      </c>
-    </row>
-    <row r="200" spans="1:17" x14ac:dyDescent="0.25">
+    </row>
+    <row r="200" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A200" s="7">
         <v>199</v>
       </c>
-      <c r="B200" s="18"/>
-      <c r="C200" s="23"/>
-      <c r="D200" s="23"/>
+      <c r="B200" s="20"/>
+      <c r="C200" s="12"/>
+      <c r="D200" s="12"/>
       <c r="E200" s="7" t="s">
-        <v>823</v>
+        <v>761</v>
       </c>
       <c r="F200" s="7" t="s">
         <v>201</v>
@@ -10669,23 +8519,16 @@
       <c r="K200" s="7"/>
       <c r="L200" s="7"/>
       <c r="M200" s="7"/>
-      <c r="N200" s="15"/>
-      <c r="P200" s="1" t="s">
-        <v>201</v>
-      </c>
-      <c r="Q200" s="1" t="s">
-        <v>823</v>
-      </c>
-    </row>
-    <row r="201" spans="1:17" x14ac:dyDescent="0.25">
+    </row>
+    <row r="201" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A201" s="7">
         <v>200</v>
       </c>
-      <c r="B201" s="18"/>
-      <c r="C201" s="23"/>
-      <c r="D201" s="23"/>
+      <c r="B201" s="20"/>
+      <c r="C201" s="12"/>
+      <c r="D201" s="12"/>
       <c r="E201" s="7" t="s">
-        <v>824</v>
+        <v>762</v>
       </c>
       <c r="F201" s="7" t="s">
         <v>202</v>
@@ -10703,23 +8546,16 @@
       <c r="K201" s="7"/>
       <c r="L201" s="7"/>
       <c r="M201" s="7"/>
-      <c r="N201" s="15"/>
-      <c r="P201" s="1" t="s">
-        <v>202</v>
-      </c>
-      <c r="Q201" s="1" t="s">
-        <v>824</v>
-      </c>
-    </row>
-    <row r="202" spans="1:17" x14ac:dyDescent="0.25">
+    </row>
+    <row r="202" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A202" s="7">
         <v>201</v>
       </c>
-      <c r="B202" s="18"/>
-      <c r="C202" s="23"/>
-      <c r="D202" s="23"/>
+      <c r="B202" s="20"/>
+      <c r="C202" s="12"/>
+      <c r="D202" s="12"/>
       <c r="E202" s="7" t="s">
-        <v>825</v>
+        <v>763</v>
       </c>
       <c r="F202" s="7" t="s">
         <v>203</v>
@@ -10737,23 +8573,16 @@
       <c r="K202" s="7"/>
       <c r="L202" s="7"/>
       <c r="M202" s="7"/>
-      <c r="N202" s="15"/>
-      <c r="P202" s="1" t="s">
-        <v>203</v>
-      </c>
-      <c r="Q202" s="1" t="s">
-        <v>825</v>
-      </c>
-    </row>
-    <row r="203" spans="1:17" x14ac:dyDescent="0.25">
+    </row>
+    <row r="203" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A203" s="7">
         <v>202</v>
       </c>
-      <c r="B203" s="18"/>
-      <c r="C203" s="23"/>
-      <c r="D203" s="23"/>
+      <c r="B203" s="20"/>
+      <c r="C203" s="12"/>
+      <c r="D203" s="12"/>
       <c r="E203" s="7" t="s">
-        <v>826</v>
+        <v>764</v>
       </c>
       <c r="F203" s="7" t="s">
         <v>204</v>
@@ -10771,23 +8600,16 @@
       <c r="K203" s="7"/>
       <c r="L203" s="7"/>
       <c r="M203" s="7"/>
-      <c r="N203" s="15"/>
-      <c r="P203" s="1" t="s">
-        <v>204</v>
-      </c>
-      <c r="Q203" s="1" t="s">
-        <v>826</v>
-      </c>
-    </row>
-    <row r="204" spans="1:17" x14ac:dyDescent="0.25">
+    </row>
+    <row r="204" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A204" s="7">
         <v>203</v>
       </c>
-      <c r="B204" s="18"/>
-      <c r="C204" s="23"/>
-      <c r="D204" s="23"/>
+      <c r="B204" s="20"/>
+      <c r="C204" s="12"/>
+      <c r="D204" s="12"/>
       <c r="E204" s="7" t="s">
-        <v>827</v>
+        <v>765</v>
       </c>
       <c r="F204" s="7" t="s">
         <v>205</v>
@@ -10805,23 +8627,16 @@
       <c r="K204" s="7"/>
       <c r="L204" s="7"/>
       <c r="M204" s="7"/>
-      <c r="N204" s="15"/>
-      <c r="P204" s="1" t="s">
-        <v>205</v>
-      </c>
-      <c r="Q204" s="1" t="s">
-        <v>827</v>
-      </c>
-    </row>
-    <row r="205" spans="1:17" x14ac:dyDescent="0.25">
+    </row>
+    <row r="205" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A205" s="7">
         <v>204</v>
       </c>
-      <c r="B205" s="18"/>
-      <c r="C205" s="23"/>
-      <c r="D205" s="23"/>
+      <c r="B205" s="20"/>
+      <c r="C205" s="12"/>
+      <c r="D205" s="12"/>
       <c r="E205" s="7" t="s">
-        <v>828</v>
+        <v>766</v>
       </c>
       <c r="F205" s="7" t="s">
         <v>206</v>
@@ -10839,23 +8654,16 @@
       <c r="K205" s="7"/>
       <c r="L205" s="7"/>
       <c r="M205" s="7"/>
-      <c r="N205" s="15"/>
-      <c r="P205" s="1" t="s">
-        <v>206</v>
-      </c>
-      <c r="Q205" s="1" t="s">
-        <v>828</v>
-      </c>
-    </row>
-    <row r="206" spans="1:17" x14ac:dyDescent="0.25">
+    </row>
+    <row r="206" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A206" s="8">
         <v>205</v>
       </c>
-      <c r="B206" s="18"/>
-      <c r="C206" s="23"/>
-      <c r="D206" s="23"/>
+      <c r="B206" s="20"/>
+      <c r="C206" s="12"/>
+      <c r="D206" s="12"/>
       <c r="E206" s="8" t="s">
-        <v>829</v>
+        <v>767</v>
       </c>
       <c r="F206" s="8" t="s">
         <v>207</v>
@@ -10873,23 +8681,16 @@
       <c r="K206" s="8"/>
       <c r="L206" s="8"/>
       <c r="M206" s="8"/>
-      <c r="N206" s="15"/>
-      <c r="P206" s="1" t="s">
-        <v>207</v>
-      </c>
-      <c r="Q206" s="1" t="s">
-        <v>829</v>
-      </c>
-    </row>
-    <row r="207" spans="1:17" x14ac:dyDescent="0.25">
+    </row>
+    <row r="207" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A207" s="7">
         <v>206</v>
       </c>
-      <c r="B207" s="18"/>
-      <c r="C207" s="23"/>
-      <c r="D207" s="23"/>
+      <c r="B207" s="20"/>
+      <c r="C207" s="12"/>
+      <c r="D207" s="12"/>
       <c r="E207" s="7" t="s">
-        <v>830</v>
+        <v>768</v>
       </c>
       <c r="F207" s="7" t="s">
         <v>208</v>
@@ -10907,23 +8708,16 @@
       <c r="K207" s="7"/>
       <c r="L207" s="7"/>
       <c r="M207" s="7"/>
-      <c r="N207" s="15"/>
-      <c r="P207" s="1" t="s">
-        <v>208</v>
-      </c>
-      <c r="Q207" s="1" t="s">
-        <v>830</v>
-      </c>
-    </row>
-    <row r="208" spans="1:17" x14ac:dyDescent="0.25">
+    </row>
+    <row r="208" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A208" s="7">
         <v>207</v>
       </c>
-      <c r="B208" s="18"/>
-      <c r="C208" s="23"/>
-      <c r="D208" s="23"/>
+      <c r="B208" s="20"/>
+      <c r="C208" s="12"/>
+      <c r="D208" s="12"/>
       <c r="E208" s="7" t="s">
-        <v>831</v>
+        <v>769</v>
       </c>
       <c r="F208" s="7" t="s">
         <v>209</v>
@@ -10941,23 +8735,16 @@
       <c r="K208" s="7"/>
       <c r="L208" s="7"/>
       <c r="M208" s="7"/>
-      <c r="N208" s="15"/>
-      <c r="P208" s="1" t="s">
-        <v>209</v>
-      </c>
-      <c r="Q208" s="1" t="s">
-        <v>831</v>
-      </c>
-    </row>
-    <row r="209" spans="1:17" x14ac:dyDescent="0.25">
+    </row>
+    <row r="209" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A209" s="7">
         <v>208</v>
       </c>
-      <c r="B209" s="18"/>
-      <c r="C209" s="23"/>
-      <c r="D209" s="23"/>
+      <c r="B209" s="20"/>
+      <c r="C209" s="12"/>
+      <c r="D209" s="12"/>
       <c r="E209" s="7" t="s">
-        <v>832</v>
+        <v>770</v>
       </c>
       <c r="F209" s="7" t="s">
         <v>210</v>
@@ -10975,23 +8762,16 @@
       <c r="K209" s="7"/>
       <c r="L209" s="7"/>
       <c r="M209" s="7"/>
-      <c r="N209" s="15"/>
-      <c r="P209" s="1" t="s">
-        <v>210</v>
-      </c>
-      <c r="Q209" s="1" t="s">
-        <v>832</v>
-      </c>
-    </row>
-    <row r="210" spans="1:17" x14ac:dyDescent="0.25">
+    </row>
+    <row r="210" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A210" s="7">
         <v>209</v>
       </c>
-      <c r="B210" s="18"/>
-      <c r="C210" s="23"/>
-      <c r="D210" s="23"/>
+      <c r="B210" s="20"/>
+      <c r="C210" s="12"/>
+      <c r="D210" s="12"/>
       <c r="E210" s="7" t="s">
-        <v>833</v>
+        <v>771</v>
       </c>
       <c r="F210" s="7" t="s">
         <v>211</v>
@@ -11009,23 +8789,16 @@
       <c r="K210" s="7"/>
       <c r="L210" s="7"/>
       <c r="M210" s="7"/>
-      <c r="N210" s="15"/>
-      <c r="P210" s="1" t="s">
-        <v>211</v>
-      </c>
-      <c r="Q210" s="1" t="s">
-        <v>833</v>
-      </c>
-    </row>
-    <row r="211" spans="1:17" x14ac:dyDescent="0.25">
+    </row>
+    <row r="211" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A211" s="8">
         <v>210</v>
       </c>
-      <c r="B211" s="18"/>
-      <c r="C211" s="23"/>
-      <c r="D211" s="23"/>
+      <c r="B211" s="20"/>
+      <c r="C211" s="12"/>
+      <c r="D211" s="12"/>
       <c r="E211" s="8" t="s">
-        <v>834</v>
+        <v>772</v>
       </c>
       <c r="F211" s="8" t="s">
         <v>212</v>
@@ -11043,23 +8816,16 @@
       <c r="K211" s="8"/>
       <c r="L211" s="8"/>
       <c r="M211" s="8"/>
-      <c r="N211" s="15"/>
-      <c r="P211" s="1" t="s">
-        <v>212</v>
-      </c>
-      <c r="Q211" s="1" t="s">
-        <v>834</v>
-      </c>
-    </row>
-    <row r="212" spans="1:17" x14ac:dyDescent="0.25">
+    </row>
+    <row r="212" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A212" s="8">
         <v>211</v>
       </c>
-      <c r="B212" s="18"/>
-      <c r="C212" s="23"/>
-      <c r="D212" s="23"/>
+      <c r="B212" s="20"/>
+      <c r="C212" s="12"/>
+      <c r="D212" s="12"/>
       <c r="E212" s="8" t="s">
-        <v>835</v>
+        <v>773</v>
       </c>
       <c r="F212" s="8" t="s">
         <v>213</v>
@@ -11077,23 +8843,16 @@
       <c r="K212" s="8"/>
       <c r="L212" s="8"/>
       <c r="M212" s="8"/>
-      <c r="N212" s="15"/>
-      <c r="P212" s="1" t="s">
-        <v>213</v>
-      </c>
-      <c r="Q212" s="1" t="s">
-        <v>835</v>
-      </c>
-    </row>
-    <row r="213" spans="1:17" x14ac:dyDescent="0.25">
+    </row>
+    <row r="213" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A213" s="7">
         <v>212</v>
       </c>
-      <c r="B213" s="18"/>
-      <c r="C213" s="23"/>
-      <c r="D213" s="23"/>
+      <c r="B213" s="20"/>
+      <c r="C213" s="12"/>
+      <c r="D213" s="12"/>
       <c r="E213" s="7" t="s">
-        <v>836</v>
+        <v>774</v>
       </c>
       <c r="F213" s="7" t="s">
         <v>214</v>
@@ -11111,23 +8870,16 @@
       <c r="K213" s="7"/>
       <c r="L213" s="7"/>
       <c r="M213" s="7"/>
-      <c r="N213" s="15"/>
-      <c r="P213" s="1" t="s">
-        <v>214</v>
-      </c>
-      <c r="Q213" s="1" t="s">
-        <v>836</v>
-      </c>
-    </row>
-    <row r="214" spans="1:17" x14ac:dyDescent="0.25">
+    </row>
+    <row r="214" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A214" s="7">
         <v>213</v>
       </c>
-      <c r="B214" s="18"/>
-      <c r="C214" s="23"/>
-      <c r="D214" s="23"/>
+      <c r="B214" s="20"/>
+      <c r="C214" s="12"/>
+      <c r="D214" s="12"/>
       <c r="E214" s="7" t="s">
-        <v>837</v>
+        <v>775</v>
       </c>
       <c r="F214" s="7" t="s">
         <v>215</v>
@@ -11145,23 +8897,16 @@
       <c r="K214" s="7"/>
       <c r="L214" s="7"/>
       <c r="M214" s="7"/>
-      <c r="N214" s="15"/>
-      <c r="P214" s="1" t="s">
-        <v>215</v>
-      </c>
-      <c r="Q214" s="1" t="s">
-        <v>837</v>
-      </c>
-    </row>
-    <row r="215" spans="1:17" x14ac:dyDescent="0.25">
+    </row>
+    <row r="215" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A215" s="7">
         <v>214</v>
       </c>
-      <c r="B215" s="18"/>
-      <c r="C215" s="23"/>
-      <c r="D215" s="23"/>
+      <c r="B215" s="20"/>
+      <c r="C215" s="12"/>
+      <c r="D215" s="12"/>
       <c r="E215" s="7" t="s">
-        <v>838</v>
+        <v>776</v>
       </c>
       <c r="F215" s="7" t="s">
         <v>216</v>
@@ -11179,23 +8924,16 @@
       <c r="K215" s="7"/>
       <c r="L215" s="7"/>
       <c r="M215" s="7"/>
-      <c r="N215" s="15"/>
-      <c r="P215" s="1" t="s">
-        <v>216</v>
-      </c>
-      <c r="Q215" s="1" t="s">
-        <v>838</v>
-      </c>
-    </row>
-    <row r="216" spans="1:17" x14ac:dyDescent="0.25">
+    </row>
+    <row r="216" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A216" s="7">
         <v>215</v>
       </c>
-      <c r="B216" s="18"/>
-      <c r="C216" s="23"/>
-      <c r="D216" s="23"/>
+      <c r="B216" s="20"/>
+      <c r="C216" s="12"/>
+      <c r="D216" s="12"/>
       <c r="E216" s="7" t="s">
-        <v>839</v>
+        <v>777</v>
       </c>
       <c r="F216" s="7" t="s">
         <v>217</v>
@@ -11213,23 +8951,16 @@
       <c r="K216" s="7"/>
       <c r="L216" s="7"/>
       <c r="M216" s="7"/>
-      <c r="N216" s="15"/>
-      <c r="P216" s="1" t="s">
-        <v>217</v>
-      </c>
-      <c r="Q216" s="1" t="s">
-        <v>839</v>
-      </c>
-    </row>
-    <row r="217" spans="1:17" x14ac:dyDescent="0.25">
+    </row>
+    <row r="217" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A217" s="7">
         <v>216</v>
       </c>
-      <c r="B217" s="18"/>
-      <c r="C217" s="23"/>
-      <c r="D217" s="23"/>
+      <c r="B217" s="20"/>
+      <c r="C217" s="12"/>
+      <c r="D217" s="12"/>
       <c r="E217" s="7" t="s">
-        <v>840</v>
+        <v>778</v>
       </c>
       <c r="F217" s="7" t="s">
         <v>218</v>
@@ -11247,23 +8978,16 @@
       <c r="K217" s="7"/>
       <c r="L217" s="7"/>
       <c r="M217" s="7"/>
-      <c r="N217" s="15"/>
-      <c r="P217" s="1" t="s">
-        <v>218</v>
-      </c>
-      <c r="Q217" s="1" t="s">
-        <v>840</v>
-      </c>
-    </row>
-    <row r="218" spans="1:17" x14ac:dyDescent="0.25">
+    </row>
+    <row r="218" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A218" s="8">
         <v>217</v>
       </c>
-      <c r="B218" s="18"/>
-      <c r="C218" s="23"/>
-      <c r="D218" s="23"/>
+      <c r="B218" s="20"/>
+      <c r="C218" s="12"/>
+      <c r="D218" s="12"/>
       <c r="E218" s="8" t="s">
-        <v>841</v>
+        <v>779</v>
       </c>
       <c r="F218" s="8" t="s">
         <v>219</v>
@@ -11281,23 +9005,16 @@
       <c r="K218" s="8"/>
       <c r="L218" s="8"/>
       <c r="M218" s="8"/>
-      <c r="N218" s="15"/>
-      <c r="P218" s="1" t="s">
-        <v>219</v>
-      </c>
-      <c r="Q218" s="1" t="s">
-        <v>841</v>
-      </c>
-    </row>
-    <row r="219" spans="1:17" x14ac:dyDescent="0.25">
+    </row>
+    <row r="219" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A219" s="8">
         <v>218</v>
       </c>
-      <c r="B219" s="18"/>
-      <c r="C219" s="23"/>
-      <c r="D219" s="23"/>
+      <c r="B219" s="20"/>
+      <c r="C219" s="12"/>
+      <c r="D219" s="12"/>
       <c r="E219" s="8" t="s">
-        <v>842</v>
+        <v>780</v>
       </c>
       <c r="F219" s="8" t="s">
         <v>220</v>
@@ -11315,23 +9032,16 @@
       <c r="K219" s="8"/>
       <c r="L219" s="8"/>
       <c r="M219" s="8"/>
-      <c r="N219" s="15"/>
-      <c r="P219" s="1" t="s">
-        <v>220</v>
-      </c>
-      <c r="Q219" s="1" t="s">
-        <v>842</v>
-      </c>
-    </row>
-    <row r="220" spans="1:17" x14ac:dyDescent="0.25">
+    </row>
+    <row r="220" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A220" s="7">
         <v>219</v>
       </c>
-      <c r="B220" s="18"/>
-      <c r="C220" s="23"/>
-      <c r="D220" s="23"/>
+      <c r="B220" s="20"/>
+      <c r="C220" s="12"/>
+      <c r="D220" s="12"/>
       <c r="E220" s="7" t="s">
-        <v>843</v>
+        <v>781</v>
       </c>
       <c r="F220" s="7" t="s">
         <v>221</v>
@@ -11349,23 +9059,16 @@
       <c r="K220" s="7"/>
       <c r="L220" s="7"/>
       <c r="M220" s="7"/>
-      <c r="N220" s="15"/>
-      <c r="P220" s="1" t="s">
-        <v>221</v>
-      </c>
-      <c r="Q220" s="1" t="s">
-        <v>843</v>
-      </c>
-    </row>
-    <row r="221" spans="1:17" x14ac:dyDescent="0.25">
+    </row>
+    <row r="221" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A221" s="8">
         <v>220</v>
       </c>
-      <c r="B221" s="18"/>
-      <c r="C221" s="23"/>
-      <c r="D221" s="23"/>
+      <c r="B221" s="20"/>
+      <c r="C221" s="12"/>
+      <c r="D221" s="12"/>
       <c r="E221" s="8" t="s">
-        <v>844</v>
+        <v>782</v>
       </c>
       <c r="F221" s="8" t="s">
         <v>222</v>
@@ -11383,23 +9086,16 @@
       <c r="K221" s="8"/>
       <c r="L221" s="8"/>
       <c r="M221" s="8"/>
-      <c r="N221" s="15"/>
-      <c r="P221" s="1" t="s">
-        <v>222</v>
-      </c>
-      <c r="Q221" s="1" t="s">
-        <v>844</v>
-      </c>
-    </row>
-    <row r="222" spans="1:17" x14ac:dyDescent="0.25">
+    </row>
+    <row r="222" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A222" s="8">
         <v>221</v>
       </c>
-      <c r="B222" s="18"/>
-      <c r="C222" s="23"/>
-      <c r="D222" s="23"/>
+      <c r="B222" s="20"/>
+      <c r="C222" s="12"/>
+      <c r="D222" s="12"/>
       <c r="E222" s="8" t="s">
-        <v>845</v>
+        <v>783</v>
       </c>
       <c r="F222" s="8" t="s">
         <v>223</v>
@@ -11417,23 +9113,16 @@
       <c r="K222" s="8"/>
       <c r="L222" s="8"/>
       <c r="M222" s="8"/>
-      <c r="N222" s="15"/>
-      <c r="P222" s="1" t="s">
-        <v>223</v>
-      </c>
-      <c r="Q222" s="1" t="s">
-        <v>845</v>
-      </c>
-    </row>
-    <row r="223" spans="1:17" x14ac:dyDescent="0.25">
+    </row>
+    <row r="223" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A223" s="8">
         <v>222</v>
       </c>
-      <c r="B223" s="18"/>
-      <c r="C223" s="23"/>
-      <c r="D223" s="23"/>
+      <c r="B223" s="20"/>
+      <c r="C223" s="12"/>
+      <c r="D223" s="12"/>
       <c r="E223" s="8" t="s">
-        <v>846</v>
+        <v>784</v>
       </c>
       <c r="F223" s="8" t="s">
         <v>224</v>
@@ -11451,23 +9140,16 @@
       <c r="K223" s="8"/>
       <c r="L223" s="8"/>
       <c r="M223" s="8"/>
-      <c r="N223" s="15"/>
-      <c r="P223" s="1" t="s">
-        <v>224</v>
-      </c>
-      <c r="Q223" s="1" t="s">
-        <v>846</v>
-      </c>
-    </row>
-    <row r="224" spans="1:17" x14ac:dyDescent="0.25">
+    </row>
+    <row r="224" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A224" s="8">
         <v>223</v>
       </c>
-      <c r="B224" s="18"/>
-      <c r="C224" s="23"/>
-      <c r="D224" s="23"/>
+      <c r="B224" s="20"/>
+      <c r="C224" s="12"/>
+      <c r="D224" s="12"/>
       <c r="E224" s="8" t="s">
-        <v>847</v>
+        <v>785</v>
       </c>
       <c r="F224" s="8" t="s">
         <v>225</v>
@@ -11485,23 +9167,16 @@
       <c r="K224" s="8"/>
       <c r="L224" s="8"/>
       <c r="M224" s="8"/>
-      <c r="N224" s="15"/>
-      <c r="P224" s="1" t="s">
-        <v>225</v>
-      </c>
-      <c r="Q224" s="1" t="s">
-        <v>847</v>
-      </c>
-    </row>
-    <row r="225" spans="1:17" x14ac:dyDescent="0.25">
+    </row>
+    <row r="225" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A225" s="8">
         <v>224</v>
       </c>
-      <c r="B225" s="18"/>
-      <c r="C225" s="23"/>
-      <c r="D225" s="23"/>
+      <c r="B225" s="20"/>
+      <c r="C225" s="12"/>
+      <c r="D225" s="12"/>
       <c r="E225" s="8" t="s">
-        <v>848</v>
+        <v>786</v>
       </c>
       <c r="F225" s="8" t="s">
         <v>226</v>
@@ -11519,23 +9194,16 @@
       <c r="K225" s="8"/>
       <c r="L225" s="8"/>
       <c r="M225" s="8"/>
-      <c r="N225" s="15"/>
-      <c r="P225" s="1" t="s">
-        <v>226</v>
-      </c>
-      <c r="Q225" s="1" t="s">
-        <v>848</v>
-      </c>
-    </row>
-    <row r="226" spans="1:17" x14ac:dyDescent="0.25">
+    </row>
+    <row r="226" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A226" s="8">
         <v>225</v>
       </c>
-      <c r="B226" s="18"/>
-      <c r="C226" s="23"/>
-      <c r="D226" s="23"/>
+      <c r="B226" s="20"/>
+      <c r="C226" s="12"/>
+      <c r="D226" s="12"/>
       <c r="E226" s="8" t="s">
-        <v>849</v>
+        <v>787</v>
       </c>
       <c r="F226" s="8" t="s">
         <v>227</v>
@@ -11553,23 +9221,16 @@
       <c r="K226" s="8"/>
       <c r="L226" s="8"/>
       <c r="M226" s="8"/>
-      <c r="N226" s="15"/>
-      <c r="P226" s="1" t="s">
-        <v>227</v>
-      </c>
-      <c r="Q226" s="1" t="s">
-        <v>849</v>
-      </c>
-    </row>
-    <row r="227" spans="1:17" x14ac:dyDescent="0.25">
+    </row>
+    <row r="227" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A227" s="7">
         <v>226</v>
       </c>
-      <c r="B227" s="18"/>
-      <c r="C227" s="23"/>
-      <c r="D227" s="23"/>
+      <c r="B227" s="20"/>
+      <c r="C227" s="12"/>
+      <c r="D227" s="12"/>
       <c r="E227" s="7" t="s">
-        <v>850</v>
+        <v>788</v>
       </c>
       <c r="F227" s="7" t="s">
         <v>228</v>
@@ -11587,23 +9248,16 @@
       <c r="K227" s="7"/>
       <c r="L227" s="7"/>
       <c r="M227" s="7"/>
-      <c r="N227" s="15"/>
-      <c r="P227" s="1" t="s">
-        <v>228</v>
-      </c>
-      <c r="Q227" s="1" t="s">
-        <v>850</v>
-      </c>
-    </row>
-    <row r="228" spans="1:17" x14ac:dyDescent="0.25">
+    </row>
+    <row r="228" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A228" s="7">
         <v>227</v>
       </c>
-      <c r="B228" s="18"/>
-      <c r="C228" s="23"/>
-      <c r="D228" s="23"/>
+      <c r="B228" s="20"/>
+      <c r="C228" s="12"/>
+      <c r="D228" s="12"/>
       <c r="E228" s="7" t="s">
-        <v>851</v>
+        <v>789</v>
       </c>
       <c r="F228" s="7" t="s">
         <v>229</v>
@@ -11621,23 +9275,16 @@
       <c r="K228" s="7"/>
       <c r="L228" s="7"/>
       <c r="M228" s="7"/>
-      <c r="N228" s="15"/>
-      <c r="P228" s="1" t="s">
-        <v>229</v>
-      </c>
-      <c r="Q228" s="1" t="s">
-        <v>851</v>
-      </c>
-    </row>
-    <row r="229" spans="1:17" x14ac:dyDescent="0.25">
+    </row>
+    <row r="229" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A229" s="7">
         <v>228</v>
       </c>
-      <c r="B229" s="18"/>
-      <c r="C229" s="23"/>
-      <c r="D229" s="23"/>
+      <c r="B229" s="20"/>
+      <c r="C229" s="12"/>
+      <c r="D229" s="12"/>
       <c r="E229" s="7" t="s">
-        <v>852</v>
+        <v>790</v>
       </c>
       <c r="F229" s="7" t="s">
         <v>230</v>
@@ -11655,23 +9302,16 @@
       <c r="K229" s="7"/>
       <c r="L229" s="7"/>
       <c r="M229" s="7"/>
-      <c r="N229" s="15"/>
-      <c r="P229" s="1" t="s">
-        <v>230</v>
-      </c>
-      <c r="Q229" s="1" t="s">
-        <v>852</v>
-      </c>
-    </row>
-    <row r="230" spans="1:17" x14ac:dyDescent="0.25">
+    </row>
+    <row r="230" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A230" s="7">
         <v>229</v>
       </c>
-      <c r="B230" s="18"/>
-      <c r="C230" s="23"/>
-      <c r="D230" s="23"/>
+      <c r="B230" s="20"/>
+      <c r="C230" s="12"/>
+      <c r="D230" s="12"/>
       <c r="E230" s="7" t="s">
-        <v>853</v>
+        <v>791</v>
       </c>
       <c r="F230" s="7" t="s">
         <v>231</v>
@@ -11689,23 +9329,16 @@
       <c r="K230" s="7"/>
       <c r="L230" s="7"/>
       <c r="M230" s="7"/>
-      <c r="N230" s="15"/>
-      <c r="P230" s="1" t="s">
-        <v>231</v>
-      </c>
-      <c r="Q230" s="1" t="s">
-        <v>853</v>
-      </c>
-    </row>
-    <row r="231" spans="1:17" x14ac:dyDescent="0.25">
+    </row>
+    <row r="231" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A231" s="7">
         <v>230</v>
       </c>
-      <c r="B231" s="18"/>
-      <c r="C231" s="23"/>
-      <c r="D231" s="23"/>
+      <c r="B231" s="20"/>
+      <c r="C231" s="12"/>
+      <c r="D231" s="12"/>
       <c r="E231" s="7" t="s">
-        <v>854</v>
+        <v>792</v>
       </c>
       <c r="F231" s="7" t="s">
         <v>232</v>
@@ -11723,23 +9356,16 @@
       <c r="K231" s="7"/>
       <c r="L231" s="7"/>
       <c r="M231" s="7"/>
-      <c r="N231" s="15"/>
-      <c r="P231" s="1" t="s">
-        <v>232</v>
-      </c>
-      <c r="Q231" s="1" t="s">
-        <v>854</v>
-      </c>
-    </row>
-    <row r="232" spans="1:17" x14ac:dyDescent="0.25">
+    </row>
+    <row r="232" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A232" s="7">
         <v>231</v>
       </c>
-      <c r="B232" s="18"/>
-      <c r="C232" s="23"/>
-      <c r="D232" s="23"/>
+      <c r="B232" s="20"/>
+      <c r="C232" s="12"/>
+      <c r="D232" s="12"/>
       <c r="E232" s="7" t="s">
-        <v>855</v>
+        <v>793</v>
       </c>
       <c r="F232" s="7" t="s">
         <v>233</v>
@@ -11757,23 +9383,16 @@
       <c r="K232" s="7"/>
       <c r="L232" s="7"/>
       <c r="M232" s="7"/>
-      <c r="N232" s="15"/>
-      <c r="P232" s="1" t="s">
-        <v>233</v>
-      </c>
-      <c r="Q232" s="1" t="s">
-        <v>855</v>
-      </c>
-    </row>
-    <row r="233" spans="1:17" x14ac:dyDescent="0.25">
+    </row>
+    <row r="233" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A233" s="8">
         <v>232</v>
       </c>
-      <c r="B233" s="18"/>
-      <c r="C233" s="23"/>
-      <c r="D233" s="23"/>
+      <c r="B233" s="20"/>
+      <c r="C233" s="12"/>
+      <c r="D233" s="12"/>
       <c r="E233" s="8" t="s">
-        <v>856</v>
+        <v>794</v>
       </c>
       <c r="F233" s="8" t="s">
         <v>234</v>
@@ -11791,23 +9410,16 @@
       <c r="K233" s="8"/>
       <c r="L233" s="8"/>
       <c r="M233" s="8"/>
-      <c r="N233" s="15"/>
-      <c r="P233" s="1" t="s">
-        <v>234</v>
-      </c>
-      <c r="Q233" s="1" t="s">
-        <v>856</v>
-      </c>
-    </row>
-    <row r="234" spans="1:17" x14ac:dyDescent="0.25">
+    </row>
+    <row r="234" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A234" s="8">
         <v>233</v>
       </c>
-      <c r="B234" s="18"/>
-      <c r="C234" s="23"/>
-      <c r="D234" s="23"/>
+      <c r="B234" s="20"/>
+      <c r="C234" s="12"/>
+      <c r="D234" s="12"/>
       <c r="E234" s="8" t="s">
-        <v>857</v>
+        <v>795</v>
       </c>
       <c r="F234" s="8" t="s">
         <v>235</v>
@@ -11825,23 +9437,16 @@
       <c r="K234" s="8"/>
       <c r="L234" s="8"/>
       <c r="M234" s="8"/>
-      <c r="N234" s="15"/>
-      <c r="P234" s="1" t="s">
-        <v>235</v>
-      </c>
-      <c r="Q234" s="1" t="s">
-        <v>857</v>
-      </c>
-    </row>
-    <row r="235" spans="1:17" x14ac:dyDescent="0.25">
+    </row>
+    <row r="235" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A235" s="7">
         <v>234</v>
       </c>
-      <c r="B235" s="18"/>
-      <c r="C235" s="23"/>
-      <c r="D235" s="23"/>
+      <c r="B235" s="20"/>
+      <c r="C235" s="12"/>
+      <c r="D235" s="12"/>
       <c r="E235" s="7" t="s">
-        <v>858</v>
+        <v>796</v>
       </c>
       <c r="F235" s="7" t="s">
         <v>236</v>
@@ -11859,23 +9464,16 @@
       <c r="K235" s="7"/>
       <c r="L235" s="7"/>
       <c r="M235" s="7"/>
-      <c r="N235" s="15"/>
-      <c r="P235" s="1" t="s">
-        <v>236</v>
-      </c>
-      <c r="Q235" s="1" t="s">
-        <v>858</v>
-      </c>
-    </row>
-    <row r="236" spans="1:17" x14ac:dyDescent="0.25">
+    </row>
+    <row r="236" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A236" s="8">
         <v>235</v>
       </c>
-      <c r="B236" s="18"/>
-      <c r="C236" s="23"/>
-      <c r="D236" s="23"/>
+      <c r="B236" s="20"/>
+      <c r="C236" s="12"/>
+      <c r="D236" s="12"/>
       <c r="E236" s="8" t="s">
-        <v>859</v>
+        <v>797</v>
       </c>
       <c r="F236" s="8" t="s">
         <v>237</v>
@@ -11893,23 +9491,16 @@
       <c r="K236" s="8"/>
       <c r="L236" s="8"/>
       <c r="M236" s="8"/>
-      <c r="N236" s="15"/>
-      <c r="P236" s="1" t="s">
-        <v>237</v>
-      </c>
-      <c r="Q236" s="1" t="s">
-        <v>859</v>
-      </c>
-    </row>
-    <row r="237" spans="1:17" x14ac:dyDescent="0.25">
+    </row>
+    <row r="237" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A237" s="8">
         <v>236</v>
       </c>
-      <c r="B237" s="18"/>
-      <c r="C237" s="23"/>
-      <c r="D237" s="23"/>
+      <c r="B237" s="20"/>
+      <c r="C237" s="12"/>
+      <c r="D237" s="12"/>
       <c r="E237" s="8" t="s">
-        <v>860</v>
+        <v>798</v>
       </c>
       <c r="F237" s="8" t="s">
         <v>238</v>
@@ -11927,23 +9518,16 @@
       <c r="K237" s="8"/>
       <c r="L237" s="8"/>
       <c r="M237" s="8"/>
-      <c r="N237" s="15"/>
-      <c r="P237" s="1" t="s">
-        <v>238</v>
-      </c>
-      <c r="Q237" s="1" t="s">
-        <v>860</v>
-      </c>
-    </row>
-    <row r="238" spans="1:17" x14ac:dyDescent="0.25">
+    </row>
+    <row r="238" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A238" s="8">
         <v>237</v>
       </c>
-      <c r="B238" s="18"/>
-      <c r="C238" s="23"/>
-      <c r="D238" s="23"/>
+      <c r="B238" s="20"/>
+      <c r="C238" s="12"/>
+      <c r="D238" s="12"/>
       <c r="E238" s="8" t="s">
-        <v>861</v>
+        <v>799</v>
       </c>
       <c r="F238" s="8" t="s">
         <v>239</v>
@@ -11961,23 +9545,16 @@
       <c r="K238" s="8"/>
       <c r="L238" s="8"/>
       <c r="M238" s="8"/>
-      <c r="N238" s="15"/>
-      <c r="P238" s="1" t="s">
-        <v>239</v>
-      </c>
-      <c r="Q238" s="1" t="s">
-        <v>861</v>
-      </c>
-    </row>
-    <row r="239" spans="1:17" x14ac:dyDescent="0.25">
+    </row>
+    <row r="239" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A239" s="8">
         <v>238</v>
       </c>
-      <c r="B239" s="18"/>
-      <c r="C239" s="23"/>
-      <c r="D239" s="23"/>
+      <c r="B239" s="20"/>
+      <c r="C239" s="12"/>
+      <c r="D239" s="12"/>
       <c r="E239" s="8" t="s">
-        <v>862</v>
+        <v>800</v>
       </c>
       <c r="F239" s="8" t="s">
         <v>240</v>
@@ -11995,23 +9572,16 @@
       <c r="K239" s="8"/>
       <c r="L239" s="8"/>
       <c r="M239" s="8"/>
-      <c r="N239" s="15"/>
-      <c r="P239" s="1" t="s">
-        <v>240</v>
-      </c>
-      <c r="Q239" s="1" t="s">
-        <v>862</v>
-      </c>
-    </row>
-    <row r="240" spans="1:17" x14ac:dyDescent="0.25">
+    </row>
+    <row r="240" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A240" s="8">
         <v>239</v>
       </c>
-      <c r="B240" s="18"/>
-      <c r="C240" s="23"/>
-      <c r="D240" s="23"/>
+      <c r="B240" s="20"/>
+      <c r="C240" s="12"/>
+      <c r="D240" s="12"/>
       <c r="E240" s="8" t="s">
-        <v>863</v>
+        <v>801</v>
       </c>
       <c r="F240" s="8" t="s">
         <v>241</v>
@@ -12029,23 +9599,16 @@
       <c r="K240" s="8"/>
       <c r="L240" s="8"/>
       <c r="M240" s="8"/>
-      <c r="N240" s="15"/>
-      <c r="P240" s="1" t="s">
-        <v>241</v>
-      </c>
-      <c r="Q240" s="1" t="s">
-        <v>863</v>
-      </c>
-    </row>
-    <row r="241" spans="1:17" x14ac:dyDescent="0.25">
+    </row>
+    <row r="241" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A241" s="8">
         <v>240</v>
       </c>
-      <c r="B241" s="18"/>
-      <c r="C241" s="23"/>
-      <c r="D241" s="23"/>
+      <c r="B241" s="20"/>
+      <c r="C241" s="12"/>
+      <c r="D241" s="12"/>
       <c r="E241" s="8" t="s">
-        <v>864</v>
+        <v>802</v>
       </c>
       <c r="F241" s="8" t="s">
         <v>242</v>
@@ -12063,23 +9626,16 @@
       <c r="K241" s="8"/>
       <c r="L241" s="8"/>
       <c r="M241" s="8"/>
-      <c r="N241" s="15"/>
-      <c r="P241" s="1" t="s">
-        <v>242</v>
-      </c>
-      <c r="Q241" s="1" t="s">
-        <v>864</v>
-      </c>
-    </row>
-    <row r="242" spans="1:17" x14ac:dyDescent="0.25">
+    </row>
+    <row r="242" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A242" s="8">
         <v>241</v>
       </c>
-      <c r="B242" s="18"/>
-      <c r="C242" s="23"/>
-      <c r="D242" s="23"/>
+      <c r="B242" s="20"/>
+      <c r="C242" s="12"/>
+      <c r="D242" s="12"/>
       <c r="E242" s="8" t="s">
-        <v>865</v>
+        <v>803</v>
       </c>
       <c r="F242" s="8" t="s">
         <v>243</v>
@@ -12097,23 +9653,16 @@
       <c r="K242" s="8"/>
       <c r="L242" s="8"/>
       <c r="M242" s="8"/>
-      <c r="N242" s="15"/>
-      <c r="P242" s="1" t="s">
-        <v>243</v>
-      </c>
-      <c r="Q242" s="1" t="s">
-        <v>865</v>
-      </c>
-    </row>
-    <row r="243" spans="1:17" x14ac:dyDescent="0.25">
+    </row>
+    <row r="243" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A243" s="8">
         <v>242</v>
       </c>
-      <c r="B243" s="18"/>
-      <c r="C243" s="23"/>
-      <c r="D243" s="23"/>
+      <c r="B243" s="20"/>
+      <c r="C243" s="12"/>
+      <c r="D243" s="12"/>
       <c r="E243" s="8" t="s">
-        <v>866</v>
+        <v>804</v>
       </c>
       <c r="F243" s="8" t="s">
         <v>244</v>
@@ -12131,23 +9680,16 @@
       <c r="K243" s="8"/>
       <c r="L243" s="8"/>
       <c r="M243" s="8"/>
-      <c r="N243" s="15"/>
-      <c r="P243" s="1" t="s">
-        <v>244</v>
-      </c>
-      <c r="Q243" s="1" t="s">
-        <v>866</v>
-      </c>
-    </row>
-    <row r="244" spans="1:17" x14ac:dyDescent="0.25">
+    </row>
+    <row r="244" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A244" s="7">
         <v>243</v>
       </c>
-      <c r="B244" s="18"/>
-      <c r="C244" s="23"/>
-      <c r="D244" s="23"/>
+      <c r="B244" s="20"/>
+      <c r="C244" s="12"/>
+      <c r="D244" s="12"/>
       <c r="E244" s="7" t="s">
-        <v>867</v>
+        <v>805</v>
       </c>
       <c r="F244" s="7" t="s">
         <v>245</v>
@@ -12165,23 +9707,16 @@
       <c r="K244" s="7"/>
       <c r="L244" s="7"/>
       <c r="M244" s="7"/>
-      <c r="N244" s="15"/>
-      <c r="P244" s="1" t="s">
-        <v>245</v>
-      </c>
-      <c r="Q244" s="1" t="s">
-        <v>867</v>
-      </c>
-    </row>
-    <row r="245" spans="1:17" x14ac:dyDescent="0.25">
+    </row>
+    <row r="245" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A245" s="7">
         <v>244</v>
       </c>
-      <c r="B245" s="18"/>
-      <c r="C245" s="23"/>
-      <c r="D245" s="23"/>
+      <c r="B245" s="20"/>
+      <c r="C245" s="12"/>
+      <c r="D245" s="12"/>
       <c r="E245" s="7" t="s">
-        <v>868</v>
+        <v>806</v>
       </c>
       <c r="F245" s="7" t="s">
         <v>246</v>
@@ -12199,23 +9734,16 @@
       <c r="K245" s="7"/>
       <c r="L245" s="7"/>
       <c r="M245" s="7"/>
-      <c r="N245" s="15"/>
-      <c r="P245" s="1" t="s">
-        <v>246</v>
-      </c>
-      <c r="Q245" s="1" t="s">
-        <v>868</v>
-      </c>
-    </row>
-    <row r="246" spans="1:17" x14ac:dyDescent="0.25">
+    </row>
+    <row r="246" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A246" s="7">
         <v>245</v>
       </c>
-      <c r="B246" s="18"/>
-      <c r="C246" s="23"/>
-      <c r="D246" s="23"/>
+      <c r="B246" s="20"/>
+      <c r="C246" s="12"/>
+      <c r="D246" s="12"/>
       <c r="E246" s="7" t="s">
-        <v>869</v>
+        <v>807</v>
       </c>
       <c r="F246" s="7" t="s">
         <v>247</v>
@@ -12233,23 +9761,16 @@
       <c r="K246" s="7"/>
       <c r="L246" s="7"/>
       <c r="M246" s="7"/>
-      <c r="N246" s="15"/>
-      <c r="P246" s="1" t="s">
-        <v>247</v>
-      </c>
-      <c r="Q246" s="1" t="s">
-        <v>869</v>
-      </c>
-    </row>
-    <row r="247" spans="1:17" x14ac:dyDescent="0.25">
+    </row>
+    <row r="247" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A247" s="7">
         <v>246</v>
       </c>
-      <c r="B247" s="18"/>
-      <c r="C247" s="23"/>
-      <c r="D247" s="23"/>
+      <c r="B247" s="20"/>
+      <c r="C247" s="12"/>
+      <c r="D247" s="12"/>
       <c r="E247" s="7" t="s">
-        <v>870</v>
+        <v>808</v>
       </c>
       <c r="F247" s="7" t="s">
         <v>248</v>
@@ -12267,23 +9788,16 @@
       <c r="K247" s="7"/>
       <c r="L247" s="7"/>
       <c r="M247" s="7"/>
-      <c r="N247" s="15"/>
-      <c r="P247" s="1" t="s">
-        <v>248</v>
-      </c>
-      <c r="Q247" s="1" t="s">
-        <v>870</v>
-      </c>
-    </row>
-    <row r="248" spans="1:17" x14ac:dyDescent="0.25">
+    </row>
+    <row r="248" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A248" s="7">
         <v>247</v>
       </c>
-      <c r="B248" s="18"/>
-      <c r="C248" s="23"/>
-      <c r="D248" s="23"/>
+      <c r="B248" s="20"/>
+      <c r="C248" s="12"/>
+      <c r="D248" s="12"/>
       <c r="E248" s="7" t="s">
-        <v>871</v>
+        <v>809</v>
       </c>
       <c r="F248" s="7" t="s">
         <v>249</v>
@@ -12301,23 +9815,16 @@
       <c r="K248" s="7"/>
       <c r="L248" s="7"/>
       <c r="M248" s="7"/>
-      <c r="N248" s="15"/>
-      <c r="P248" s="1" t="s">
-        <v>249</v>
-      </c>
-      <c r="Q248" s="1" t="s">
-        <v>871</v>
-      </c>
-    </row>
-    <row r="249" spans="1:17" x14ac:dyDescent="0.25">
+    </row>
+    <row r="249" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A249" s="7">
         <v>248</v>
       </c>
-      <c r="B249" s="18"/>
-      <c r="C249" s="23"/>
-      <c r="D249" s="23"/>
+      <c r="B249" s="20"/>
+      <c r="C249" s="12"/>
+      <c r="D249" s="12"/>
       <c r="E249" s="7" t="s">
-        <v>872</v>
+        <v>810</v>
       </c>
       <c r="F249" s="7" t="s">
         <v>250</v>
@@ -12335,23 +9842,16 @@
       <c r="K249" s="7"/>
       <c r="L249" s="7"/>
       <c r="M249" s="7"/>
-      <c r="N249" s="15"/>
-      <c r="P249" s="1" t="s">
-        <v>250</v>
-      </c>
-      <c r="Q249" s="1" t="s">
-        <v>872</v>
-      </c>
-    </row>
-    <row r="250" spans="1:17" x14ac:dyDescent="0.25">
+    </row>
+    <row r="250" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A250" s="7">
         <v>249</v>
       </c>
-      <c r="B250" s="18"/>
-      <c r="C250" s="23"/>
-      <c r="D250" s="23"/>
+      <c r="B250" s="20"/>
+      <c r="C250" s="12"/>
+      <c r="D250" s="12"/>
       <c r="E250" s="7" t="s">
-        <v>873</v>
+        <v>811</v>
       </c>
       <c r="F250" s="7" t="s">
         <v>251</v>
@@ -12369,23 +9869,16 @@
       <c r="K250" s="7"/>
       <c r="L250" s="7"/>
       <c r="M250" s="7"/>
-      <c r="N250" s="15"/>
-      <c r="P250" s="1" t="s">
-        <v>251</v>
-      </c>
-      <c r="Q250" s="1" t="s">
-        <v>873</v>
-      </c>
-    </row>
-    <row r="251" spans="1:17" x14ac:dyDescent="0.25">
+    </row>
+    <row r="251" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A251" s="7">
         <v>250</v>
       </c>
-      <c r="B251" s="18"/>
-      <c r="C251" s="23"/>
-      <c r="D251" s="23"/>
+      <c r="B251" s="20"/>
+      <c r="C251" s="12"/>
+      <c r="D251" s="12"/>
       <c r="E251" s="7" t="s">
-        <v>874</v>
+        <v>812</v>
       </c>
       <c r="F251" s="7" t="s">
         <v>252</v>
@@ -12403,23 +9896,16 @@
       <c r="K251" s="7"/>
       <c r="L251" s="7"/>
       <c r="M251" s="7"/>
-      <c r="N251" s="15"/>
-      <c r="P251" s="1" t="s">
-        <v>252</v>
-      </c>
-      <c r="Q251" s="1" t="s">
-        <v>874</v>
-      </c>
-    </row>
-    <row r="252" spans="1:17" x14ac:dyDescent="0.25">
+    </row>
+    <row r="252" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A252" s="7">
         <v>251</v>
       </c>
-      <c r="B252" s="18"/>
-      <c r="C252" s="23"/>
-      <c r="D252" s="23"/>
+      <c r="B252" s="20"/>
+      <c r="C252" s="12"/>
+      <c r="D252" s="12"/>
       <c r="E252" s="7" t="s">
-        <v>875</v>
+        <v>813</v>
       </c>
       <c r="F252" s="7" t="s">
         <v>253</v>
@@ -12437,23 +9923,16 @@
       <c r="K252" s="7"/>
       <c r="L252" s="7"/>
       <c r="M252" s="7"/>
-      <c r="N252" s="15"/>
-      <c r="P252" s="1" t="s">
-        <v>253</v>
-      </c>
-      <c r="Q252" s="1" t="s">
-        <v>875</v>
-      </c>
-    </row>
-    <row r="253" spans="1:17" x14ac:dyDescent="0.25">
+    </row>
+    <row r="253" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A253" s="8">
         <v>252</v>
       </c>
-      <c r="B253" s="18"/>
-      <c r="C253" s="23"/>
-      <c r="D253" s="23"/>
+      <c r="B253" s="20"/>
+      <c r="C253" s="12"/>
+      <c r="D253" s="12"/>
       <c r="E253" s="8" t="s">
-        <v>876</v>
+        <v>814</v>
       </c>
       <c r="F253" s="8" t="s">
         <v>254</v>
@@ -12471,23 +9950,16 @@
       <c r="K253" s="8"/>
       <c r="L253" s="8"/>
       <c r="M253" s="8"/>
-      <c r="N253" s="15"/>
-      <c r="P253" s="1" t="s">
-        <v>254</v>
-      </c>
-      <c r="Q253" s="1" t="s">
-        <v>876</v>
-      </c>
-    </row>
-    <row r="254" spans="1:17" x14ac:dyDescent="0.25">
+    </row>
+    <row r="254" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A254" s="8">
         <v>253</v>
       </c>
-      <c r="B254" s="18"/>
-      <c r="C254" s="23"/>
-      <c r="D254" s="23"/>
+      <c r="B254" s="20"/>
+      <c r="C254" s="12"/>
+      <c r="D254" s="12"/>
       <c r="E254" s="8" t="s">
-        <v>877</v>
+        <v>815</v>
       </c>
       <c r="F254" s="8" t="s">
         <v>255</v>
@@ -12505,23 +9977,16 @@
       <c r="K254" s="8"/>
       <c r="L254" s="8"/>
       <c r="M254" s="8"/>
-      <c r="N254" s="15"/>
-      <c r="P254" s="1" t="s">
-        <v>255</v>
-      </c>
-      <c r="Q254" s="1" t="s">
-        <v>877</v>
-      </c>
-    </row>
-    <row r="255" spans="1:17" x14ac:dyDescent="0.25">
+    </row>
+    <row r="255" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A255" s="8">
         <v>254</v>
       </c>
-      <c r="B255" s="18"/>
-      <c r="C255" s="23"/>
-      <c r="D255" s="23"/>
+      <c r="B255" s="20"/>
+      <c r="C255" s="12"/>
+      <c r="D255" s="12"/>
       <c r="E255" s="8" t="s">
-        <v>878</v>
+        <v>816</v>
       </c>
       <c r="F255" s="8" t="s">
         <v>256</v>
@@ -12539,23 +10004,16 @@
       <c r="K255" s="8"/>
       <c r="L255" s="8"/>
       <c r="M255" s="8"/>
-      <c r="N255" s="15"/>
-      <c r="P255" s="1" t="s">
-        <v>256</v>
-      </c>
-      <c r="Q255" s="1" t="s">
-        <v>878</v>
-      </c>
-    </row>
-    <row r="256" spans="1:17" x14ac:dyDescent="0.25">
+    </row>
+    <row r="256" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A256" s="8">
         <v>255</v>
       </c>
-      <c r="B256" s="18"/>
-      <c r="C256" s="23"/>
-      <c r="D256" s="23"/>
+      <c r="B256" s="20"/>
+      <c r="C256" s="12"/>
+      <c r="D256" s="12"/>
       <c r="E256" s="8" t="s">
-        <v>879</v>
+        <v>817</v>
       </c>
       <c r="F256" s="8" t="s">
         <v>257</v>
@@ -12573,23 +10031,16 @@
       <c r="K256" s="8"/>
       <c r="L256" s="8"/>
       <c r="M256" s="8"/>
-      <c r="N256" s="15"/>
-      <c r="P256" s="1" t="s">
-        <v>257</v>
-      </c>
-      <c r="Q256" s="1" t="s">
-        <v>879</v>
-      </c>
-    </row>
-    <row r="257" spans="1:18" x14ac:dyDescent="0.25">
+    </row>
+    <row r="257" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A257" s="8">
         <v>256</v>
       </c>
-      <c r="B257" s="18"/>
-      <c r="C257" s="23"/>
-      <c r="D257" s="23"/>
+      <c r="B257" s="20"/>
+      <c r="C257" s="12"/>
+      <c r="D257" s="12"/>
       <c r="E257" s="8" t="s">
-        <v>880</v>
+        <v>818</v>
       </c>
       <c r="F257" s="8" t="s">
         <v>258</v>
@@ -12607,23 +10058,16 @@
       <c r="K257" s="8"/>
       <c r="L257" s="8"/>
       <c r="M257" s="8"/>
-      <c r="N257" s="15"/>
-      <c r="P257" s="1" t="s">
-        <v>258</v>
-      </c>
-      <c r="Q257" s="1" t="s">
-        <v>880</v>
-      </c>
-    </row>
-    <row r="258" spans="1:18" x14ac:dyDescent="0.25">
+    </row>
+    <row r="258" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A258" s="7">
         <v>257</v>
       </c>
-      <c r="B258" s="18"/>
-      <c r="C258" s="23"/>
-      <c r="D258" s="23"/>
+      <c r="B258" s="20"/>
+      <c r="C258" s="12"/>
+      <c r="D258" s="12"/>
       <c r="E258" s="7" t="s">
-        <v>881</v>
+        <v>819</v>
       </c>
       <c r="F258" s="7" t="s">
         <v>259</v>
@@ -12641,25 +10085,18 @@
       <c r="K258" s="7"/>
       <c r="L258" s="7"/>
       <c r="M258" s="7"/>
-      <c r="N258" s="15"/>
-      <c r="P258" s="1" t="s">
-        <v>259</v>
-      </c>
-      <c r="Q258" s="1" t="s">
-        <v>881</v>
-      </c>
-    </row>
-    <row r="259" spans="1:18" x14ac:dyDescent="0.25">
+    </row>
+    <row r="259" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A259" s="5">
         <v>258</v>
       </c>
-      <c r="B259" s="12" t="s">
+      <c r="B259" s="24" t="s">
         <v>568</v>
       </c>
-      <c r="C259" s="24"/>
-      <c r="D259" s="24"/>
+      <c r="C259" s="13"/>
+      <c r="D259" s="13"/>
       <c r="E259" s="5" t="s">
-        <v>882</v>
+        <v>820</v>
       </c>
       <c r="F259" s="5" t="s">
         <v>260</v>
@@ -12677,25 +10114,16 @@
       <c r="K259" s="5"/>
       <c r="L259" s="5"/>
       <c r="M259" s="5"/>
-      <c r="N259" s="15"/>
-      <c r="O259" s="1"/>
-      <c r="P259" s="1" t="s">
-        <v>260</v>
-      </c>
-      <c r="Q259" s="1" t="s">
-        <v>882</v>
-      </c>
-      <c r="R259" s="1"/>
-    </row>
-    <row r="260" spans="1:18" x14ac:dyDescent="0.25">
+    </row>
+    <row r="260" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A260" s="5">
         <v>259</v>
       </c>
-      <c r="B260" s="13"/>
-      <c r="C260" s="24"/>
-      <c r="D260" s="24"/>
+      <c r="B260" s="25"/>
+      <c r="C260" s="13"/>
+      <c r="D260" s="13"/>
       <c r="E260" s="5" t="s">
-        <v>883</v>
+        <v>821</v>
       </c>
       <c r="F260" s="5" t="s">
         <v>261</v>
@@ -12713,24 +10141,16 @@
       <c r="K260" s="5"/>
       <c r="L260" s="5"/>
       <c r="M260" s="5"/>
-      <c r="N260" s="15"/>
-      <c r="O260" s="1"/>
-      <c r="P260" s="1" t="s">
-        <v>261</v>
-      </c>
-      <c r="Q260" s="1" t="s">
-        <v>883</v>
-      </c>
-    </row>
-    <row r="261" spans="1:18" x14ac:dyDescent="0.25">
+    </row>
+    <row r="261" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A261" s="6">
         <v>260</v>
       </c>
-      <c r="B261" s="13"/>
-      <c r="C261" s="24"/>
-      <c r="D261" s="24"/>
+      <c r="B261" s="25"/>
+      <c r="C261" s="13"/>
+      <c r="D261" s="13"/>
       <c r="E261" s="6" t="s">
-        <v>884</v>
+        <v>822</v>
       </c>
       <c r="F261" s="6" t="s">
         <v>262</v>
@@ -12748,25 +10168,16 @@
       <c r="K261" s="6"/>
       <c r="L261" s="6"/>
       <c r="M261" s="6"/>
-      <c r="N261" s="15"/>
-      <c r="O261" s="1"/>
-      <c r="P261" s="1" t="s">
-        <v>262</v>
-      </c>
-      <c r="Q261" s="1" t="s">
-        <v>884</v>
-      </c>
-      <c r="R261" s="1"/>
-    </row>
-    <row r="262" spans="1:18" x14ac:dyDescent="0.25">
+    </row>
+    <row r="262" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A262" s="5">
         <v>261</v>
       </c>
-      <c r="B262" s="14"/>
-      <c r="C262" s="24"/>
-      <c r="D262" s="24"/>
+      <c r="B262" s="26"/>
+      <c r="C262" s="13"/>
+      <c r="D262" s="13"/>
       <c r="E262" s="5" t="s">
-        <v>885</v>
+        <v>823</v>
       </c>
       <c r="F262" s="5" t="s">
         <v>263</v>
@@ -12784,21 +10195,14 @@
       <c r="K262" s="5"/>
       <c r="L262" s="5"/>
       <c r="M262" s="5"/>
-      <c r="N262" s="15"/>
-      <c r="P262" s="1" t="s">
-        <v>263</v>
-      </c>
-      <c r="Q262" s="1" t="s">
-        <v>885</v>
-      </c>
-    </row>
-    <row r="263" spans="1:18" x14ac:dyDescent="0.25">
+    </row>
+    <row r="263" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A263" s="6">
         <v>262</v>
       </c>
-      <c r="B263" s="28"/>
-      <c r="C263" s="24"/>
-      <c r="D263" s="24"/>
+      <c r="B263" s="17"/>
+      <c r="C263" s="13"/>
+      <c r="D263" s="13"/>
       <c r="E263" s="6" t="s">
         <v>564</v>
       </c>
@@ -12814,10 +10218,6 @@
       <c r="K263" s="6"/>
       <c r="L263" s="6"/>
       <c r="M263" s="6"/>
-      <c r="N263" s="15"/>
-      <c r="Q263" t="s">
-        <v>564</v>
-      </c>
     </row>
   </sheetData>
   <mergeCells count="5">
@@ -12842,10 +10242,10 @@
   <sheetData>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>918</v>
+        <v>856</v>
       </c>
       <c r="B2" t="s">
-        <v>917</v>
+        <v>855</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
@@ -12853,23 +10253,23 @@
         <v>403</v>
       </c>
       <c r="B3" t="s">
-        <v>916</v>
+        <v>854</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>919</v>
+        <v>857</v>
       </c>
       <c r="B4" t="s">
-        <v>916</v>
+        <v>854</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>920</v>
+        <v>858</v>
       </c>
       <c r="B5" t="s">
-        <v>916</v>
+        <v>854</v>
       </c>
     </row>
   </sheetData>

--- a/data/template/boq/BOQ Documentation.xlsx
+++ b/data/template/boq/BOQ Documentation.xlsx
@@ -8,20 +8,21 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\JACOBS\SERVICE\API\data\template\boq\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F8A2A263-974A-404F-B2E5-6E06898FFC61}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2B00A3D2-B59D-4F51-B9A0-525EAD92B4B1}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12105" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12105" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Save" sheetId="3" r:id="rId1"/>
-    <sheet name="Question" sheetId="5" r:id="rId2"/>
+    <sheet name="BOQ Sheet" sheetId="3" r:id="rId1"/>
+    <sheet name="BOQ PR Sheet" sheetId="6" r:id="rId2"/>
+    <sheet name="Question" sheetId="5" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1323" uniqueCount="859">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1389" uniqueCount="887">
   <si>
     <t>program</t>
   </si>
@@ -2598,6 +2599,93 @@
   </si>
   <si>
     <t>Test OTDR</t>
+  </si>
+  <si>
+    <t>Variable</t>
+  </si>
+  <si>
+    <t>num</t>
+  </si>
+  <si>
+    <t>permit</t>
+  </si>
+  <si>
+    <t>shop_incl_pole_aerial</t>
+  </si>
+  <si>
+    <t>shop_excl_pole_aerial</t>
+  </si>
+  <si>
+    <t>shop_burial</t>
+  </si>
+  <si>
+    <t>comcase</t>
+  </si>
+  <si>
+    <t>mat_pole_7</t>
+  </si>
+  <si>
+    <t>mat_pole_9</t>
+  </si>
+  <si>
+    <t>mat_cable_fo_24</t>
+  </si>
+  <si>
+    <t>mat_cable_fo_96</t>
+  </si>
+  <si>
+    <t>mat_hdpe</t>
+  </si>
+  <si>
+    <t>total_e2e_dist</t>
+  </si>
+  <si>
+    <t>pole_exist</t>
+  </si>
+  <si>
+    <t>Shopping List Pekerjaan FO Intersite 
+(Incl. Instalasi Pole) - Aerial (All In)</t>
+  </si>
+  <si>
+    <t>Shopping List Pekerjaan FO Intersite 
+(Excl. Instalasi Pole) - Aerial (All In)</t>
+  </si>
+  <si>
+    <t>Shopping List Pekerjaan FO Intersite
+- Burial (All In)</t>
+  </si>
+  <si>
+    <t>Comcase</t>
+  </si>
+  <si>
+    <t>Material HDPE</t>
+  </si>
+  <si>
+    <t>Pole Exist</t>
+  </si>
+  <si>
+    <t>Column</t>
+  </si>
+  <si>
+    <t>Material Pole 7</t>
+  </si>
+  <si>
+    <t>Material Pole 9</t>
+  </si>
+  <si>
+    <t>Material Kabel FO 24 C</t>
+  </si>
+  <si>
+    <t>Material Kabel FO 96 C</t>
+  </si>
+  <si>
+    <t>meter</t>
+  </si>
+  <si>
+    <t>Permit (Arial - Burial) All In</t>
+  </si>
+  <si>
+    <t>Formula berbeda di XL sama dengan material HDPE di Surge material/2</t>
   </si>
 </sst>
 </file>
@@ -2740,7 +2828,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="27">
+  <cellXfs count="30">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -2803,6 +2891,11 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -10233,6 +10326,264 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5863C4C0-30E9-48D3-B4AA-B4587F53915C}">
+  <dimension ref="A1:C22"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="71.28515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="6.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="22" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1" s="27" t="s">
+        <v>879</v>
+      </c>
+      <c r="B1" s="27" t="s">
+        <v>464</v>
+      </c>
+      <c r="C1" s="27" t="s">
+        <v>859</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2" s="28" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" s="28" t="s">
+        <v>432</v>
+      </c>
+      <c r="C2" s="29" t="s">
+        <v>860</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3" s="28" t="s">
+        <v>4</v>
+      </c>
+      <c r="B3" s="28" t="s">
+        <v>432</v>
+      </c>
+      <c r="C3" s="29" t="s">
+        <v>556</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4" s="28" t="s">
+        <v>5</v>
+      </c>
+      <c r="B4" s="28" t="s">
+        <v>432</v>
+      </c>
+      <c r="C4" s="29" t="s">
+        <v>557</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5" s="28" t="s">
+        <v>6</v>
+      </c>
+      <c r="B5" s="28" t="s">
+        <v>432</v>
+      </c>
+      <c r="C5" s="29" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A6" s="28" t="s">
+        <v>7</v>
+      </c>
+      <c r="B6" s="28" t="s">
+        <v>432</v>
+      </c>
+      <c r="C6" s="29" t="s">
+        <v>558</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A7" s="28" t="s">
+        <v>8</v>
+      </c>
+      <c r="B7" s="28" t="s">
+        <v>432</v>
+      </c>
+      <c r="C7" s="29" t="s">
+        <v>559</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A8" s="28" t="s">
+        <v>9</v>
+      </c>
+      <c r="B8" s="28" t="s">
+        <v>432</v>
+      </c>
+      <c r="C8" s="29" t="s">
+        <v>555</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A9" s="28" t="s">
+        <v>10</v>
+      </c>
+      <c r="B9" s="28" t="s">
+        <v>432</v>
+      </c>
+      <c r="C9" s="29" t="s">
+        <v>560</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A10" s="28" t="s">
+        <v>11</v>
+      </c>
+      <c r="B10" s="28" t="s">
+        <v>432</v>
+      </c>
+      <c r="C10" s="29" t="s">
+        <v>561</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A11" s="28" t="s">
+        <v>885</v>
+      </c>
+      <c r="B11" s="28" t="s">
+        <v>884</v>
+      </c>
+      <c r="C11" s="29" t="s">
+        <v>861</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A12" s="28" t="s">
+        <v>873</v>
+      </c>
+      <c r="B12" s="28" t="s">
+        <v>884</v>
+      </c>
+      <c r="C12" s="29" t="s">
+        <v>862</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A13" s="28" t="s">
+        <v>874</v>
+      </c>
+      <c r="B13" s="28" t="s">
+        <v>884</v>
+      </c>
+      <c r="C13" s="29" t="s">
+        <v>863</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A14" s="28" t="s">
+        <v>875</v>
+      </c>
+      <c r="B14" s="28" t="s">
+        <v>884</v>
+      </c>
+      <c r="C14" s="29" t="s">
+        <v>864</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A15" s="28" t="s">
+        <v>876</v>
+      </c>
+      <c r="B15" s="28" t="s">
+        <v>884</v>
+      </c>
+      <c r="C15" s="29" t="s">
+        <v>865</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A16" s="28" t="s">
+        <v>880</v>
+      </c>
+      <c r="B16" s="28" t="s">
+        <v>463</v>
+      </c>
+      <c r="C16" s="29" t="s">
+        <v>866</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A17" s="28" t="s">
+        <v>881</v>
+      </c>
+      <c r="B17" s="28" t="s">
+        <v>463</v>
+      </c>
+      <c r="C17" s="29" t="s">
+        <v>867</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A18" s="28" t="s">
+        <v>882</v>
+      </c>
+      <c r="B18" s="28" t="s">
+        <v>884</v>
+      </c>
+      <c r="C18" s="29" t="s">
+        <v>868</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A19" s="28" t="s">
+        <v>883</v>
+      </c>
+      <c r="B19" s="28" t="s">
+        <v>884</v>
+      </c>
+      <c r="C19" s="29" t="s">
+        <v>869</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A20" s="28" t="s">
+        <v>877</v>
+      </c>
+      <c r="B20" s="28" t="s">
+        <v>884</v>
+      </c>
+      <c r="C20" s="29" t="s">
+        <v>870</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A21" s="28" t="s">
+        <v>16</v>
+      </c>
+      <c r="B21" s="28" t="s">
+        <v>884</v>
+      </c>
+      <c r="C21" s="29" t="s">
+        <v>871</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A22" s="28" t="s">
+        <v>878</v>
+      </c>
+      <c r="B22" s="28" t="s">
+        <v>884</v>
+      </c>
+      <c r="C22" s="29" t="s">
+        <v>872</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9CA441E6-6BE3-4CCB-8299-2EEB305EB638}">
   <dimension ref="A2:B5"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -10261,7 +10612,7 @@
         <v>857</v>
       </c>
       <c r="B4" t="s">
-        <v>854</v>
+        <v>886</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
